--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S551"/>
+  <dimension ref="A1:S601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -41752,6 +41752,3846 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>EX-0551</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Let's take this to a vote.</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>意見が割れたときに、多数決で決めようという提案。</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>If we can't agree, let's take this to a vote.</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>意見が一致しないなら、多数決で決めましょう。</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Let's take this to a vote so we can move on.</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>先に進めるように、これは多数決にしましょう。</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Let's put it to a vote.</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>EX-0552</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>I'll defer to the group on this.</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>自分の意見よりチーム全体の判断に従うという意味。</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>I don't have a strong preference, so I'll defer to the group on this.</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>強いこだわりはないので、この件はチームの判断に従います。</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>I'll go with whatever the team decides.</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>EX-0553</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Can we get consensus before we move on?</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>次に進む前に全員の合意が取れているか確認するフレーズ。</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Can we get consensus before we move on to the next item?</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>次の議題に進む前に、みんなの合意を確認できますか？</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Let's make sure we get consensus before we move on.</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>進む前に、必ず合意を取っておきましょう。</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>全員の意見を確認したいときに使う、やや慎重なニュアンス。</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>EX-0554</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Let's put a bookmark on this and continue.</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>この議題に印をつけておいて、後で戻る前提で先に進もうという表現。</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>We're low on time, so let's put a bookmark on this and continue.</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>時間がないので、これは印をつけておいて先に進みましょう。</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>Let's park that for now.</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>EX-0555</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>I want to make sure we're not talking past each other.</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>お互いの話がかみ合っていないのではと確認するときの表現。</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>I want to make sure we're not talking past each other — can you rephrase your concern?</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>話がすれ違っていないか確認したいのですが、懸念点を言い換えてもらえますか？</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Let's slow down; I want to make sure we're not talking past each other.</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>少しペースを落としましょう、話がかみ合っているか確認したいので。</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>議論が平行線になっていると感じたときに使う。</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>EX-0556</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Let's set a placeholder for now and confirm later.</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>今は仮の内容にしておき、後で正式に確認しようという表現。</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>We don't have final numbers yet, so let's set a placeholder for now and confirm later.</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>まだ最終的な数字が出ていないので、今は仮置きにして後で確認しましょう。</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>EX-0557</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Can we drill down into the specifics?</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>全体像ではなく詳細な部分をもっと詳しく見たいときの表現。</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Before we conclude, can we drill down into the specifics of the budget?</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>結論を出す前に、予算の詳細をもう少し掘り下げられますか？</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>I'd like to drill down into the specifics of this proposal.</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>この提案の詳細をもっと掘り下げたいです。</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Let's dig deeper into this.</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>EX-0558</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>I think we're overcomplicating this.</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>議論が必要以上に複雑になっていると指摘するフレーズ。</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>I think we're overcomplicating this — can we simplify the approach?</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>これは複雑にしすぎている気がします。もっとシンプルなやり方にできませんか？</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>Let's not overthink this.</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>相手の案を否定しすぎないよう、トーンには注意する。</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>EX-0559</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Let's keep the ball rolling.</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>この勢いのまま進めよう、という意味。</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Great progress so far — let's keep the ball rolling.</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>ここまで順調ですね。この調子で進めましょう。</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Let's keep the ball rolling and finish this by Friday.</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>この勢いのまま、金曜日までに終わらせましょう。</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>Let's keep the momentum going.</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>EX-0560</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Can we get a sense of the room on this?</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>この場にいる人たちの大まかな意見や雰囲気を知りたいときの表現。</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Before we decide, can we get a sense of the room on this?</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>決定する前に、みなさんの大体の意見を聞かせてもらえますか？</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Can we get a show of hands on this?</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>EX-0561</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>What do you do for fun outside of work?</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>仕事以外の趣味を尋ねる、雑談の定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>What do you do for fun outside of work?</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>仕事以外では何をして楽しんでいますか？</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>So, what do you do for fun outside of work these days?</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>最近、仕事以外では何をして楽しんでいますか？</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>What do you like to do in your free time?</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>EX-0562</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>I'm still finding my feet here.</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>新しい環境にまだ慣れていないという意味。</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>It's only my second week, so I'm still finding my feet here.</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>まだ2週目なので、この職場にはまだ慣れていないんです。</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>I'm still getting the hang of things.</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>EX-0563</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>You look like you could use a vacation.</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>相手が疲れているように見えるときにかける気遣いの言葉。</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>You look like you could use a vacation — everything okay?</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>休暇が必要そうに見えますよ。大丈夫ですか？</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>EX-0564</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>It's been a whirlwind week.</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>慌ただしく忙しい一週間だった、という表現。</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>It's been a whirlwind week, but we finally hit our targets.</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>慌ただしい一週間でしたが、なんとか目標を達成しました。</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Sorry for the slow reply, it's been a whirlwind week.</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>返信が遅くなってすみません、今週は慌ただしくて。</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>EX-0565</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>I'm counting down the days to the holidays.</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>休暇を心待ちにしているという表現。</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Only two more weeks — I'm counting down the days to the holidays.</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>あと2週間だけ。休暇が待ち遠しいです。</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>EX-0566</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>How's the family doing?</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>家族の様子を尋ねる、親しい間柄での雑談フレーズ。</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>How's the family doing? I heard your daughter started school.</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>ご家族はお元気ですか？娘さんが学校に入ったと聞きました。</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>EX-0567</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Same time, same place next week?</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>いつもの時間・場所で来週も会うかを確認する表現。</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Great catching up — same time, same place next week?</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>話せてよかったです。来週も同じ時間・場所でいいですか？</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>Same time next week?</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>EX-0568</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Please see below for my response.</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>返信内容が下に続いていることを伝えるメール表現。</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Thanks for your questions — please see below for my response.</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>ご質問ありがとうございます。回答は以下をご覧ください。</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>My response is below.</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>EX-0569</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>I'll loop back once I have an update.</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>進捗があり次第、改めて連絡するという表現。</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Nothing to report yet — I'll loop back once I have an update.</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>まだ報告できることはありません。進捗があり次第、改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>I'll loop back once I have an update from the vendor.</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>ベンダーから連絡があり次第、改めてお伝えします。</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>I'll circle back once I hear more.</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>EX-0570</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Kindly confirm at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>できるだけ早く確認・返信してほしいと丁寧に依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Kindly confirm at your earliest convenience so we can proceed.</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>進めるために、できるだけ早くご確認いただけますと幸いです。</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Please confirm as soon as possible.</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>やや硬い表現なので、社外向けやフォーマルなメールに向く。</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>EX-0571</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Please let me know if this timeline works for you.</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>提示したスケジュールで問題ないか確認する表現。</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Please let me know if this timeline works for you, or suggest an alternative.</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>このスケジュールで問題なければ教えてください。難しければ代案をご提案ください。</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>EX-0572</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>I'm following up in case this got buried in your inbox.</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>返信がない相手に、埋もれてしまっているかもしれないと柔らかくリマインドする表現。</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Just following up in case this got buried in your inbox.</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>埋もれてしまっているかもしれないので、念のため再度ご連絡しました。</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Just bumping this to the top of your inbox.</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>催促を柔らかく伝えたいときに便利な表現。</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>EX-0573</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Thank you for your prompt reply.</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>早い返信への感謝を伝える定番のメール表現。</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Thank you for your prompt reply — this is very helpful.</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>迅速なご返信ありがとうございます。大変助かります。</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>EX-0574</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Please advise on how you'd like to proceed.</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>今後どう進めたいか、相手の指示を仰ぐ表現。</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Given the delay, please advise on how you'd like to proceed.</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>遅延が発生しているため、今後の進め方についてご指示いただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Please let us know how you would like us to proceed.</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>EX-0575</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>I've included everyone for visibility.</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>情報共有のために関係者全員をCCに入れたことを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>I've included everyone for visibility, but no action is needed from most of you.</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>情報共有のため全員を含めていますが、ほとんどの方はご対応不要です。</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>EX-0576</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Apologies for the delayed response; I was out of office.</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>不在にしていたため返信が遅れたことを謝る表現。</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Apologies for the delayed response; I was out of office last week.</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>返信が遅くなり申し訳ございません。先週は不在にしておりました。</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>EX-0577</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Could you hold the line for a moment?</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>電話口で少し待ってほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Could you hold the line for a moment while I check?</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>確認しますので、少しそのままお待ちいただけますか？</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Could you hold for just a second?</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>EX-0578</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>I'm having trouble hearing you — can you switch to a landline?</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>音声が聞き取りづらいので固定電話に切り替えてほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>I'm having trouble hearing you — can you switch to a landline?</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>声が聞き取りにくいのですが、固定電話に切り替えていただけますか？</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>EX-0579</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Let me transfer you to the right extension.</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>適切な内線に電話をつなぐという表現。</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Let me transfer you to the right extension for billing questions.</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>請求に関するお問い合わせは、担当の内線におつなぎします。</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>I'll transfer you to the right department.</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>EX-0580</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Thanks for holding, sorry about that.</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>待たせたことをお詫びする、電話対応での定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Thanks for holding, sorry about that — I'm back now.</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>お待たせしてすみません、戻りました。</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>EX-0581</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Can I get your callback number in case we get disconnected?</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>通話が切れた場合に備えて、折り返し用の電話番号を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Can I get your callback number in case we get disconnected?</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>通話が切れた場合に備えて、折り返し用の電話番号を伺えますか？</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>EX-0582</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>I'll ring you back within the hour.</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>1時間以内に折り返し電話をするという表現。</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>I need to check with my manager first, but I'll ring you back within the hour.</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>まず上司に確認しますが、1時間以内に折り返します。</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>I'll call you right back.</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>EX-0583</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Is this line secure for us to discuss this?</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>機密性の高い内容を話す前に、回線の安全性を確認する表現。</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Before we go further, is this line secure for us to discuss this?</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>この先の話をする前に、この回線は安全でしょうか？</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>契約金額や個人情報など、機密事項を話す前に使う。</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>EX-0584</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Let's jump straight to the numbers.</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>前置きを省いて、すぐにデータの説明に入ろうという表現。</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>I'll skip the intro — let's jump straight to the numbers.</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>前置きは省きますので、すぐに数字の説明に入りましょう。</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>EX-0585</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>I'll leave time for questions at the end.</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>質疑応答の時間をプレゼンの最後に設けるという表現。</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>I'll leave time for questions at the end, so please hold them until then.</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>最後に質疑応答の時間を設けますので、それまで質問はお待ちください。</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>I'll leave the technical Q&amp;A for after the session.</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>EX-0586</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>This slide sums up our strategy going forward.</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>このスライドが今後の戦略の要点をまとめているという表現。</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>This slide sums up our strategy going forward for the next fiscal year.</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>このスライドは来期に向けた戦略の要点をまとめたものです。</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>EX-0587</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Let me back up and explain the context.</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>話を少し戻して背景を説明しようという表現。</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Let me back up and explain the context before diving into the results.</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>結果に入る前に、少し話を戻して背景を説明させてください。</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>Let me back up for a second.</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>EX-0588</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>I'll hand it over to my colleague for the demo.</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>デモの説明を同僚に引き継ぐという表現。</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>That covers the overview — I'll hand it over to my colleague for the demo.</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>概要は以上です。ここからは同僚がデモをご案内します。</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>I'll hand it over to...</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>EX-0589</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>That concludes my presentation, thank you for your attention.</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>プレゼンを締めくくる定番の表現。</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>That concludes my presentation, thank you for your attention today.</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>以上でプレゼンを終わります。本日はご清聴ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>That wraps up my presentation.</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>EX-0590</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Let's zoom in on this particular trend.</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>全体ではなく、ある特定の傾向を詳しく見ようという表現。</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Let's zoom in on this particular trend before we discuss the forecast.</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>予測の話をする前に、この特定の傾向を詳しく見てみましょう。</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Let's take a closer look at this data point.</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>EX-0591</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Would you be willing to lend a hand with this?</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>手伝ってもらえるか、丁寧に頼む表現。</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Would you be willing to lend a hand with this before the deadline?</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>締め切り前に、これを手伝っていただけないでしょうか。</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>Could you give me a hand with this?</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>EX-0592</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>依頼・断り,交渉</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>I'm afraid that's outside the scope of what I can commit to.</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>自分が対応できる範囲を超えているため難しいと断る表現。</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>I'm afraid that's outside the scope of what I can commit to right now.</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが、現時点でお約束できる範囲を超えています。</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>断る際に、理由（範囲外である）を添えて角を立てにくくする表現。</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>EX-0593</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>I hate to impose, but could you cover for me tomorrow?</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>申し訳ないと思いつつ、代わってもらえるか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>I hate to impose, but could you cover for me tomorrow morning?</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>申し訳ないのですが、明日の朝、代わっていただけませんか？</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>I hate to be a bother, but...</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>EX-0594</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Unfortunately, my schedule won't allow it this time.</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>スケジュールの都合で対応できないと丁寧に断る表現。</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Unfortunately, my schedule won't allow it this time, but let's find another opportunity.</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>残念ながら今回はスケジュールの都合で難しいですが、また別の機会にぜひ。</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>EX-0595</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>依頼・断り,雑談</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>I'll have to take a rain check on that.</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>今回は見送って、また今度にしてほしいという意味の慣用表現。</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>I'd love to join, but I'll have to take a rain check on that.</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>参加したいのですが、今回は見送らせてください。</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Can I take a rain check on lunch this week?</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>今週のランチは、また今度にさせてもらえますか？</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>カジュアルな誘いを断るときによく使われる。</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>EX-0596</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>We're willing to meet you partway on this.</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>双方が歩み寄れる範囲で妥協する用意があるという表現。</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>We're willing to meet you partway on this if you can adjust the timeline.</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>スケジュールを調整いただけるなら、こちらもある程度歩み寄る用意があります。</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Let's see if we can meet in the middle.</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>EX-0597</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Let's find terms that work for both sides.</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>双方にとって都合の良い条件を探ろうという表現。</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Instead of arguing over the price, let's find terms that work for both sides.</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>価格でもめるより、双方にとって良い条件を探しましょう。</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>EX-0598</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>That's not quite within reach for us right now.</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>提示された条件には現時点で応じられないと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>That's not quite within reach for us right now, but we could revisit it next quarter.</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>それは現時点では少し難しいですが、来四半期にまた検討できます。</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>That's a bit outside our budget.</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>EX-0599</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Would you consider a phased payment instead?</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>一括ではなく分割での支払いを提案する表現。</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Would you consider a phased payment instead of paying the full amount upfront?</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>全額前払いの代わりに、分割払いをご検討いただけますか？</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>EX-0600</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>We'd need firmer commitments before moving forward.</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>先に進む前に、より確実な約束が欲しいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>We'd need firmer commitments before moving forward with the full contract.</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>正式な契約に進む前に、より確実なお約束をいただく必要があります。</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>慎重に交渉を進めたいときの表現。強すぎない程度に懸念を伝えられる。</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S601"/>
+  <dimension ref="A1:S651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -45592,6 +45592,3796 @@
         </is>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>EX-0601</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Let's park the follow-up questions for the Q&amp;A.</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>フォローアップの質問は質疑応答の時間に回そうという提案。</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Let's park the follow-up questions for the Q&amp;A at the end.</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>フォローアップの質問は最後の質疑応答の時間に回しましょう。</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>We can park that question for the Q&amp;A session.</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>その質問は質疑応答のときに回せますね。</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Let's save that for the Q&amp;A,Let's table that until Q&amp;A</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>EX-0602</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Can we get through the agenda a bit faster?</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>議題をもう少し早く進められないか提案する表現。</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Can we get through the agenda a bit faster? We're running behind.</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>議題をもう少し早く進められますか？予定より遅れています。</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Can we pick up the pace?</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>EX-0603</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>I'd like to table a formal proposal for next quarter.</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>来四半期に向けて正式な提案を提出したいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>I'd like to table a formal proposal for next quarter's budget.</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>来四半期の予算について正式な提案を提出したいと思います。</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>We'll table a formal proposal once the numbers are finalized.</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>数字が確定次第、正式な提案を提出します。</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>"table"はイギリス英語では「提出する」、アメリカ英語では「棚上げする」の意味になることがあるため文脈に注意。</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>EX-0604</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Let's not lose the thread of this conversation.</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>話の要点や流れを見失わないようにしようという表現。</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Let's not lose the thread of this conversation — we were talking about the budget.</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>話の流れを見失わないようにしましょう。予算の話をしていましたね。</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>I lost the thread for a second — could you recap?</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>一瞬話についていけなくなりました。要点をもう一度お願いできますか？</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>lose track of the conversation</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>EX-0605</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>会議,電話</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Could everyone mute themselves when not speaking?</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>オンライン会議で発言時以外はミュートにするよう依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Could everyone mute themselves when not speaking? There's some background noise.</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>発言していないときはミュートにしていただけますか？雑音が入っているようです。</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>EX-0606</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Let's take a five-minute break before we continue.</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>続ける前に5分程度の休憩を取ろうと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Let's take a five-minute break before we continue with the second half.</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>後半に入る前に5分ほど休憩を取りましょう。</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Would everyone like a quick break before we continue?</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>続ける前に少し休憩を取りますか？</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>take a short recess</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>EX-0607</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>I think we've covered everything on today's agenda.</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>本日の議題をすべて終えたと確認・宣言する表現。</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>I think we've covered everything on today's agenda. Any final comments?</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>本日の議題はすべて終えたと思います。最後に何かコメントはありますか？</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>That wraps up today's agenda</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>EX-0608</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Can we push this item to the next meeting?</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>この議題を次回の会議に持ち越せないか提案する表現。</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>We're running short on time — can we push this item to the next meeting?</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>時間が足りなくなってきたので、この議題は次回に持ち越せますか？</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Let's push the budget discussion to next week's meeting.</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>予算の議論は来週の会議に持ち越しましょう。</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>table this for next time</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>EX-0609</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>What do you usually do to unwind after work?</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>仕事終わりの過ごし方を尋ねる雑談表現。</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>What do you usually do to unwind after work?</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>仕事終わりは普段どうやってリラックスしていますか？</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>I usually go for a run to unwind after work.</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>仕事終わりはたいてい走ってリラックスしています。</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>EX-0610</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Did you manage to catch up on sleep this weekend?</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>週末に睡眠不足を解消できたか尋ねる雑談表現。</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Did you manage to catch up on sleep this weekend?</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>週末は寝不足を解消できましたか？</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>EX-0611</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>It's been a scorcher this week, hasn't it?</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>今週はとても暑かったですね、という天気についての雑談表現。</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>It's been a scorcher this week, hasn't it? I can barely stand the heat.</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>今週はかなり暑かったですね。もう暑さに耐えられません。</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>It's been boiling hot lately</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>"scorcher"は「非常に暑い日」を指すカジュアルな口語表現。</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>EX-0612</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>雑談,メール</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Are you working from home tomorrow?</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>明日は在宅勤務かどうかを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Are you working from home tomorrow, or will you be in the office?</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>明日は在宅勤務ですか、それとも出社されますか？</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>EX-0613</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>I heard you just got back from a trip — how was it?</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>旅行から戻ったばかりの相手にどうだったか尋ねる雑談表現。</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>I heard you just got back from a trip — how was it?</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>旅行から戻ったばかりだと聞きました。どうでしたか？</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>It was amazing, thanks for asking!</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>すごく良かったです、聞いてくれてありがとう！</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>EX-0614</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Please see the attached for your reference.</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>参考として添付ファイルを確認してほしいと伝えるメール表現。</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Please see the attached for your reference and let me know if you have questions.</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>ご参考までに添付をご確認ください。ご質問があればお知らせください。</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Please find attached</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>EX-0615</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>I'm writing to follow up on the item below.</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>以前のメールの内容についてフォローアップすることを伝える書き出し表現。</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>I'm writing to follow up on the item below regarding the contract renewal.</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>下記の契約更新の件についてフォローアップのご連絡です。</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>I'm following up on my previous email</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>EX-0616</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Kindly let us know your preferred time slot.</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>希望の時間帯を教えてほしいと丁寧に依頼するメール表現。</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Kindly let us know your preferred time slot for the call.</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>お電話のご希望の時間帯をお知らせください。</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>EX-0617</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Please expect a formal response within 48 hours.</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>正式な返答を48時間以内に送ることを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Please expect a formal response within 48 hours of submission.</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>ご提出後48時間以内に正式な回答をお送りいたします。</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>EX-0618</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>This email serves as confirmation of our agreement.</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>このメールが合意事項の確認として機能することを示す表現。</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>This email serves as confirmation of our agreement reached during today's call.</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>本メールは本日の通話で合意した内容の確認とさせていただきます。</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>This email confirms our agreement</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>EX-0619</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>We apologize for any confusion caused by our earlier message.</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>以前のメールで生じた混乱について謝罪する表現。</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>We apologize for any confusion caused by our earlier message regarding the schedule.</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>スケジュールに関する以前のメールで混乱を招いたことをお詫びいたします。</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>EX-0620</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Please reach out should you require further assistance.</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>さらにサポートが必要な場合は連絡してほしいと伝える結びの表現。</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Please reach out should you require further assistance with the setup.</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>設定についてさらにサポートが必要な場合はご連絡ください。</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>Don't hesitate to reach out</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>EX-0621</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I look that up?</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>調べる間、少し待ってほしいと頼む電話表現。</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I look that up in our system?</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>システムで確認する間、少々お待ちいただけますか？</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Could you hold for a moment?</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>EX-0622</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>I'll transfer your call to the appropriate extension.</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>適切な内線に電話を転送することを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>I'll transfer your call to the appropriate extension right away.</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>すぐに適切な内線にお電話をお繋ぎいたします。</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>EX-0623</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Sorry, you cut out for a second — could you repeat that?</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>電話の音声が一瞬途切れたため聞き返す表現。</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Sorry, you cut out for a second — could you repeat that last part?</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>すみません、一瞬音声が途切れました。今の部分をもう一度お願いできますか？</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>You broke up for a second</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>EX-0624</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Let me just confirm your account details before we proceed.</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>手続きを進める前にアカウント情報を確認する電話表現。</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Let me just confirm your account details before we proceed with the request.</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>ご依頼を進める前に、アカウント情報を確認させてください。</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>EX-0625</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Thanks for your patience while I pull up your file.</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>ファイルを表示する間待たせたことへの感謝・お詫びの表現。</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Thanks for your patience while I pull up your file.</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>ファイルを表示する間、お待たせして申し訳ございません。</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>EX-0626</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>依頼,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>I'll make sure this gets escalated right away.</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>この件をすぐに上位担当へエスカレーションすると約束する表現。</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>I'll make sure this gets escalated right away so we can resolve it quickly.</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>迅速に解決できるよう、すぐにこの件をエスカレーションいたします。</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>EX-0627</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Let's move on to the next section of today's talk.</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>発表の次のセクションに移ることを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Let's move on to the next section of today's talk.</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>それでは本日の発表の次のセクションに移りましょう。</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Moving on to the next part</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>EX-0628</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>I'll leave the details in the appendix for those interested.</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>詳細は興味のある人のために付録に載せておくと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>I'll leave the details in the appendix for those interested in the methodology.</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>方法論の詳細については、興味のある方のために付録に記載しておきます。</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>EX-0629</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>This chart illustrates the trend over the past year.</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>このグラフが過去1年の傾向を示していると説明する表現。</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>This chart illustrates the trend over the past year in customer growth.</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>このグラフは過去1年間の顧客数増加の傾向を示しています。</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>EX-0630</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Let me pause here to check we're all following.</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>皆が理解できているか確認するため一旦止まる表現。</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Let me pause here to check we're all following before I continue.</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>続ける前に、ここで一旦止まって皆さんが理解できているか確認させてください。</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>Let me check we're all on the same page</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>EX-0631</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>That brings us to the end of today's presentation.</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>本日の発表の終わりであることを示す締めの表現。</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>That brings us to the end of today's presentation. Thank you for listening.</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>以上で本日の発表を終わります。ご清聴ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>That concludes today's presentation</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>EX-0632</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Feel free to reach out after the session with any questions.</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>セッション後に質問があれば連絡してほしいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Feel free to reach out after the session with any questions you might have.</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>何か質問があれば、セッション後にお気軽にご連絡ください。</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>EX-0633</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Would you mind covering this while I'm away?</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>不在の間、代わりに対応してほしいと依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Would you mind covering this while I'm away next week?</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>来週不在の間、これを代わりに対応していただけますか？</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Could you cover for me while I'm out?</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>EX-0634</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not something I can take on right now.</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>現在それを引き受けることができないと丁寧に断る表現。</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not something I can take on right now given my workload.</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>今の業務量では、それを引き受けるのは難しいと思います。</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>EX-0635</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Could I trouble you to double-check these figures?</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>数字を再確認してほしいと丁寧に頼む表現。</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Could I trouble you to double-check these figures before we submit the report?</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>レポートを提出する前に、この数字を再確認していただけますか？</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>EX-0636</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>I appreciate the offer, but I'll have to pass.</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>提案はありがたいが、今回は見送ると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>I appreciate the offer, but I'll have to pass this time.</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>お誘いはありがたいのですが、今回は見送らせていただきます。</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>I'll have to pass this time</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>EX-0637</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>依頼・断り,メール</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Unfortunately, my calendar is fully booked this week.</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>今週の予定がすでに埋まっていることを伝える断りの表現。</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Unfortunately, my calendar is fully booked this week. Could we look at next week instead?</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>あいにく今週の予定はすでに埋まっております。来週で調整可能でしょうか？</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>EX-0638</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Would it be possible to get an extra pair of hands on this?</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>追加の人手を借りられないか依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Would it be possible to get an extra pair of hands on this before the deadline?</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>締め切り前に、もう少し人手を借りることは可能でしょうか？</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>an extra pair of hands</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>EX-0639</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>I hate to add to your plate, but could you help with this?</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>相手の負担を増やすことを申し訳なく思いつつ依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>I hate to add to your plate, but could you help with this one more thing?</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>これ以上お願いするのは申し訳ないのですが、もう一つ手伝っていただけますか？</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>"have a lot on your plate"（やることが多い）という表現と関連。</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>EX-0640</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>依頼・断り,雑談</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>I'm going to have to sit this one out.</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>今回は参加せず見送ることを伝えるカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>I'm going to have to sit this one out — I'm just too swamped.</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>今回は見送らせてください。あまりに忙しくて。</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>EX-0641</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>We'd need to see some concessions on your end as well.</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>相手側にも譲歩を求める交渉表現。</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>We'd need to see some concessions on your end as well before we agree to this.</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>これに合意する前に、そちらにもいくつか譲歩していただく必要があります。</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>EX-0642</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Is there any flexibility on the delivery timeline?</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>納期に融通が利くか尋ねる交渉表現。</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Is there any flexibility on the delivery timeline given our current volume?</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>現在の発注量を考慮すると、納期に融通は利きますか？</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>EX-0643</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>We're willing to lock in a longer contract for a better rate.</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>より良い料金と引き換えに長期契約を結んでもよいと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>We're willing to lock in a longer contract for a better rate.</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>より良い料金であれば、長期契約を結ぶことも可能です。</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>EX-0644</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Let's find a number that works for both parties.</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>双方にとって納得できる金額を見つけようと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Let's find a number that works for both parties before we finalize.</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>最終決定の前に、双方にとって納得できる金額を見つけましょう。</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>find a middle ground</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>EX-0645</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>反論・懸念,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>That's a stretch for us, but we can look into it.</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>こちらにとっては厳しい条件だが検討はできると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>That's a stretch for us, but we can look into it and get back to you.</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>それはこちらにとっては厳しい条件ですが、検討して改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>EX-0646</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>We'd be open to revisiting this once volumes increase.</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>取引量が増えれば改めて検討する用意があると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>We'd be open to revisiting this once volumes increase next year.</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>来年取引量が増えれば、改めてこの件を検討することは可能です。</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>EX-0647</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Can we settle on these terms and finalize the paperwork?</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>これらの条件で合意し、書類を確定させようと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Can we settle on these terms and finalize the paperwork by Friday?</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>金曜日までにこれらの条件で合意し、書類を確定できますか？</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>EX-0648</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>We're not far apart — let's close the gap.</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>条件の差はわずかなので、その差を埋めようと提案する交渉表現。</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>We're not far apart — let's close the gap and get this signed.</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>そこまで大きな差はないので、その差を埋めて契約を締結しましょう。</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>EX-0649</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Would you consider a trial period before committing long-term?</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>長期契約の前に試用期間を設けることを提案する表現。</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Would you consider a trial period before committing long-term?</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>長期契約を結ぶ前に、試用期間を設けることをご検討いただけますか？</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>EX-0650</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Let's put together a term sheet and go from there.</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>条件概要書（タームシート）を作成し、それを基に進めようと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Let's put together a term sheet and go from there.</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>まずはタームシートを作成し、そこから進めていきましょう。</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>"term sheet"は投資や取引の主要条件をまとめた文書。</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S651"/>
+  <dimension ref="A1:S701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -49382,6 +49382,3726 @@
         </is>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>EX-0651</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Let's touch base before the deadline.</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>締め切り前に一度連絡を取り合おう、という意味。</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Let's touch base before the deadline so we're both aligned.</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>締め切り前に一度連絡を取り合って、認識をすり合わせましょう。</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>I'll touch base with you on Wednesday.</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>水曜日に一度連絡しますね。</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>check in</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>EX-0652</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>メール,雑談</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>I'll shoot you an email with the details.</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>詳細をメールで送るね、というカジュアルな言い方。</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>I'll shoot you an email with the details later today.</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>今日中に詳細をメールで送りますね。</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Can you shoot me an email with the updated numbers?</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>最新の数字をメールで送ってもらえますか？</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>send an email</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>shoot はカジュアルな口語表現。</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>EX-0653</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>会議,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Could we push the meeting back by an hour?</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>会議を1時間後ろにずらせないか、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Could we push the meeting back by an hour? Something's come up.</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>用事ができたので、会議を1時間後ろにずらせますか？</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Sure, pushing it back to 3 PM works for me.</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>はい、3時に後ろ倒しで大丈夫です。</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>move the meeting</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>EX-0654</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>I'm afraid I'll have to jump off this call early.</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>申し訳ないが早めに通話から抜けなければならない、という表現。</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>I'm afraid I'll have to jump off this call early for another meeting.</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>恐れ入りますが、別の会議があるため早めに通話を抜けなければなりません。</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>drop off the call</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>EX-0655</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Let's not lose sight of the end goal.</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>最終目標を見失わないようにしよう、という呼びかけ。</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Let's not lose sight of the end goal amid all these details.</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>細かい話に気を取られて、最終目標を見失わないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>EX-0656</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>I'll need to double-check with legal before signing off.</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>法務に確認してから承認する必要がある、という保留表現。</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>I'll need to double-check with legal before signing off on this contract.</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>この契約書に承認印を押す前に、法務に確認する必要があります。</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Let me get back to you once legal has reviewed it.</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>法務が確認した後、改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>EX-0657</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>We're on the same team here.</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>対立せず協力していこう、という一体感を示す表現。</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Let's remember we're on the same team here.</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>私たちは同じチームだということを忘れないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>EX-0658</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Let's not put too fine a point on it.</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>遠回しに言わず、率直に言おう、という前置き表現。</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Let's not put too fine a point on it: the project is behind schedule.</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>率直に言いますが、このプロジェクトは予定より遅れています。</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>to put it bluntly</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>やや硬い言い回しで、フォーマルな場面向き。</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>EX-0659</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>I'll take the lead on this one.</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>この件は自分が主導する、という申し出。</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>I'll take the lead on this one and keep everyone posted.</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>この件は私が主導しますので、随時共有します。</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>spearhead</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>EX-0660</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Could you loop in the finance team?</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>財務チームを話に加えてほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Could you loop in the finance team on this thread?</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>このメールのやり取りに財務チームも加えてもらえますか？</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>cc someone</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>EX-0661</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Let's not lock ourselves into anything just yet.</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>まだ何も確約せず、選択肢を残しておこう、という提案。</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Let's not lock ourselves into anything just yet — we might get a better offer.</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>もっと良い条件が出るかもしれないので、まだ何も確約しないでおきましょう。</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>keep our options open</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>EX-0662</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>I'll defer to whoever has more context here.</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>この件について詳しい人の判断に従う、という表現。</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>I'll defer to whoever has more context here — I just joined the project.</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>私はまだこのプロジェクトに参加したばかりなので、詳しい方の判断に従います。</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>EX-0663</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Can we sanity-test this before rolling it out?</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>展開する前に一度妥当性を確認しよう、という提案。</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Can we sanity-test this before rolling it out to all users?</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>全ユーザーに展開する前に、一度妥当性を確認できますか？</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>sanity-check</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>EX-0664</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>I appreciate you flagging that so early.</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>早めに指摘してくれたことへの感謝。</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>I appreciate you flagging that so early — it gives us time to fix it.</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>早めに指摘してくれてありがとうございます。おかげで対応する時間ができました。</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>EX-0665</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Let's keep our powder dry on this until we hear back.</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>返事が来るまで動かず様子を見よう、という表現。</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Let's keep our powder dry on this until we hear back from legal.</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>法務からの返事があるまで、この件は動かずに様子を見ましょう。</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>hold off</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>やや軍事由来の慣用句で、フォーマルな交渉場面で使われる。</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>EX-0666</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>We'd like to explore other avenues before committing.</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>決める前に他の選択肢も検討したい、という表現。</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>We'd like to explore other avenues before committing to this vendor.</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>このベンダーに決める前に、他の選択肢も検討したいと考えています。</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>EX-0667</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>I don't want to jump the gun here.</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>早まった判断をしたくない、という表現。</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>I don't want to jump the gun here — let's wait for the full report.</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>早まった判断はしたくないので、報告書が揃うまで待ちましょう。</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>EX-0668</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>メール,交渉</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Could we get this in writing for the record?</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>記録に残すため文書化してほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Could we get this agreement in writing for the record?</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>この合意内容を記録として書面にしてもらえますか？</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>EX-0669</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>I'll flag this to the right stakeholders.</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>関係者に共有・報告する、という表現。</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>I'll flag this to the right stakeholders so nothing gets missed.</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>見落としがないよう、関係者にこの件を共有します。</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>EX-0670</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Let's not lose the forest for the trees.</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>細部にとらわれて全体像を見失わないように、という慣用句。</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Let's not lose the forest for the trees — focus on the overall strategy first.</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>細部にとらわれて全体像を見失わないよう、まず全体戦略に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>don't lose sight of the big picture</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>EX-0671</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>We're stretched pretty thin this quarter.</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>今四半期は人手・時間に余裕がない、という表現。</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>We're stretched pretty thin this quarter with two people out.</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>今四半期は2人が休んでいて、かなり手が回っていません。</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>short-staffed</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>EX-0672</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Could you give me the lay of the land before I start?</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>始める前に状況・概要を教えてほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Could you give me the lay of the land before I start on this project?</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>このプロジェクトを始める前に、大まかな状況を教えてもらえますか？</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>EX-0673</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>交渉,電話</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>I'll circle the wagons with my team and get back to you.</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>社内でチームと相談し体制を整えてから返答する、という表現。</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>I'll circle the wagons with my team and get back to you by tomorrow.</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>チームと相談して体制を整えてから、明日までにご連絡します。</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>circle the wagons はもともと「守りを固める」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>EX-0674</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Let's not overpromise and underdeliver here.</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>実現できないことを約束しないようにしよう、という戒め。</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Let's not overpromise and underdeliver on the launch date.</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>発売日について、実現できない約束はしないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>EX-0675</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>We're happy to entertain other proposals.</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>他の提案も前向きに検討する、という表現。</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>We're happy to entertain other proposals if this doesn't work for you.</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>この条件が合わなければ、他のご提案も前向きに検討いたします。</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>EX-0676</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>I'll need to run the numbers again before confirming.</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>確認前にもう一度数字を計算し直す必要がある、という表現。</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>I'll need to run the numbers again before confirming the budget.</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>予算を確定させる前に、もう一度数字を計算し直す必要があります。</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>EX-0677</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Could we get a status update by end of day?</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>今日中に進捗を教えてほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Could we get a status update by end of day on the migration?</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>移行作業について、今日中に進捗を教えてもらえますか？</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Sure, I'll send an update by 5 PM.</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>はい、5時までに進捗を送りますね。</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>EX-0678</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>That's not quite what I had in mind.</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>想定していたものと少し違う、と穏やかに伝える表現。</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>That's not quite what I had in mind, but let's discuss it further.</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>少し想定していたものとは違いますが、もう少し話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>EX-0679</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Let's not overthink the small stuff.</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>細かいことを気にしすぎないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Let's not overthink the small stuff and just move forward.</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>細かいことは気にしすぎず、とにかく前に進みましょう。</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>EX-0680</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>I'll leave that decision in your hands.</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>その判断はあなたに任せる、という表現。</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>I'll leave that decision in your hands since you know the client best.</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>クライアントのことを一番よく知っているあなたに、その判断は任せます。</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>EX-0681</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>We're a bit gun-shy after last quarter's numbers.</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>前四半期の結果を受けて慎重になっている、という表現。</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>We're a bit gun-shy after last quarter's numbers, so we're being cautious.</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>前四半期の数字を受けて少し慎重になっているので、今回は用心しています。</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>gun-shy はもともと「臆病になった」という口語表現。</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>EX-0682</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Could you weigh in before we finalize this?</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>最終決定の前に意見を聞かせてほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Could you weigh in before we finalize this proposal?</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>この提案を確定させる前に、ご意見を聞かせてもらえますか？</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>EX-0683</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>I'll take that under advisement.</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>その意見を検討材料として受け止める、というフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>I'll take that under advisement and discuss it with the board.</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>そのご意見は検討材料として受け止め、役員会で議論します。</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>EX-0684</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Let's not burn any bridges here.</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>関係を壊さないよう慎重に進めよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Let's not burn any bridges here — we may need to work with them again.</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>また一緒に仕事をする可能性もあるので、関係を壊さないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>EX-0685</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>We should have this buttoned up by Friday.</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>金曜日までにきちんと片付けておくべきだ、という表現。</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>We should have this buttoned up by Friday so we can present it Monday.</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>月曜日に発表できるよう、金曜日までにきちんと仕上げておくべきです。</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>wrap up</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>EX-0686</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>I'll need a moment to gather my thoughts.</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>少し考えをまとめる時間がほしい、という表現。</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>I'll need a moment to gather my thoughts before answering.</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>お答えする前に、少し考えをまとめる時間をいただけますか。</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>EX-0687</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Could we get everyone rowing in the same direction?</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>全員が同じ方向を向いて協力できるようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Could we get everyone rowing in the same direction before the launch?</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>発売前に、全員が同じ方向を向いて協力できるようにしませんか？</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>on the same page</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>EX-0688</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>雑談,交渉</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>That's music to my ears.</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>それは嬉しい知らせだ、という表現。</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>You got the approval? That's music to my ears!</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>承認が下りたんですね？それは嬉しい知らせです！</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>EX-0689</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Let's not put the burden entirely on one team.</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>負担を一つのチームだけに偏らせないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Let's not put the burden entirely on one team — let's share the workload.</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>負担を一つのチームだけに偏らせず、作業を分担しましょう。</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>EX-0690</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>I'll need to sleep on it before deciding.</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>決める前に一晩考えたい、という表現。</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>I'll need to sleep on it before deciding whether to accept the offer.</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>このオファーを受けるかどうか、決める前に一晩考えさせてください。</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>EX-0691</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>We're keeping our options open for now.</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>今のところ選択肢を絞らず様子を見ている、という表現。</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>We're keeping our options open for now until we see other bids.</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>他の入札を見るまでは、今のところ選択肢を絞らずにいます。</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>EX-0692</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Could you break that down for me in simpler terms?</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>もっと簡単な言葉で説明してほしい、という依頼。</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Could you break that down for me in simpler terms? I'm not familiar with the jargon.</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>専門用語に詳しくないので、もっと簡単な言葉で説明してもらえますか？</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>EX-0693</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>I'll be the first to admit I got that wrong.</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>自分の間違いを率直に認める、という表現。</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>I'll be the first to admit I got that wrong — let's fix it together.</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>私が間違えていたことは素直に認めます。一緒に修正しましょう。</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>EX-0694</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Let's not throw good money after bad.</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>失敗した投資にさらに資金をつぎ込まないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Let's not throw good money after bad on this failing project.</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>失敗しているこのプロジェクトに、これ以上お金をつぎ込まないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>投資判断の場面でよく使われる慣用句。</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>EX-0695</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>We're all ears on this one.</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>ぜひ聞きたい、注目している、という表現。</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Go ahead, we're all ears on this one.</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>どうぞ、この件についてぜひお聞きしたいです。</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>EX-0696</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>I'll need buy-in from the whole team before proceeding.</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>進める前にチーム全体の同意が必要だ、という表現。</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>I'll need buy-in from the whole team before proceeding with this change.</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>この変更を進める前に、チーム全体の同意が必要です。</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>EX-0697</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Could we get this over the finish line by Friday?</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>金曜日までに完成させられないか、という依頼。</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Could we get this over the finish line by Friday? The client is waiting.</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>クライアントが待っているので、金曜日までに完成させられますか？</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>wrap up</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>EX-0698</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>That's a can of worms we'd rather not open.</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>触れると厄介な問題になるので避けたい、という表現。</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>That's a can of worms we'd rather not open right before the deadline.</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>締め切り直前にその問題に触れると厄介なことになるので、避けたいですね。</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>EX-0699</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Let's not put the finishing touches on this too early.</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>早い段階で仕上げにかからないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Let's not put the finishing touches on this too early — feedback might change things.</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>フィードバックで内容が変わるかもしれないので、早い段階で仕上げにかからないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>EX-0700</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>I'll take that on board and get back to you.</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>その意見を受け止めて、後で返答する、という表現。</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>I'll take that on board and get back to you with our revised proposal.</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>そのご意見を受け止めて、修正した提案で改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S701"/>
+  <dimension ref="A1:S751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -53102,6 +53102,4106 @@
         </is>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>EX-0701</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Let's park the minor issues and focus on the big rocks.</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>些末な問題は後回しにして、重要な課題に集中しようという提案。</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Let's park the minor issues and focus on the big rocks for today's meeting.</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>今日の会議では、細かい問題は後回しにして重要な課題に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>We only have an hour, so let's park the minor issues and focus on the big rocks.</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>1時間しかないので、細かい話は置いておいて重要な点に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>let's prioritize the key issues,let's focus on what matters most</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>"big rocks"はビジネス英語で「最重要事項」を指す比喩表現。</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>EX-0702</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>提案,確認</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Can we timebox this discussion to ten minutes?</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>この議題の議論時間を10分に制限しようという提案。</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Can we timebox this discussion to ten minutes so we can move on to the next item?</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>次の議題に移れるように、この議論を10分に区切りませんか。</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Let's timebox this to fifteen minutes and revisit if needed.</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>15分で区切って、必要ならまた後で戻りましょう。</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>let's set a time limit on this</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>EX-0703</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>提案,確認</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Let's assign a DRI for each action item.</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>各アクションアイテムに責任者(DRI: Directly Responsible Individual)を割り当てようという提案。</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Let's assign a DRI for each action item before we close the meeting.</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>会議を終える前に、各アクションアイテムに責任者を割り当てましょう。</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>let's designate an owner for this</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>"DRI"はIT・スタートアップ業界でよく使われる略語。フォーマルな場では正式名称を添えるとよい。</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>EX-0704</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Could we do a round-robin so everyone gets a chance to speak?</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>参加者全員が順番に発言できるようにしようという提案。</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Could we do a round-robin so everyone gets a chance to speak before we decide?</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>決定する前に、全員が順番に発言できるようにしませんか。</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Let's do a quick round-robin to hear everyone's initial thoughts.</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>まずは全員の第一印象を聞くために、簡単に一巡しましょう。</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>let's go around the room</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>EX-0705</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Let's capture that as a parking lot item.</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>その話題は一旦保留にして別途リストに記録しておこうという提案。</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>That's a good point, but let's capture that as a parking lot item for now.</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>いい指摘ですが、それは一旦保留リストに記録しておきましょう。</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>I'll capture that as a parking lot item and we'll revisit it next week.</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>それは保留リストに入れておいて、来週改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>let's put a pin in that</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>EX-0706</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>I'll take the pen on drafting the summary.</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>自分が議事録・要約の作成担当を引き受けるという表現。</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>I'll take the pen on drafting the summary and share it by tomorrow.</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>私が要約の作成を担当して、明日までに共有します。</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>I'll take the lead on writing this up</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>"take the pen"は「文書作成の主担当になる」という比喩表現。</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>EX-0707</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Can we get alignment on the rollout plan before we adjourn?</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>会議を終える前に展開計画について全員の合意を得たいという表現。</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Can we get alignment on the rollout plan before we adjourn today?</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>今日の会議を終える前に、展開計画について合意を得られますか。</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Let's make sure we have alignment on the rollout plan before moving forward.</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>先に進む前に、展開計画について合意が取れていることを確認しましょう。</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>let's make sure everyone's on the same page</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>EX-0708</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>提案,確認</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Let's do a quick gut-check before finalizing.</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>最終決定する前に直感的な意見を簡単に確認しようという表現。</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Let's do a quick gut-check before finalizing the budget numbers.</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>予算の数字を確定する前に、簡単に感触を確認しましょう。</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Before we finalize, can I get a gut-check from the team?</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>確定する前に、チームの率直な意見を聞かせてもらえますか。</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>let's get a sense of the room</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>EX-0709</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>I'd like to table a counter-proposal.</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>対案を正式に提示したいという表現。</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>I'd like to table a counter-proposal based on today's discussion.</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>本日の議論を踏まえて、対案を提示させていただきたいと思います。</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>I'd like to propose an alternative</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>米では"table"は「棚上げする」の意味にもなるため文脈に注意。ここでは「正式に提出する」の意味（英式用法）。</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>EX-0710</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>How's the new hire settling in?</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>新しく入社した人がうまく馴染んでいるか尋ねるカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>How's the new hire settling in on your team?</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>あなたのチームの新入社員はうまく馴染んでいますか。</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>How's the new hire settling in? Any questions I can help with?</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>新入社員はうまくやっていますか。何か手伝えることはありますか。</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>how's the new person doing</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>EX-0711</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Did you manage to unplug over the long weekend?</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>連休中にきちんと仕事から離れてリフレッシュできたか尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Did you manage to unplug over the long weekend, or did work follow you?</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>連休中はちゃんと仕事から離れられましたか、それとも仕事に追われましたか。</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>did you get a chance to relax</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>"unplug"は「仕事や通知から意識的に離れる」という口語表現。</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>EX-0712</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>I heard the office is moving floors next month.</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>オフィスが来月フロア移転すると聞いたという雑談の切り出し。</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>I heard the office is moving floors next month — do you know which one?</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>来月オフィスがフロア移転すると聞きましたが、何階かご存知ですか。</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>I heard the office is moving floors next month. Have you heard anything?</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>来月フロア移転があると聞きましたが、何か聞いていますか。</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>EX-0713</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>雑談,電話</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Are you dialing in from home today?</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>今日は自宅から電話・会議に参加しているのか尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Are you dialing in from home today, or are you at the office?</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>今日は自宅から参加していますか、それともオフィスにいますか。</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>are you calling in from home</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>EX-0714</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Any exciting plans for the company offsite?</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>社外研修・合宿について何か楽しみな予定があるか尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Any exciting plans for the company offsite next month?</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>来月の社外研修、何か楽しみな予定はありますか。</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Any exciting plans for the company offsite, or just the usual team-building stuff?</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>社外研修は何か特別な予定がありますか、それともいつも通りのチームビルディングですか。</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>"offsite"は社外で行う研修・合宿・戦略会議などを指す。</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>EX-0715</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>I'm writing to seek your approval on the attached proposal.</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>添付の提案書について承認を求めるフォーマルなメール表現。</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>I'm writing to seek your approval on the attached proposal before we proceed.</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>先に進める前に、添付の提案書についてご承認をいただきたくご連絡いたしました。</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>I'm writing to seek your approval on the attached budget revision.</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>添付の予算修正案について、ご承認をいただきたくご連絡いたします。</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>I'm reaching out for your sign-off on...</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>EX-0716</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Kindly find enclosed the revised contract for your signature.</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>署名用に修正済みの契約書を同封している旨を伝えるフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Kindly find enclosed the revised contract for your signature at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>ご都合のよいときに、署名用の修正済み契約書を同封しておりますのでご確認ください。</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>please find attached the revised contract</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>"enclosed"は郵送物、"attached"はメール添付でよく使われるが、フォーマルなメールでは両方使われることがある。</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>EX-0717</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>確認,依頼</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Please let me know if the attached figures require any adjustment.</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>添付の数字に修正が必要かどうか確認を求める表現。</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Please let me know if the attached figures require any adjustment before the deadline.</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>締め切りまでに、添付の数字に修正が必要かお知らせください。</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Please let me know if the attached figures require any adjustment on your end.</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>そちらで添付の数字に修正が必要でしたらお知らせください。</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>EX-0718</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>This is a gentle nudge on my email from last week.</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>先週送ったメールについて、催促を柔らかく伝える表現。</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>This is a gentle nudge on my email from last week — just checking if you had a chance to review it.</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>先週のメールについての軽いリマインドです。ご確認いただけたか気になりまして。</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>just a friendly reminder about my earlier email</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>"gentle nudge"は角の立たない催促を表す口語的なビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>EX-0719</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>I'll loop in procurement for visibility on this thread.</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>このメールスレッドに購買部門を情報共有のため追加するという表現。</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>I'll loop in procurement for visibility on this thread going forward.</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>今後はこのスレッドに購買部門も入れて情報共有します。</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>I'll loop in procurement for visibility, since this affects the vendor contract.</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>ベンダー契約に関わる件なので、購買部門もこのスレッドに入れておきます。</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>I'll add procurement to this thread</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>EX-0720</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Let me check with my supervisor and call you back shortly.</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>上司に確認してから折り返し電話するという表現。</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Let me check with my supervisor and call you back shortly.</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>上司に確認してから、すぐに折り返しお電話します。</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Let me check with my supervisor and call you back within the hour.</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>上司に確認して、1時間以内に折り返しお電話します。</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>EX-0721</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I transfer this call?</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>電話を転送する間、少し待ってもらうよう頼む表現。</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I transfer this call to the right department?</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>適切な部署にお電話を転送しますので、少々お待ちいただけますか。</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>please hold while I transfer your call</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>EX-0722</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>I'm sorry, the line dropped for a second — could you repeat that?</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>通話が一瞬途切れたので、もう一度言ってもらうよう頼む表現。</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>I'm sorry, the line dropped for a second — could you repeat what you just said?</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>すみません、一瞬回線が切れました。今おっしゃったことをもう一度お願いできますか。</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>sorry, we got cut off — could you say that again?</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>EX-0723</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Let me pull up the account before we proceed further.</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>話を進める前にアカウント情報を表示するという表現。</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Let me pull up the account before we proceed further with the request.</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>ご依頼を進める前に、アカウント情報を確認させてください。</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Let me pull up the account — could you confirm your name and ID?</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>アカウントを確認しますので、お名前とIDを教えていただけますか。</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>EX-0724</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>依頼,提案</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>I'll have someone from support return your call within the hour.</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>サポート担当者から1時間以内に折り返し電話させるという表現。</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>I'll have someone from support return your call within the hour.</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>サポート担当者から1時間以内に折り返しお電話させます。</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>someone will call you back shortly</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>EX-0725</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Let's zoom in on the year-over-year growth here.</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>前年比の成長率に注目して詳しく見ようという表現。</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Let's zoom in on the year-over-year growth here — it's the key story.</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>ここで前年比の成長率に注目してみましょう。これが重要なポイントです。</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Let's zoom in on the year-over-year growth for our top three markets.</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>上位3つの市場における前年比成長率に注目してみましょう。</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S726" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>EX-0726</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>I'll leave the deep dive for the appendix slides.</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>詳細な分析は付録スライドに譲るという表現。</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>I'll leave the deep dive for the appendix slides in case anyone wants the details.</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>詳細が気になる方のために、深い分析は付録スライドに載せておきます。</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>I'll save the details for the appendix</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S727" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>EX-0727</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>This next section covers our go-to-market strategy.</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>次のセクションで市場投入戦略について説明するという表現。</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>This next section covers our go-to-market strategy for the new product.</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>次のセクションでは、新製品の市場投入戦略についてご説明します。</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>This next section covers our go-to-market strategy in more detail.</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>次のセクションでは市場投入戦略について詳しくご説明します。</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>EX-0728</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>To close things out, here are the three key takeaways.</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>締めくくりとして、重要なポイントを3つ挙げるという表現。</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>To close things out, here are the three key takeaways from today's presentation.</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>締めくくりに、本日のプレゼンの重要なポイントを3つご紹介します。</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>to wrap things up, here are the main points</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S729" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>EX-0729</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>I'll hand the floor over to my co-presenter for the Q&amp;A.</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>質疑応答のために共同発表者に進行を渡すという表現。</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>I'll hand the floor over to my co-presenter for the Q&amp;A session.</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>質疑応答の時間は、共同発表者に進行をお渡しします。</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>I'll pass it over to my colleague for questions</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>EX-0730</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Would you mind fast-tracking this request given the deadline?</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>締め切りを考慮して、この依頼を優先的に処理してもらえないか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Would you mind fast-tracking this request given the deadline next week?</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>来週締め切りなので、この依頼を優先的に進めていただけないでしょうか。</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Would you mind fast-tracking this request? It's more urgent than usual.</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>いつもより急ぎなので、この依頼を優先していただけますか。</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>could you expedite this request</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S731" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>EX-0731</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>I'm afraid this falls outside our current scope of work.</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>依頼内容が現在の業務範囲外であると丁寧に断る表現。</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>I'm afraid this falls outside our current scope of work, but we can discuss a separate arrangement.</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>恐れ入りますが、これは現在の業務範囲外です。別途対応をご相談できます。</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>that's beyond what we agreed to cover</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S732" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>EX-0732</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>依頼・断り,メール</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Could I ask you to CC me on future updates?</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>今後の更新情報を自分にもCCで共有してほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Could I ask you to CC me on future updates regarding this project?</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>今後このプロジェクトについて更新があれば、私もCCに入れていただけますか。</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S733" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>EX-0733</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>依頼・断り,会議</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Unfortunately, we'll have to table this until next fiscal year.</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>残念ながら来年度まで先送りにせざるを得ないという表現。</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Unfortunately, we'll have to table this until next fiscal year due to budget constraints.</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>残念ながら予算の都合で、来年度まで先送りにせざるを得ません。</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Unfortunately, we'll have to table this until next fiscal year, but let's revisit it in Q1.</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>残念ながら来年度まで先送りですが、第1四半期に改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>we'll need to push this to next year</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>EX-0734</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>依頼・断り,会議</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>I hate to push back, but the timeline feels unrealistic.</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>反対意見を言いにくいが、スケジュールが非現実的だと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>I hate to push back, but the timeline feels unrealistic given our current resources.</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>反対したくはないのですが、現在のリソースを考えるとこのスケジュールは現実的ではないと思います。</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>I have some concerns about the timeline</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S735" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>EX-0735</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>反論・懸念,確認</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>We'd need to see firmer numbers before signing off.</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>承認する前に、もっと確実な数字を見せてほしいという表現。</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>We'd need to see firmer numbers before signing off on this contract.</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>この契約を承認する前に、もっと確実な数字を見せていただく必要があります。</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>we need more concrete figures before we approve this</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S736" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>EX-0736</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Is there room to renegotiate the payment terms?</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>支払い条件を再交渉する余地があるか尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Is there room to renegotiate the payment terms given the current market conditions?</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>現在の市場状況を踏まえて、支払い条件を再交渉する余地はありますか。</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Is there room to renegotiate the payment terms, or is this final?</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>支払い条件を再交渉する余地はありますか、それともこれが最終条件ですか。</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>can we revisit the payment terms</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S737" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>EX-0737</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>We're willing to fast-track delivery in exchange for a longer contract.</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>契約期間を延長する代わりに納期を早めてもよいという交渉表現。</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>We're willing to fast-track delivery in exchange for a longer contract term.</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>契約期間を延長していただければ、納期を早めることも可能です。</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>we can expedite delivery if you extend the contract</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S738" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>EX-0738</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Let's find common ground on the service-level agreement.</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>サービスレベル合意(SLA)について双方が納得できる点を探そうという表現。</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Let's find common ground on the service-level agreement before we finalize the deal.</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>契約を確定する前に、サービスレベル合意について双方が納得できる点を探しましょう。</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>let's find a middle ground on the SLA</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>"SLA (service-level agreement)"はIT・アウトソーシング契約で頻出する用語。</t>
+        </is>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S739" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>EX-0739</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>That's close to what we had in mind, but not quite there.</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>提示された条件が想定に近いが、まだ十分ではないと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>That's close to what we had in mind, but not quite there — could you come down a bit more?</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>想定に近いですが、まだ十分ではありません。もう少し下げていただけますか。</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>we're getting closer, but not quite</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>EX-0740</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Let's regroup once the budget is finalized.</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>予算が確定してから改めて集まって話そうという表現。</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Let's regroup once the budget is finalized and revisit the plan.</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>予算が確定したら改めて集まって、計画を見直しましょう。</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Let's regroup once the budget is finalized next week.</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>来週予算が確定したら、改めて話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>let's reconvene once we have the budget</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>EX-0741</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>メール,交渉</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>I'll ballpark the cost and follow up with exact figures.</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>おおよそのコストを見積もり、正確な数字は後で伝えるという表現。</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>I'll ballpark the cost and follow up with exact figures by tomorrow.</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>おおよそのコストをお伝えして、正確な数字は明日改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>I'll give you a rough estimate for now</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>"ballpark"は「大まかな見積もり」を表す口語的な動詞・名詞。</t>
+        </is>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>EX-0742</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Could we get this fast-tracked through legal review?</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>法務レビューを優先的に進めてもらえないか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Could we get this fast-tracked through legal review given the tight deadline?</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>締め切りが迫っているので、法務レビューを優先的に進めていただけますか。</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>could we expedite the legal review</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>EX-0743</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>We're seeing some scope creep on this project.</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>プロジェクトの範囲が当初の想定より広がってきていると指摘する表現。</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>We're seeing some scope creep on this project, so we may need to revisit the timeline.</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>このプロジェクトで範囲の拡大が見られるので、スケジュールを見直す必要があるかもしれません。</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>We're seeing some scope creep — can we lock down the requirements again?</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>範囲が広がってきているので、もう一度要件を確定させませんか。</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>"scope creep"はプロジェクト管理用語で、当初の合意範囲を超えて作業が拡大する現象を指す。</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>EX-0744</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Let's ring-fence the budget for this initiative.</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>この施策のために予算を他に流用されないよう確保しようという表現。</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Let's ring-fence the budget for this initiative so it doesn't get reallocated.</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>他に流用されないよう、この施策のための予算を確保しておきましょう。</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>let's set aside a dedicated budget for this</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>"ring-fence"は英式ビジネス英語で「予算・資金を保護し他の用途に使わせない」という意味。</t>
+        </is>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>EX-0745</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>I'll follow up with a recap email after the call.</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>通話後に内容をまとめたメールを送るという表現。</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>I'll follow up with a recap email after the call so everyone has the details.</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>通話後に、皆さんが詳細を確認できるようまとめのメールをお送りします。</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>I'll send a summary email after we hang up</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>EX-0746</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>雑談,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Could you walk me through the onboarding checklist?</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>新人研修のチェックリストについて説明してほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Could you walk me through the onboarding checklist for new hires?</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>新入社員向けのオンボーディングチェックリストについて説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Could you walk me through the onboarding checklist? I want to make sure I'm not missing anything.</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>見落としがないか確認したいので、オンボーディングチェックリストについて説明してもらえますか。</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>EX-0747</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>会議,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>提案,確認</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Let's make sure this doesn't fall through the cracks.</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>この件が見落とされて放置されないよう気をつけようという表現。</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Let's make sure this doesn't fall through the cracks — can someone own it?</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>これが見落とされないように、誰か担当を決めましょう。</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Let's make sure this doesn't fall through the cracks during the transition.</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>引き継ぎの間にこの件が見落とされないよう気をつけましょう。</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>let's not let this get lost in the shuffle</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>EX-0748</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>I'll escalate this to the department head if needed.</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>必要であればこの件を部門長にエスカレーションするという表現。</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>I'll escalate this to the department head if needed to get a faster resolution.</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>早く解決するために、必要であればこの件を部門長にエスカレーションします。</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>I'll raise this with management if necessary</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>EX-0749</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>依頼,提案</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Could we push the kickoff to early next week?</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>プロジェクトの開始会議を来週早々に延期できないか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Could we push the kickoff to early next week? A few stakeholders can't make it tomorrow.</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>キックオフを来週早々に延期できますか。明日は関係者が数名参加できないので。</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Could we push the kickoff to early next week to give everyone more time to prepare?</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>皆がもっと準備時間を取れるよう、キックオフを来週早々に延期できますか。</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>could we delay the kickoff meeting</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>EX-0750</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Could we meet somewhere between these two figures?</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>2つの金額の間で妥協点を見つけられないか尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Could we meet somewhere between these two figures instead of picking one extreme?</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>極端などちらかではなく、2つの金額の間で妥協できませんか。</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Could we meet somewhere between these two figures to keep both sides happy?</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>双方が納得できるよう、2つの金額の中間あたりで折り合えませんか。</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>let's split the difference</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S751" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S751"/>
+  <dimension ref="A1:S801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -57202,6 +57202,3781 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>EX-0751</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Let's park that thought and come back to the main agenda.</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>それた話題や意見を一旦保留にして、本来の議題に戻ろうという提案。</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Let's park that thought and come back to the main agenda.</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>その考えはいったん保留にして、本来の議題に戻りましょう。</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>We can park that thought and revisit it once we've covered the main items.</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>その件はいったん保留にして、主要な議題を終えてから戻りましょう。</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Let's table that for now</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>EX-0752</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Can we get a quick pulse check on where everyone stands?</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>会議の参加者が現時点でどう考えているかを、手短に確認したいときの表現。</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Can we get a quick pulse check on where everyone stands?</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>皆さんの現状の意見を手短に確認できますか？</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Before we move on, let's get a quick pulse check on where everyone stands.</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>先に進む前に、皆さんの現状の考えを手短に確認しましょう。</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>「pulse check」はビジネスで「簡易な状況確認」を意味するカジュアルな比喩表現。</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>EX-0753</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>I'd like to flag this for further discussion offline.</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>この話題は会議の場ではなく、別の機会に改めて詳しく話し合いたいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>I'd like to flag this for further discussion offline.</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>この件については、別の場で改めて詳しく話し合いたいと思います。</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>I'd like to flag this for further discussion offline with the relevant stakeholders.</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>この件については、関係者と別の場で改めて詳しく話し合いたいと思います。</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Let's take this offline</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>EX-0754</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Let's not lose our train of thought — where did we leave off?</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>話の脈絡を見失わないように、中断する前にどこまで話していたかを確認する表現。</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Let's not lose our train of thought — where did we leave off?</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>話の流れを見失わないように、どこまで話していたか確認しましょう。</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Sorry for the interruption — let's not lose our train of thought, where did we leave off?</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>中断してすみません、話の流れを見失わないように、どこまで話していたか確認しましょう。</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>EX-0755</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Could we nail down a firm decision before we adjourn?</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>会議を終える前に、曖昧なままにせず確実に結論を出しておきたいという表現。</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Could we nail down a firm decision before we adjourn?</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>終了する前に、確実な結論を出しておけますか？</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>「nail down」は「（決定事項などを）はっきり確定させる」という口語表現。</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>EX-0756</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>I think we're aligned on the broad strokes.</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>細かい点はさておき、大まかな方向性については合意できているという表現。</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>I think we're aligned on the broad strokes.</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>大枠については意見が一致していると思います。</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>I think we're aligned on the broad strokes, even if the details still need work.</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>細部はまだ詰める必要がありますが、大枠については一致していると思います。</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>EX-0757</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Let's keep this focused and table any tangents.</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>会議の焦点を保ち、脱線した話題は後回しにしようという提案。</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Let's keep this focused and table any tangents.</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>この場では焦点を絞って、脱線した話題は後回しにしましょう。</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S758" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>EX-0758</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>Can we get everyone's thumbs up or down on this?</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>賛成か反対か、簡単な形で全員の意見を確認する表現。</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Can we get everyone's thumbs up or down on this?</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>これについて、皆さんの賛成・反対を確認できますか？</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Let's go around and get everyone's thumbs up or down on this before we decide.</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>決める前に、一人ずつ賛成か反対か確認していきましょう。</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R759" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S759" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>EX-0759</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Things going smoothly for you lately?</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>相手の最近の調子を尋ねる、気軽な雑談のきっかけとなる表現。</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Things going smoothly for you lately?</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>最近、うまくいっていますか？</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>How's it going?</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S760" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>EX-0760</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>You've been keeping busy, I take it?</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>相手が忙しくしているようだと察して、それとなく声をかける表現。</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>You've been keeping busy, I take it?</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>お忙しくされているようですね。</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>You've been keeping busy, I take it? Your calendar looked packed all week.</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>お忙しくされているようですね。今週はスケジュールがぎっしりのようでした。</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S761" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>EX-0761</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>It's been a minute since we last caught up.</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>しばらく会っていなかった相手に対して使う、久しぶりの挨拶表現。</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>It's been a minute since we last caught up.</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>しばらくゆっくり話していませんでしたね。</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Long time no see!</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R762" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S762" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>EX-0762</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>I'm still recovering from that last deadline.</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>直前の忙しい締め切りの疲れがまだ抜けていないと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>I'm still recovering from that last deadline.</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>この前の締め切りの疲れがまだ抜けていません。</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>I'm still recovering from that last deadline — it really wiped me out.</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>この前の締め切りの疲れがまだ抜けていません。本当にへとへとになりました。</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S763" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>EX-0763</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>What's been keeping you occupied these days?</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>最近何をして過ごしているか尋ねる、カジュアルな質問。</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>What's been keeping you occupied these days?</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>最近は何に忙しくされていますか？</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>What have you been up to?</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S764" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>EX-0764</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>I heard you've settled into the new office nicely.</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>相手が新しい環境にうまく馴染んでいると聞いて、それを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>I heard you've settled into the new office nicely.</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>新しいオフィスにうまく馴染まれたと聞きました。</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>I heard you've settled into the new office nicely — that's great to hear.</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>新しいオフィスにうまく馴染まれたと聞きました。それは何よりです。</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R765" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S765" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>EX-0765</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>Any big plans once things quiet down?</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>忙しい時期が落ち着いた後の予定を尋ねる、軽い質問。</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Any big plans once things quiet down?</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>落ち着いたら何か予定はありますか？</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S766" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>EX-0766</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>I wanted to circle back on this before it slips through the cracks.</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>対応が忘れられてしまわないよう、改めて確認の連絡をするという表現。</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>I wanted to circle back on this before it slips through the cracks.</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>対応漏れにならないよう、改めてこの件についてご連絡しました。</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>I wanted to circle back on this before it slips through the cracks, given the upcoming deadline.</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>締め切りも近いので、対応漏れにならないよう改めてご連絡しました。</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>Just circling back on this</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>「slip through the cracks」は「見落とされる、対応漏れになる」という比喩表現。</t>
+        </is>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S767" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>EX-0767</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Please let me know if this aligns with your expectations.</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>内容が相手の期待していたものと合っているか、確認を求める表現。</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Please let me know if this aligns with your expectations.</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>こちらの内容がご期待に沿うものかご確認いただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Please let me know if this aligns with your expectations, or if any revisions are needed.</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>こちらの内容がご期待に沿うものか、修正が必要かご確認いただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R768" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S768" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>EX-0768</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>I've flagged the relevant sections in yellow for your convenience.</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>該当箇所を分かりやすく色付けして知らせておいたと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>I've flagged the relevant sections in yellow for your convenience.</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>分かりやすいように、該当箇所を黄色でマークしておきました。</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S769" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>EX-0769</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Kindly advise at your earliest opportunity.</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>できるだけ早く返答してほしいと、丁寧に依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Kindly advise at your earliest opportunity.</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>できるだけ早くご連絡いただけますと幸いです。</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Please advise at your earliest convenience</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S770" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>EX-0770</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>I'll follow up separately with the finer details.</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>詳細な情報については、後ほど別途連絡すると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>I'll follow up separately with the finer details.</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>細かい詳細については、別途改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>I'll follow up separately with the finer details once the numbers are confirmed.</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>数字が確定次第、細かい詳細については別途ご連絡します。</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S771" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>EX-0771</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Apologies for the cross-post — wanted to make sure this reached the right team.</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>複数の関係者に同じ内容を送ったことを詫びつつ、確実に届けたかったと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Apologies for the cross-post — wanted to make sure this reached the right team.</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>複数の方に同じ内容をお送りして申し訳ありません。確実に担当の方に届けたく思いました。</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S772" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>EX-0772</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Thanks in advance for your help with this.</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>これから頼むことについて、前もってお礼を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Thanks in advance for your help with this.</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>これから対応いただくことになりますが、あらかじめお礼申し上げます。</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Thank you in advance</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R773" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S773" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>EX-0773</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>You're cutting out a bit — could you say that again?</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>電話の音声が途切れていて、もう一度言ってほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>You're cutting out a bit — could you say that again?</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>少し声が途切れています。もう一度言っていただけますか？</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S774" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>EX-0774</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>I'll patch you through right away.</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>電話をすぐに担当者へつなぐと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>I'll patch you through right away.</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>すぐに担当者へおつなぎします。</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S775" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>EX-0775</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I pull up the details?</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>詳細を確認する間、少し待ってほしいと丁寧に頼む表現。</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Could you bear with me while I pull up the details?</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>詳細を確認する間、少しお待ちいただけますか？</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Could you hold the line for a moment?</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S776" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>EX-0776</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Let me just double-check that on my end.</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>自分の方でもう一度確認すると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Let me just double-check that on my end.</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>こちらでもう一度確認させてください。</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S777" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>EX-0777</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>I'll ring you back the moment I know more.</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>詳しいことが分かり次第、折り返し電話すると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>I'll ring you back the moment I know more.</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>詳しいことが分かり次第、折り返しお電話します。</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R778" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S778" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>EX-0778</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Sorry for the delay — I was tied up on another call.</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>他の電話対応で手が離せず、返信や対応が遅れてしまったことを詫びる表現。</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Sorry for the delay — I was tied up on another call.</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>お返事が遅くなり申し訳ありません。別の電話対応で手が離せませんでした。</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R779" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S779" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>EX-0779</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Could we schedule a proper call to go over this in detail?</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>この件についてはメールではなく、きちんと電話で話す時間を設けたいという提案。</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Could we schedule a proper call to go over this in detail?</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>この件について詳しく話すため、改めてお電話の時間をいただけますか？</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R780" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S780" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>EX-0780</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>I'll keep the technical detail to a minimum here.</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>技術的な詳細は最小限にとどめて説明すると前置きする表現。</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>I'll keep the technical detail to a minimum here.</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>ここでは技術的な詳細は最小限にとどめておきます。</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>I'll spare you the technical details</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R781" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S781" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>EX-0781</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>This next slide ties everything together.</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>次のスライドで、これまでの内容が一つにまとまるという表現。</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>This next slide ties everything together.</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>次のスライドで、これまでの内容がひとつにまとまります。</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R782" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S782" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>EX-0782</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>Let me pause here in case anything needs clarifying.</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>聞き手が理解できているか確認するため、一旦話を止める表現。</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Let me pause here in case anything needs clarifying.</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>ここで一旦止めますので、不明な点があれば教えてください。</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R783" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S783" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>EX-0783</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>I'll leave the finer points for the handout.</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>細かい点については、配布資料に譲るという表現。</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>I'll leave the finer points for the handout.</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>細かい点については、配布資料をご覧いただければと思います。</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S784" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>EX-0784</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>That's the headline number I want you to remember.</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>最も覚えておいてほしい重要な数字を強調する表現。</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>That's the headline number I want you to remember.</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>これが、皆さんに覚えておいていただきたい最も重要な数字です。</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>That's the headline number I want you to remember — everything else supports this point.</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>これが、皆さんに覚えておいていただきたい最も重要な数字です。他の内容はこの点を補足するものです。</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S785" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>EX-0785</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>Let's jump to the part that matters most to you.</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>聞き手にとって最も関心のある部分へ、話を進めようという表現。</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Let's jump to the part that matters most to you.</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>皆さんに一番関係のある部分に進みましょう。</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>EX-0786</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>I'll open it up for discussion after this section.</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>このパートの後に、質疑応答や議論の時間を設けると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>I'll open it up for discussion after this section.</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>このパートの後に、質疑応答の時間を設けます。</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>Let's open the floor for questions</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S787" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>EX-0787</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>Would it be out of line to request a short extension?</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>少し図々しいかもしれないと前置きしつつ、短い延長を依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Would it be out of line to request a short extension?</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>少し図々しいかもしれませんが、短い延長をお願いできますでしょうか？</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S788" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>EX-0788</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>I hate to be a stickler, but could we stick to the original plan?</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>細かいことを言うようで恐縮だが、当初の予定通りに進めてほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>I hate to be a stickler, but could we stick to the original plan?</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>細かいことを言うようで恐縮ですが、当初の予定通りに進めていただけますか？</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>「stickler」は「細かいことにうるさい人」という意味。</t>
+        </is>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S789" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>EX-0789</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>I think I'll have to bow out of this one.</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>今回は参加や関与を見送るという意思を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>I think I'll have to bow out of this one.</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>今回は見送らせていただこうと思います。</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>I'll have to pass this time</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S790" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>EX-0790</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>Much as I'd like to help, my calendar's booked solid through Friday.</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>手伝いたい気持ちはあるが、金曜日までスケジュールが埋まっていて難しいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Much as I'd like to help, my calendar's booked solid through Friday.</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>お手伝いしたい気持ちはあるのですが、金曜日まで予定が詰まっています。</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S791" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>EX-0791</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Could I lean on you for a second opinion?</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>相手に意見や助言を求める、カジュアルな依頼表現。</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Could I lean on you for a second opinion?</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>もう一つ意見をいただけますか？</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Could I lean on you for a second opinion before I send this out?</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>これを送る前に、もう一つ意見をいただけますか？</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S792" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>EX-0792</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>I'll have to check with the higher-ups before agreeing.</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>即答を避け、上の立場の人に確認してから返事すると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>I'll have to check with the higher-ups before agreeing.</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>合意する前に、上の者に確認する必要があります。</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S793" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>EX-0793</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Would you be willing to make an exception just this once?</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>通常の対応とは異なる特別な配慮を、今回だけお願いする表現。</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Would you be willing to make an exception just this once?</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>今回だけ、特別に対応いただくことは可能でしょうか？</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>make an exception</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S794" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>EX-0794</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>We'd need to see a bit more give on the pricing side.</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>価格面でもう少し譲歩してほしいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>We'd need to see a bit more give on the pricing side.</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>価格面でもう少し譲歩していただく必要があります。</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S795" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>EX-0795</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Let's not let a minor difference get in the way of a solid partnership.</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>小さな条件の違いのために、良好な協力関係を損ないたくないという表現。</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Let's not let a minor difference get in the way of a solid partnership.</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>些細な違いのために、良好な協力関係を損ないたくありません。</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S796" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>EX-0796</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>Is there any wiggle room on the delivery date?</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>納期について融通が利く余地があるかどうかを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Is there any wiggle room on the delivery date?</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>納期について、多少の融通は利きますか？</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>Is there any room for negotiation?</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S797" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>EX-0797</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>We can sweeten the terms if you commit to a longer contract.</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>契約期間を延ばしてもらえるなら、条件を良くできると提案する表現。</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>We can sweeten the terms if you commit to a longer contract.</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>より長期の契約をお約束いただければ、条件を良くすることができます。</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S798" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>EX-0798</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>That number is higher than we budgeted, but we're open to discussing it.</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>提示された金額は予算より高いが、話し合う余地はあると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>That number is higher than we budgeted, but we're open to discussing it.</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>その金額は予算より高いですが、話し合う余地はあります。</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>EX-0799</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>Let's shake on the headline terms and iron out the rest later.</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>主要な条件についてひとまず合意し、細部は後で詰めようという表現。</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Let's shake on the headline terms and iron out the rest later.</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>主要な条件について合意し、細部は後で詰めましょう。</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>「shake on」は「握手して合意する」という意味の口語表現。</t>
+        </is>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S800" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>EX-0800</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Let's settle on a flat rate rather than nickel-and-diming every line item.</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>細かい項目ごとに値切り合うのではなく、一律の料金にまとめようという提案。</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Let's settle on a flat rate rather than nickel-and-diming every line item.</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>項目ごとに細かく値切るのではなく、一律の料金にまとめましょう。</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S801"/>
+  <dimension ref="A1:S851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -60977,6 +60977,3956 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>EX-0801</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Let's table this discussion for now.</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>その議題は一旦保留にしよう、という意味。会議で扱いを先送りするときの定番表現。</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Let's table this discussion for now and come back to it once we have more data.</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>この議題は一旦保留にして、データが揃ってから改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>I know it's important, but let's table this for today's meeting.</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>重要な件だとは思いますが、今日の会議ではこの議題は保留にしましょう。</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Let's put this on hold.,Let's shelve this for now.</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S802" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>EX-0802</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>I'd like to get everyone's buy-in before we proceed.</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>先に進める前に全員の同意・納得を得たい、という意味。合意形成を重視する場面で使う。</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>I'd like to get everyone's buy-in before we proceed with the new policy.</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>新しい方針を進める前に、皆さんの同意を得ておきたいと思います。</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Without buy-in from the whole team, this initiative won't succeed.</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>チーム全体の同意がなければ、この取り組みは成功しないでしょう。</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>get everyone on board</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>「buy-in」は単なる賛成ではなく、当事者意識を持った合意というニュアンスがある。</t>
+        </is>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>EX-0803</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Could you walk us through the numbers again?</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>数字についてもう一度説明してもらえますか、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Could you walk us through the numbers again? I want to make sure I understood correctly.</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>数字についてもう一度説明してもらえますか。正しく理解できているか確認したいので。</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Could you walk us through the numbers again before we finalize the budget?</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>予算を確定する前に、もう一度数字について説明してもらえますか。</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S804" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>EX-0804</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>I don't want to derail the discussion, but...</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>話を脱線させたくない、と前置きしてから懸念点や別の論点を述べるときの表現。</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>I don't want to derail the discussion, but I think we should reconsider the budget first.</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>話を脱線させたくないのですが、まず予算を再検討すべきだと思います。</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>I don't want to derail things, but has anyone looked into the legal implications?</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>話を逸らしたくはないのですが、誰か法的な影響について調べましたか。</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>Not to get off track, but...,Sorry to sidetrack, but...</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>反対意見や新しい論点を切り出す前のクッション表現として使う。</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S805" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>EX-0805</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>I want to flag a potential risk here.</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>ここで潜在的なリスクを指摘しておきたい、という意味。懸念を丁寧に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>I want to flag a potential risk here regarding the vendor's delivery schedule.</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>ベンダーの納品スケジュールについて、ここで潜在的なリスクを指摘しておきたいと思います。</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Before we sign off, I want to flag a potential risk with the current approach.</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>承認する前に、現在のアプローチに潜在的なリスクがあることを指摘しておきたいです。</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S806" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>EX-0806</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>ミドル,カジュアル</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Let's shelve that for now.</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>その件は今は棚上げにしよう、という意味。議題を一時保留するときの表現。</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>We're low on time, so let's shelve that for now and revisit next week.</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>時間が足りないので、その件は今は棚上げにして来週改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>I think we should shelve this idea until we have more data.</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>もっとデータが揃うまで、このアイデアは棚上げにすべきだと思います。</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S807" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>EX-0807</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>We're on the same page, I believe.</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>私たちの認識は一致していると思う、という確認・同意の表現。</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>We're on the same page, I believe, but let's confirm the next steps just in case.</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>認識は一致していると思いますが、念のため次のステップを確認しましょう。</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>We're aligned.</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S808" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>EX-0808</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>I've been swamped with work lately.</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>最近仕事で忙殺されている、と近況を伝えるときの表現。</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>I've been swamped with work lately, barely had time to breathe.</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>最近仕事で忙殺されていて、息つく暇もありません。</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Sorry for the late reply, I've been swamped with work lately.</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>返信が遅くなってすみません、最近仕事で忙殺されていて。</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>I've been slammed.,It's been non-stop lately.</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>EX-0809</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Things have been pretty hectic lately.</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>最近何かと慌ただしい、という近況を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Things have been pretty hectic lately with the product launch coming up.</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>製品発売が近づいていて、最近何かと慌ただしいです。</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>I know things have been pretty hectic lately, so thanks for taking the time.</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>最近何かと慌ただしいのはわかっていますので、時間を取ってくれてありがとうございます。</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>EX-0810</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>I could really use a coffee break.</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>ちょっと一息つきたい、コーヒーブレイクが欲しい、という気軽な表現。</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>I could really use a coffee break after that long meeting.</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>あの長い会議の後は、ちょっとコーヒーブレイクが欲しいですね。</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>EX-0811</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>It's been a while since we last caught up.</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>しばらく近況を話していなかったね、という久しぶりの再会を意識した表現。</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>It's been a while since we last caught up—how have you been?</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>しばらく近況を話していなかったですね。最近どうですか。</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>It's been a while since we last caught up, so let's grab lunch sometime.</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>しばらく話していなかったので、今度ランチでもどうですか。</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S812" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>EX-0812</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Work's been keeping me on my toes.</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>仕事のおかげで気を抜けない状態が続いている、という意味の慣用表現。</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Work's been keeping me on my toes lately, but I'm enjoying the challenge.</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>最近仕事で気を抜けない状態が続いていますが、その分やりがいがあります。</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>keep someone on their toes</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>「on one's toes」は緊張感を持って注意深く対応している状態を表す慣用表現。</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S813" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>EX-0813</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Any exciting plans for the holidays?</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>休暇に何か楽しい予定はありますか、という気軽な雑談の切り出し表現。</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Any exciting plans for the holidays this year?</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>今年の休暇は何か楽しい予定がありますか。</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>EX-0814</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Please find the attached file for your reference.</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>ご参考までに添付ファイルをお送りします、というメールの定型表現。</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Please find the attached file for your reference and let me know if you have any questions.</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>ご参考までに添付ファイルをお送りします。ご質問があればお知らせください。</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Please find the attached file for your reference regarding next week's agenda.</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>来週の議題についての添付ファイルをご参考までにお送りします。</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>Please see the attached file.</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S815" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>EX-0815</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>I'm writing to follow up on my previous email.</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>以前送ったメールについてフォローアップする、という書き出し表現。</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>I'm writing to follow up on my previous email regarding the contract details.</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>契約内容について、以前のメールのフォローアップとしてご連絡しています。</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>I'm writing to follow up on my previous email—have you had a chance to review it?</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>以前のメールのフォローアップですが、ご確認いただけましたでしょうか。</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S816" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>EX-0816</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Kindly let me know if this works for you.</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>これでよろしければお知らせください、という丁寧な確認依頼の表現。</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Kindly let me know if this works for you, and I'll send over the calendar invite.</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>これでよろしければお知らせください。カレンダーの招待をお送りします。</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Kindly let me know if this works for you by the end of the day.</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>本日中にこれでよろしいかお知らせいただけますと幸いです。</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>「Kindly」はやや堅い印象を与えるため、社外や目上の相手とのメールでよく使われる。</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S817" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>EX-0817</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Apologies for the delayed response.</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>返信が遅れたことをお詫びする、というメールの定型表現。</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Apologies for the delayed response—I've been out of the office this week.</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>返信が遅くなり申し訳ございません。今週は外出しておりました。</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Apologies for the delayed response. Please find my answers below.</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>返信が遅くなり申し訳ございません。以下に回答をご用意しました。</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>Sorry for the late reply.</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>EX-0818</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>I look forward to hearing from you soon.</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>近いうちにご連絡をお待ちしております、というメールの結びの表現。</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>I look forward to hearing from you soon regarding the proposal.</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>ご提案の件について、近いうちにご連絡をお待ちしております。</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>I look forward to your reply.</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>EX-0819</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Please do not hesitate to reach out with any questions.</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>ご質問があれば遠慮なくご連絡ください、という丁寧な結びの表現。</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Please do not hesitate to reach out with any questions regarding the invoice.</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>請求書についてご質問があれば、遠慮なくご連絡ください。</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Please do not hesitate to reach out with any questions before the deadline.</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>締め切り前にご質問があれば、遠慮なくご連絡ください。</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>Feel free to contact me anytime.</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>EX-0820</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>I wanted to touch base regarding the project timeline.</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>プロジェクトのスケジュールについて連絡を取りたかった、という書き出し表現。</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>I wanted to touch base regarding the project timeline before our next check-in.</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>次のチェックインの前に、プロジェクトのスケジュールについてご連絡したいと思いました。</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>I wanted to touch base regarding the project timeline—are we still on track?</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>プロジェクトのスケジュールについてご連絡したいのですが、予定通り進んでいますか。</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>EX-0821</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Could you speak up a little? The line's a bit unclear.</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>電話越しで聞き取りにくいときに、もう少し大きな声で話してもらう依頼表現。</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Could you speak up a little? The line's a bit unclear on my end.</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>もう少し大きな声で話していただけますか。こちら側で電波が悪いようです。</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>EX-0822</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Let me put you on hold for a moment.</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>少しお待たせします、という電話対応で保留にするときの表現。</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Let me put you on hold for a moment while I check your account.</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>アカウントを確認する間、少しお待たせします。</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Let me put you on hold for a moment and transfer you to the right person.</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>少しお待たせして、担当者にお繋ぎします。</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>EX-0823</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Let me patch you through to the sales team.</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>営業チームにお繋ぎします、という電話取次ぎの表現。</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Let me patch you through to the sales team, one moment please.</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>営業チームにお繋ぎします、少々お待ちください。</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>I'll patch you through to someone who can help with billing.</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>請求に関して対応できる者にお繋ぎします。</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>I'll put you through to...,I'll connect you with...</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>EX-0824</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Sorry, you're breaking up a bit.</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>電話の声が途切れている、と伝えるときの表現。</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Sorry, you're breaking up a bit. Could you say that again?</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>すみません、声が少し途切れています。もう一度言っていただけますか。</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Sorry, you're breaking up a bit—let me call you back on a better line.</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>すみません、声が少し途切れています。電波の良い回線からかけ直します。</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>EX-0825</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Sorry, could you say that once more?</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>すみません、もう一度言っていただけますか、と聞き返すときの表現。</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Sorry, could you say that once more? The connection's not great.</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>すみません、もう一度言っていただけますか。電波が悪くて。</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Could you say that once more? I want to make sure I got it right.</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>もう一度言っていただけますか。正しく理解できているか確認したいので。</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>EX-0826</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Let me just pull up your account details.</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>アカウント情報を今開きますね、という電話対応の表現。</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Let me just pull up your account details—this will take a moment.</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>アカウント情報を今開きますね。少々お時間をいただきます。</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>EX-0827</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Let's dive right into the numbers.</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>早速数字の話に入りましょう、というプレゼン冒頭の表現。</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Let's dive right into the numbers and see how we performed last quarter.</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>早速数字の話に入って、前四半期の実績を見てみましょう。</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>Let's get straight to the numbers.</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>EX-0828</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>As you can see from this slide...</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>このスライドをご覧いただくと分かる通り、というプレゼンでの説明表現。</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>As you can see from this slide, sales have grown steadily over the past year.</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>このスライドをご覧いただくと分かる通り、過去1年間で売上は着実に伸びています。</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>As you can see from this slide, our main competitor is gaining market share.</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>このスライドをご覧いただくと分かる通り、主要な競合他社がシェアを伸ばしています。</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>EX-0829</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>I'll keep this brief and to the point.</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>手短に要点だけお伝えします、というプレゼンの前置き表現。</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>I'll keep this brief and to the point since we're short on time today.</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>今日は時間が限られているので、手短に要点だけお伝えします。</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>EX-0830</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Feel free to hold your questions until the end.</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>質問は最後までお待ちください、というプレゼンの進行に関する依頼表現。</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Feel free to hold your questions until the end of the presentation.</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>ご質問はプレゼンの最後までお待ちいただければと思います。</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Feel free to hold your questions until the end, and I'll leave plenty of time for discussion.</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>ご質問は最後までお待ちください。議論の時間は十分に取ります。</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>EX-0831</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Let me break this down for you.</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>これを分かりやすく説明しますね、というプレゼンでの補足表現。</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Let me break this down for you step by step.</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>これを一つずつ分かりやすく説明しますね。</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>EX-0832</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>To wrap things up, here are the key takeaways.</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>まとめとして、要点をお伝えします、というプレゼンの締めくくり表現。</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>To wrap things up, here are the key takeaways from today's presentation.</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>まとめとして、今日のプレゼンの要点をお伝えします。</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>In summary...,To sum up...</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>EX-0833</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>I'll hand it over to my colleague for the next part.</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>ここからは同僚に引き継ぎます、というプレゼンでの進行表現。</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>I'll hand it over to my colleague for the next part of the presentation.</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>プレゼンの次の部分は同僚に引き継ぎます。</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>I'll pass it over to...</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S834" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>EX-0834</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Would it be possible to push the deadline back a few days?</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>締め切りを数日延ばしていただくことは可能でしょうか、という丁寧な依頼表現。</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Would it be possible to push the deadline back a few days due to the delayed shipment?</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>出荷の遅れのため、締め切りを数日延ばしていただくことは可能でしょうか。</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Would it be possible to push the deadline back a few days to accommodate the review?</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>レビューの時間を確保するため、締め切りを数日延ばしていただくことは可能でしょうか。</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>EX-0835</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not something we can accommodate right now.</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>申し訳ございませんが、現時点では対応いたしかねます、という丁寧な断りの表現。</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not something we can accommodate right now, given our current capacity.</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>現在のキャパシティを考えますと、申し訳ございませんがそれは対応いたしかねます。</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not something we can accommodate right now, but we can revisit it next quarter.</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>申し訳ございませんが現時点では対応いたしかねますが、来四半期に改めて検討できればと思います。</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S836" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>EX-0836</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>I hate to ask, but could you cover for me tomorrow?</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>言いにくいのですが、明日代わってもらえますか、という気軽な依頼表現。</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>I hate to ask, but could you cover for me tomorrow? Something came up.</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>言いにくいのですが、明日代わってもらえますか。急用ができてしまって。</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S837" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>EX-0837</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>I'll do my best, but I can't make any promises.</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>できる限りやってみるが、確約はできない、というやわらかい保留の表現。</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>I'll do my best, but I can't make any promises about the deadline.</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>できる限りやってみますが、締め切りについては確約できません。</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>I'll do my best, but I can't make any promises given how busy we are.</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>これだけ忙しいので、できる限りやってみますが確約はできません。</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>EX-0838</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>I'm going to have to pass on this one.</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>今回は遠慮しておきます、という気軽な断りの表現。</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Thanks for the invite, but I'm going to have to pass on this one.</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>お誘いありがとうございます、でも今回は遠慮しておきます。</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>I'm going to have to pass on this one—my plate's already full.</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>今回は遠慮しておきます。今すでに手一杯なので。</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>EX-0839</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Would you mind giving this a second look?</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>もう一度見ていただけますか、という丁寧な確認依頼の表現。</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Would you mind giving this a second look before I send it out?</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>送付する前に、もう一度見ていただけますか。</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Would you mind giving this a second look? I might have missed something.</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>もう一度見ていただけますか。何か見落としているかもしれないので。</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S840" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>EX-0840</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>反論・懸念,断り・保留</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>That's outside the scope of what we agreed on.</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>それは当初合意した範囲を超えている、という丁寧な反論・断りの表現。</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>I'm afraid that's outside the scope of what we agreed on in the original contract.</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>申し訳ございませんが、それは当初の契約で合意した範囲を超えています。</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>That's outside the scope of what we agreed on, so it would require an additional fee.</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>それは合意した範囲を超えていますので、追加料金が必要になります。</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>「scope」は契約や業務範囲の話でよく使われる語。範囲外であることを角を立てずに伝えられる。</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S841" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>EX-0841</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>Is there any room for negotiation on the price?</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>価格について交渉の余地はありますか、という確認表現。</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Is there any room for negotiation on the price given the volume we're ordering?</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>この発注量を考慮すると、価格について交渉の余地はありますか。</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S842" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>EX-0842</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>Let's find some middle ground here.</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>お互いに歩み寄れる点を見つけましょう、という交渉での提案表現。</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Let's find some middle ground here so both sides can walk away satisfied.</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>双方が納得できるよう、お互いに歩み寄れる点を見つけましょう。</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>I think we can find some middle ground on the pricing.</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>価格について、歩み寄れる点が見つかると思います。</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>meet in the middle</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S843" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>EX-0843</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>反論・懸念,提案</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>We'd need to see some flexibility on your end as well.</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>そちらにも柔軟に対応していただく必要がある、という交渉での表現。</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>We'd need to see some flexibility on your end as well if we're going to lower the price.</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>価格を下げるのであれば、そちらにも柔軟に対応していただく必要があります。</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>EX-0844</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>That's our final offer.</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>これが最終提示額です、という交渉での断定的な表現。</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>I'm sorry, but that's our final offer—we can't go any lower.</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>申し訳ございませんが、これが最終提示額です。これ以上は下げられません。</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>EX-0845</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>I think we can work something out.</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>何とか解決策を見つけられると思います、という前向きな交渉表現。</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>I think we can work something out that benefits both companies.</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>両社にとって利益になる解決策を見つけられると思います。</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>EX-0846</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Let's revisit the terms once more.</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>条件をもう一度見直しましょう、という交渉での提案表現。</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Let's revisit the terms once more before we finalize the contract.</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>契約を確定する前に、条件をもう一度見直しましょう。</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>EX-0847</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>We're willing to meet you halfway.</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>こちらも歩み寄る用意があります、という交渉での表現。</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>We're willing to meet you halfway on the delivery schedule.</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>納品スケジュールについては、こちらも歩み寄る用意があります。</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>If you can lower the minimum order quantity, we're willing to meet you halfway on price.</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>最低発注数量を下げていただければ、価格についてこちらも歩み寄る用意があります。</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>meet in the middle</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>EX-0848</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>I don't think that's going to fly with management.</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>それは上層部の承認を得られないと思う、という懸念を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>I don't think that's going to fly with management given the current budget constraints.</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>現在の予算制約を考えると、それは上層部の承認を得られないと思います。</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Honestly, I don't think that's going to fly with management as it stands.</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>正直なところ、今のままでは上層部の承認を得られないと思います。</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>「fly」はここでは「受け入れられる、通用する」という意味の口語表現。</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S849" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>EX-0849</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Let's not get bogged down in the details.</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>細部にこだわりすぎて話が進まなくならないようにしよう、という提案表現。</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Let's not get bogged down in the details and focus on the big picture first.</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>細部にこだわりすぎず、まず全体像に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>We're getting bogged down in the details—can we move on to the next point?</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>細かい話に入り込みすぎています。次の論点に移ってもいいですか。</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Let's not get sidetracked.,Let's keep this high-level for now.</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S850" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>EX-0850</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>メール,雑談</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>I really appreciate you taking the time to explain this.</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>説明のために時間を取ってくれて本当に感謝しています、という感謝の表現。</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>I really appreciate you taking the time to explain this so thoroughly.</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>これほど丁寧に説明のために時間を取ってくれて、本当に感謝しています。</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S851" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S851"/>
+  <dimension ref="A1:S901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -64927,6 +64927,3936 @@
         </is>
       </c>
     </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>EX-0851</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>Let's circle back to this after the break.</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>この件については休憩の後にもう一度話し合いましょう、という意味の表現。</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Let's circle back to this after the break and hear everyone's thoughts.</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>休憩の後にこの件に戻って、みんなの意見を聞きましょう。</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>We're running out of time, so let's circle back to this tomorrow.</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>時間がなくなってきたので、この件は明日改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Let's revisit this later</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>「circle back」は「後で改めて取り上げる」という意味のビジネス頻出フレーズ。</t>
+        </is>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>EX-0852</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>I'll loop you in on the email thread.</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>メールのやり取りにあなたも加える、共有するという意味。</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>I'll loop you in on the email thread so you can follow the discussion.</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>議論を追えるように、メールのやり取りにあなたも加えておきますね。</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Could you loop me in on that thread as well?</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>そのメールのやり取りに私も加えていただけますか。</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>cc you in,keep you in the loop</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>EX-0853</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>Could you walk me through your reasoning?</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>考えに至った経緯や理由を順を追って説明してほしい、と頼む表現。</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Could you walk me through your reasoning behind this proposal?</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>この提案に至った理由を順を追って説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Could you explain your thought process?</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>EX-0854</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Let's park that for now and move on.</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>その議題は一旦保留にして、次に進みましょうという表現。</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Let's park that for now and move on to the next agenda item.</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>それは一旦保留にして、次の議題に進みましょう。</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>I think we should park this issue until we get more data.</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>この問題はもっとデータが集まるまで保留にすべきだと思います。</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>table this for now,put this on hold</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>「park」は口語的に「一時的に保留する」という意味で使われる。</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>EX-0855</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>I hear you, but I have some reservations.</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>相手の意見を理解した上で、懸念点があることを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>I hear you, but I have some reservations about the timeline.</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>おっしゃることは分かりますが、スケジュールについて少し懸念があります。</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>I understand, but I'm a bit concerned</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>EX-0856</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>メール,雑談</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Let's touch base early next week.</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>来週の早いうちに簡単に近況確認や打ち合わせをしましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Let's touch base early next week to check on progress.</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>進捗確認のために来週の早いうちに一度連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Can we touch base before the client meeting?</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>クライアントとの打ち合わせの前に一度話しておけますか。</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>check in,sync up</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>EX-0857</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>メール,雑談</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>I'll drop you a line with the specifics.</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>詳細を簡単なメールで送りますね、というカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>I'll drop you a line with the specifics once I confirm the dates.</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>日程を確認したら、詳細を簡単にメールしますね。</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>I'll send you a quick note</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>「drop someone a line」は「軽くメールや連絡をする」というカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>EX-0858</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>電話,雑談</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Sorry to keep you waiting.</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>待たせてしまったことを謝る、基本的なフレーズ。</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Sorry to keep you waiting, I was on another call.</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>お待たせしてすみません、別の電話に出ていました。</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>Sorry for the wait</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>EX-0859</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Bear with me for a second.</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>少し待ってほしい、我慢して待っていてほしいという表現。</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Bear with me for a second while I pull up the file.</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>ファイルを開くので少しだけお待ちください。</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>Give me a moment,Hold on a second</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>EX-0860</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>I'll check my calendar and confirm shortly.</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>スケジュールを確認してすぐに返事します、という表現。</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>I'll check my calendar and confirm shortly.</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>スケジュールを確認して、すぐにご返事します。</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Let me check and get back to you</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>EX-0861</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>We're on the same page.</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>お互いの認識が一致している、という意味の表現。</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Great, it sounds like we're on the same page.</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>よかった、私たちの認識は一致しているようですね。</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>We're aligned</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>EX-0862</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>I'll leave the final call up to you.</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>最終判断はあなたに任せます、という表現。</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>I'll leave the final call up to you since you know the client best.</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>クライアントのことを一番よく知っているのはあなたなので、最終判断はお任せします。</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>I'll leave it up to you</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>EX-0863</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>Let's zoom out and look at the whole picture.</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>細部ではなく全体像に目を向けましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Let's zoom out and look at the whole picture before deciding.</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>決める前に、視点を広げて全体像を見てみましょう。</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Let's take a step back</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>EX-0864</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>I want to flag a potential issue.</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>潜在的な問題点を指摘したい、注意を促したいという表現。</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>I want to flag a potential issue with the current schedule.</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>現在のスケジュールについて、懸念点を一つ指摘させてください。</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>I'd like to raise a concern</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>「flag」は「注意喚起する」の意味で会議やメールでよく使われる。</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>EX-0865</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>依頼・断り,交渉</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Could we push the deadline back a bit?</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>締め切りを少し延ばしてもらえないか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Could we push the deadline back a bit? We need more time for testing.</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>締め切りを少し延ばしていただけますか。テストにもう少し時間が必要です。</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Could we extend the deadline?</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>EX-0866</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>I'm afraid that won't be feasible.</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>それは実現が難しいということを丁寧に伝える断りの表現。</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>I'm afraid that won't be feasible given our current budget.</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>現在の予算を考えると、それは難しいかと思います。</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>That won't work on our end</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>EX-0867</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Let's table this discussion for our next meeting.</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>この議論は次回の会議に持ち越しましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Let's table this discussion for our next meeting since we're running low on time.</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>時間が少なくなってきたので、この議論は次回の会議に持ち越しましょう。</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Let's postpone this discussion</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>米国英語では「table」は「保留する」、英国英語では逆に「議題に上げる」の意味になる点に注意。</t>
+        </is>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>EX-0868</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>I'll give that some more thought.</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>その件についてもう少し考えます、という表現。</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>I'll give that some more thought and let you know by Friday.</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>もう少し考えて、金曜日までにお知らせします。</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Let me think it over</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>EX-0869</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>That's a relief to hear.</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>それを聞いて安心した、という表現。</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>The shipment arrived on time? That's a relief to hear.</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>荷物は時間通りに届いたんですね。それを聞いて安心しました。</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>That's good to know</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>EX-0870</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Let's not beat around the bush.</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>遠回しな言い方をせず、単刀直入に話しましょうという表現。</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Let's not beat around the bush, what's your bottom line?</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>遠回しな言い方はやめて、率直に最低条件を教えてください。</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>Let's get straight to the point</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>EX-0871</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>I'd like to pick your brain about something.</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>ちょっと知恵を借りたい、意見を聞きたいという表現。</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Do you have a minute? I'd like to pick your brain about something.</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>少しお時間ありますか。ちょっとご意見を伺いたくて。</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>Can I get your input on something?</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>EX-0872</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>We're a bit stretched thin at the moment.</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>人手や余裕がなく手一杯である、という状況を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>We're a bit stretched thin at the moment, so it might take a few extra days.</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>今少し手一杯な状況なので、数日余分にかかるかもしれません。</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>We're short-staffed right now</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>EX-0873</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Let's iron out the details later.</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>細かい点は後で詰めましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Let's agree on the general direction first and iron out the details later.</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>まず大枠で合意して、細かい点は後で詰めましょう。</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Let's sort out the details later</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>EX-0874</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>I appreciate your patience on this matter.</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>お待たせしていることへの感謝を丁寧に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>I appreciate your patience on this matter while we resolve the issue.</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>問題解決までの間、この件についてご辛抱いただき感謝いたします。</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>Thank you for your patience</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>EX-0875</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Could you elaborate on that point?</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>その点についてもう少し詳しく説明してほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Could you elaborate on that point a bit more?</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>その点についてもう少し詳しく説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Could you go into more detail?</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>EX-0876</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Let's cut to the chase.</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>前置きを省いて本題に入りましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>We don't have much time, so let's cut to the chase.</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>あまり時間がないので、本題に入りましょう。</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>Let's get to the point</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>EX-0877</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>I don't want to put you on the spot.</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>相手を困らせたくない、答えにくい状況にしたくないという配慮を示す表現。</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>I don't want to put you on the spot, but do you have an opinion on this?</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>困らせるつもりはないのですが、この件についてご意見はありますか。</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>I don't mean to pressure you</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>相手に急な質問をする際に、配慮を示すために前置きとして使われる。</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>EX-0878</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>We need to think outside the box here.</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>既存の枠にとらわれず新しい発想で考える必要がある、という表現。</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>We need to think outside the box here if we want to solve this problem.</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>この問題を解決したいなら、既存の枠にとらわれない発想が必要です。</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>We need a fresh perspective</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>EX-0879</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Let's keep each other in the loop.</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>お互いに情報を共有し続けましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Let's keep each other in the loop as the project progresses.</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>プロジェクトが進む中で、お互い情報共有していきましょう。</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Let's keep each other posted</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>EX-0880</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>I'll follow up with you by end of day.</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>今日中にもう一度連絡します、という表現。</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>I'll follow up with you by end of day with an update.</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>今日中に進捗をご連絡します。</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>I'll get back to you today</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>EX-0881</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>That's a fair point.</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>相手の意見に一理あると認める表現。</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>That's a fair point, I hadn't considered that angle.</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>それは一理ありますね、その視点は考えていませんでした。</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>You have a point there</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>EX-0882</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>反論・懸念,断り・保留</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>Let's leave that point open for now.</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>その点については結論を出さず、今は保留にしておきましょうという表現。</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Let's leave that point open for now and revisit it next week.</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>その点は今は保留にして、来週改めて話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>Let's leave that undecided for now</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>EX-0883</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>I'd rather not commit to that just yet.</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>まだ確約はしたくない、という慎重な返答の表現。</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>I'd rather not commit to that just yet until I see the full proposal.</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>提案の全体像を見るまでは、まだ確約は控えたいです。</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>I'm not ready to commit to that</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>EX-0884</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>会議,電話</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>Can we sync up before the client call?</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>クライアントとの電話の前に打ち合わせをしませんか、と提案する表現。</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Can we sync up before the client call to align on talking points?</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>話す内容をすり合わせるため、クライアントとの電話の前に打ち合わせできますか。</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>Can we align beforehand?</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>EX-0885</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions.</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>早合点せず、慎重に判断しましょうという表現。</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions before we have all the facts.</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>すべての事実が揃う前に、早合点しないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>Let's not be hasty</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>EX-0886</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>断り・保留,依頼</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>I'm swamped this week, can we reschedule?</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>今週は非常に忙しいので、予定を変更できないか頼む表現。</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>I'm swamped this week, can we reschedule our meeting to next Monday?</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>今週は立て込んでいて、打ち合わせを来週月曜に変更できますか。</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>I'm slammed this week</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>EX-0887</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>We should leverage our existing resources.</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>既存のリソースを有効活用すべきだ、という提案の表現。</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>We should leverage our existing resources before investing in new tools.</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>新しいツールに投資する前に、既存のリソースを有効活用すべきです。</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>We should make the most of what we already have</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>「leverage」は「てこの原理を使う」が原義で、ビジネスでは「有効活用する」の意味で頻出。</t>
+        </is>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>EX-0888</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>I take full responsibility for the oversight.</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>その見落としについて全責任を負う、という謝罪の表現。</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>I take full responsibility for the oversight and will correct it immediately.</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>この見落としについては全責任を負い、直ちに修正いたします。</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>I'm fully accountable for this mistake</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>EX-0889</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>Let's drill down into the numbers.</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>数字を詳しく掘り下げて見ていきましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Let's drill down into the numbers to see what's driving the increase.</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>何が増加の要因なのか、数字を詳しく掘り下げてみましょう。</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>Let's dig into the details</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>EX-0890</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>断り・保留,確認</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>I'll run it by my manager first.</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>まず上司に確認を取ります、という表現。</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>I'll run it by my manager first before I give you a final answer.</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>最終的な回答をする前に、まず上司に確認します。</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>I'll check with my manager</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>EX-0891</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>That's easier said than done.</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>言うのは簡単だが実行するのは難しい、という慣用表現。</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Cutting costs by 20%? That's easier said than done.</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>コストを20%削減する？言うのは簡単ですが実行は難しいですね。</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>Easier said than done</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S892" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>EX-0892</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>Let's not reinvent the wheel.</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>既にあるものをわざわざ作り直す必要はない、という表現。</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Let's not reinvent the wheel; we can reuse the template from last year.</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>わざわざ一から作り直さなくても、去年のテンプレートを再利用できます。</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>No need to start from scratch</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>EX-0893</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>We're open to negotiating the terms.</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>条件について交渉の余地がある、という表現。</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>We're open to negotiating the terms if the volume increases.</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>取引量が増えるのであれば、条件について交渉の余地はあります。</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>The terms are negotiable</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S894" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>EX-0894</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>I'd like to table a counterproposal.</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>代替案を提示したい、という交渉の場での表現。</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>I'd like to table a counterproposal that addresses both concerns.</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>両方の懸念に対応する代替案を提示させていただきたいです。</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>I'd like to offer an alternative proposal</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>ここでの「table」は英国用法で「議題に上げる」の意味。米国用法（保留する）と混同しないよう注意。</t>
+        </is>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S895" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>EX-0895</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>同意・肯定,提案</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>Let's meet halfway on this.</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>お互いに歩み寄りましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Let's meet halfway on this and split the difference.</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>ここはお互い歩み寄って、差額を折半しましょう。</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>Let's find some middle ground</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S896" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>EX-0896</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>I'm not in a position to authorize that.</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>その承認をする権限は自分にない、という表現。</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>I'm afraid I'm not in a position to authorize that without approval from finance.</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>恐れ入りますが、財務部の承認なしにはその許可を出す立場にありません。</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>That's outside my authority</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S897" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>EX-0897</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>Let's put a pin in this until the numbers come in.</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>数字が出揃うまでこの件は一旦保留にしましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Let's put a pin in this until the numbers come in next week.</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>来週数字が出るまで、この件は一旦保留にしておきましょう。</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>Let's hold off on this</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>「put a pin in it」は「一旦保留する」という口語的なイディオム。</t>
+        </is>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S898" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>EX-0898</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>メール,交渉</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>謝罪,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>We appreciate your flexibility on this matter.</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>柔軟に対応してくれたことへの感謝を伝える丁寧な表現。</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>We appreciate your flexibility on this matter and will keep you updated.</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>この件について柔軟にご対応いただき感謝いたします。今後も進捗をご連絡します。</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>Thank you for being flexible</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S899" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>EX-0899</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>I'll cascade this information to the team.</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>この情報をチーム全体に順次共有します、という表現。</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>I'll cascade this information to the team by the end of the week.</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>今週末までにこの情報をチーム全体へ共有します。</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>I'll share this with the whole team</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>「cascade」は情報が上から下へ段階的に伝わることを表す、ややフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S900" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>EX-0900</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>確認,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>Let's nail down the action items before we finish.</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>終わる前にやるべきことをはっきり決めましょう、という表現。</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Let's nail down the action items before we finish today's meeting.</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>今日の会議を終える前に、やるべきことをはっきり決めておきましょう。</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>Let's finalize the action items</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R901" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S901"/>
+  <dimension ref="A1:S951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -68857,6 +68857,3776 @@
         </is>
       </c>
     </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>EX-0901</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>Let's park that for now and circle back after the break.</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>それは一旦保留にして、休憩後にまた話しましょう。</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Let's park that for now and circle back after the break so we can stay on schedule.</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>予定通り進めるために、それは一旦保留にして休憩後にまた話しましょう。</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>I think we should park the pricing discussion and circle back once finance weighs in.</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>価格の議論は一旦保留にして、財務部の意見が出てから戻るべきだと思います。</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>Let's table that for later,Let's revisit that afterward</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>「park」は「一時的に保留する」というカジュアルなビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R902" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>EX-0902</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>Can we take this offline?</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>この話は別の場で（会議の後で個別に）しませんか。</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>This is getting into the weeds — can we take this offline?</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>話が細かくなりすぎているので、この件は別の場で話しませんか。</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Let's take this offline and I'll follow up with you after the meeting.</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>この件は会議の外で話しましょう、後でフォローアップします。</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>Let's discuss this separately</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S903" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>EX-0903</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>To put it another way, ...</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>別の言い方をすると、〜。</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>To put it another way, our costs are rising faster than our revenue.</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>別の言い方をすると、コストが売上よりも速いペースで増えています。</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>In other words, ...,Put differently, ...</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S904" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>EX-0904</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>Piggybacking off that idea, what if we tried a different approach?</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>その案に乗っかると、別のアプローチを試してみるのはどうでしょう。</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Piggybacking off that idea, what if we tried a different approach for the launch?</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>その案に乗っかると、ローンチで別のアプローチを試してみるのはどうでしょう。</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>Building on that idea...</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>「piggyback off」は他人の意見やアイデアに乗って発展させることを表す口語表現。</t>
+        </is>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S905" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>EX-0905</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>Let's make sure we're all on the same page before we move forward.</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>先に進む前に、みんなの認識を揃えておきましょう。</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Let's make sure we're all on the same page before we move forward with the launch.</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>ローンチを進める前に、みんなの認識を揃えておきましょう。</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>Let's align on this first</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S906" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>EX-0906</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but is that a fair summary?</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>勝手に代弁したくはないのですが、それで要約は合っていますか。</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but is that a fair summary of your concern?</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>勝手に代弁したくはないのですが、それであなたの懸念の要約は合っていますか。</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>相手の発言を要約・確認する際に丁寧さを保つ表現。</t>
+        </is>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S907" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>EX-0907</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>Let's not boil the ocean here — can we narrow the scope?</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>あれもこれもやろうとせず、範囲を絞りませんか。</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Let's not boil the ocean here — can we narrow the scope to just the top three issues?</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>あれもこれもやろうとせず、上位3つの問題だけに範囲を絞りませんか。</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>Let's not try to do everything at once</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>「boil the ocean」は「実現不可能なほど手を広げる」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S908" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>EX-0908</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>Just to play devil's advocate for a second...</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>あえて反対意見を言わせてもらうと〜。</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Just to play devil's advocate for a second, what if the client says no?</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>あえて反対意見を言わせてもらうと、クライアントが断ったらどうしますか。</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>議論を深めるためにわざと反対の立場を取ることを示す前置き。</t>
+        </is>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S909" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>EX-0909</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>Can we take a step back and look at the bigger picture?</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>一歩下がって全体像を見てみませんか。</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Before we dive into details, can we take a step back and look at the bigger picture?</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>詳細に入る前に、一歩下がって全体像を見てみませんか。</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S910" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>EX-0910</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>I'll defer to your judgment on this one.</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>この件についてはあなたの判断に従います。</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>You know the client better than I do, so I'll defer to your judgment on this one.</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>あなたの方がクライアントをよく知っているので、この件はあなたの判断に従います。</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>I'll leave it up to you</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S911" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>EX-0911</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>雑談,電話</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>It's great to finally catch up with you again.</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>お久しぶりです。</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>It's great to finally catch up with you again — how have you been?</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>ようやく近況を話せて嬉しいです。お元気でしたか。</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S912" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>EX-0912</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>Did you have a good weekend?</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>良い週末を過ごせましたか。</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Good morning! Did you have a good weekend?</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>おはようございます。良い週末を過ごせましたか。</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S913" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>EX-0913</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>I could really use a coffee right about now.</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>今すぐコーヒーが欲しい気分です。</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Long meeting, huh? I could really use a coffee right about now.</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>長い会議でしたね。今すぐコーヒーが欲しい気分です。</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S914" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>EX-0914</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>Small world, isn't it?</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>世間って狭いですね。</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>You used to work at the same company as my brother? Small world, isn't it?</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>私の兄と同じ会社で働いていたんですか。世間って狭いですね。</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S915" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>EX-0915</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>I've been meaning to ask you about that.</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>それについて聞こうと思っていたんです。</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>I've been meaning to ask you about that new project you're on.</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>あなたが今関わっている新しいプロジェクトについて聞こうと思っていたんです。</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S916" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>EX-0916</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>It's on the tip of my tongue.</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>喉まで出かかっているんですが（思い出せない）。</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>What's the name of that client... it's on the tip of my tongue.</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>あのクライアントの名前、何でしたっけ…喉まで出かかっているんですが。</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>言葉や名前を思い出せそうで思い出せない時の慣用表現。</t>
+        </is>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S917" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>EX-0917</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>Don't be a stranger.</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>また連絡してくださいね（疎遠にならないで）。</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>It was great catching up — don't be a stranger, okay?</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>近況を話せて良かったです。また連絡してくださいね。</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>別れ際の挨拶として使われるカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S918" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>EX-0918</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>Thank you for your continued support.</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>いつもご支援いただきありがとうございます。</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Thank you for your continued support throughout this project.</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>このプロジェクトを通じて、いつもご支援いただきありがとうございます。</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>We appreciate your ongoing support</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>EX-0919</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>Should you require any further information, please let me know.</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>追加情報が必要でしたら、お知らせください。</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Should you require any further information, please let me know at your convenience.</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>追加情報が必要でしたら、ご都合の良いときにお知らせください。</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>Let me know if you need anything else</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S920" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>EX-0920</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>I'll loop in the relevant team members.</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>関係するチームメンバーを話に加えます。</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>I'll loop in the relevant team members so we can move this forward faster.</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>話を早く進められるように、関係するチームメンバーを加えます。</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Let me loop in our legal team before we finalize the contract.</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>契約を確定させる前に、法務チームを話に加えさせてください。</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>I'll bring in...</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S921" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>EX-0921</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>Kindly find the revised document attached for your review.</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>ご確認用に修正版の文書を添付いたしましたのでご覧ください。</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Kindly find the revised document attached for your review at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>ご都合の良いときに、ご確認用に修正版の文書を添付いたしましたのでご覧ください。</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>Please find attached...</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S922" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>EX-0922</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>確認,依頼</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>I don't want this to fall by the wayside, so I'm following up again.</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>この件が放置されないよう、改めてフォローアップしています。</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>I don't want this to fall by the wayside, so I'm following up again on the contract details.</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>契約の詳細が放置されないよう、改めてフォローアップしています。</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>I don't want this to slip through the cracks</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>「fall by the wayside」は「放置される、うやむやになる」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S923" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>EX-0923</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>Per our conversation earlier, I'm sending over the details.</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>先ほどお話しした通り、詳細をお送りします。</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Per our conversation earlier, I'm sending over the details of the proposed schedule.</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>先ほどお話しした通り、提案するスケジュールの詳細をお送りします。</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>As discussed, ...</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S924" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>EX-0924</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>Apologies for jumping in late on this thread.</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>このスレッドに今さら参加してすみません。</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Apologies for jumping in late on this thread — I just got back from leave.</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>このスレッドに今さら参加してすみません。休暇から戻ったばかりでして。</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S925" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>EX-0925</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>Let me get back to you on that shortly.</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>それについては折り返しご連絡します。</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>I don't have that number in front of me — let me get back to you on that shortly.</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>その数字が今手元にないので、折り返しご連絡します。</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>I'll follow up with you soon</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S926" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>EX-0926</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>You're breaking up a little — could you repeat that?</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>少し声が途切れています。もう一度言っていただけますか。</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Sorry, you're breaking up a little — could you repeat that last part?</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>すみません、少し声が途切れています。最後の部分をもう一度言っていただけますか。</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S927" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>EX-0927</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>Can you hear me okay on your end?</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>そちらでちゃんと聞こえていますか。</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Can you hear me okay on your end? The connection seems a bit unstable.</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>そちらでちゃんと聞こえていますか。接続が少し不安定なようです。</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S928" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>EX-0928</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>I'll put you on speaker so the rest of the team can join in.</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>他のメンバーも参加できるようスピーカーにします。</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>I'll put you on speaker so the rest of the team can join in on the call.</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>他のメンバーも通話に参加できるよう、スピーカーにします。</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S929" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>EX-0929</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>Let's touch base again once the numbers come in.</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>数字が出たらまた連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Let's touch base again once the numbers come in from the finance team.</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>財務チームから数字が出たら、また連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>Let's reconnect later</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S930" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>EX-0930</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>電話,雑談</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>I'll shoot you a text if anything changes.</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>何か変更があればメッセージを送ります。</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>I'll shoot you a text if anything changes before tomorrow's call.</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>明日の電話までに何か変更があればメッセージを送ります。</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S931" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>EX-0931</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>Without further ado, let's get into it.</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>それでは早速、本題に入りましょう。</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Without further ado, let's get into it — we have a lot to cover today.</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>それでは早速、本題に入りましょう。今日は話すことがたくさんあります。</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>Let's get right to it</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S932" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>EX-0932</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>I'll hand it over to my colleague to walk you through the numbers.</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>数字については同僚から説明させます。</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>I'll hand it over to my colleague to walk you through the numbers in detail.</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>数字の詳細については同僚から説明させます。</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>I'll pass it over to...</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S933" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>EX-0933</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>Bear with me while I pull up the next slide.</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>次のスライドを出す間、少々お待ちください。</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Bear with me while I pull up the next slide — technical difficulties.</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>次のスライドを出す間、少々お待ちください。ちょっと技術的な問題がありまして。</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>Just a moment, please</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S934" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>EX-0934</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>That brings me to my final point.</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>それが最後のポイントにつながります。</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>That brings me to my final point: customer retention starts on day one.</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>それが最後のポイントにつながります。顧客維持は初日から始まります。</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>This leads to my last point</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S935" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>EX-0935</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>I'll leave you with this thought before we close.</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>最後に一つ、皆さんに考えていただきたいことがあります。</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>I'll leave you with this thought before we close: the market won't wait for us.</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>最後に一つ、市場は私たちを待ってくれないということを考えていただきたいです。</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S936" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>EX-0936</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>I'll try to keep this brief.</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>手短にまとめようと思います。</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>I know everyone's busy, so I'll try to keep this brief.</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>皆さん忙しいと思いますので、手短にまとめようと思います。</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>I'll keep it short</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S937" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>EX-0937</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>Let the data speak for itself.</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>データそのものに語らせましょう（数字が明白な証拠になっている）。</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>I won't editorialize further — let the data speak for itself.</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>これ以上の解説は控えます。データそのものに語らせましょう。</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S938" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>EX-0938</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>依頼・断り,電話</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>Could we set up a quick call to go over this?</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>この件について、簡単に電話で話す機会をいただけますか。</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Could we set up a quick call to go over this later today?</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>今日中に、この件について簡単に電話で話す機会をいただけますか。</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>Can we hop on a call?</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S939" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>EX-0939</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>依頼・断り,交渉</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>断り・保留,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>We'd need a separate agreement to cover that request.</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>それは当初合意した範囲外です。</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>We'd need a separate agreement to cover that request, so it would require a separate quote.</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>そのご依頼に対応するには別途契約が必要ですので、別途お見積もりが必要になります。</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>That falls outside our original agreement</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S940" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>EX-0940</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>I hate to be a bother, but could you clarify one thing?</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>お手数をおかけして恐縮ですが、一点確認させていただけますか。</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>I hate to be a bother, but could you clarify one thing about the invoice?</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>お手数をおかけして恐縮ですが、請求書について一点確認させていただけますか。</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>Sorry to trouble you, but...</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S941" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>EX-0941</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>Let me check my bandwidth and get back to you.</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>自分の空き状況を確認してからお返事します。</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Let me check my bandwidth and get back to you by tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>自分の空き状況を確認して、明日の朝までにお返事します。</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>Let me check my schedule</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>「bandwidth」は「対応できる余力・時間」を指す口語的な比喩表現。</t>
+        </is>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S942" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>EX-0942</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>I'd rather not commit to that without checking with my manager first.</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>上司に確認する前に、それを確約するのは避けたいです。</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>I'd rather not commit to that without checking with my manager first, if that's okay.</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>よろしければ、上司に確認する前にそれを確約するのは避けたいです。</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S943" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>EX-0943</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>Would you mind terribly if I asked for an extension?</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>大変恐縮ですが、延長をお願いしてもよろしいでしょうか。</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Would you mind terribly if I asked for an extension on the final report?</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>大変恐縮ですが、最終報告書の提出期限の延長をお願いしてもよろしいでしょうか。</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>かなり丁寧・へりくだった依頼表現。</t>
+        </is>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S944" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>EX-0944</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>Where does that leave us in terms of pricing?</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>価格についてはどのような状況になりますか。</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Where does that leave us in terms of pricing for the second phase?</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>第2フェーズの価格についてはどのような状況になりますか。</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S945" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>EX-0945</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>That's a bit of a tough sell on our end.</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>こちらとしては、それはなかなか納得しがたい条件です。</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>That's a bit of a tough sell on our end, given the current budget constraints.</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>現在の予算制約を考えると、こちらとしてはそれはなかなか納得しがたい条件です。</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S946" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>EX-0946</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>提案,依頼</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>Could we revisit the terms once the pilot phase wraps up?</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>パイロット期間が終わったら、条件を見直すことはできますか。</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Could we revisit the terms once the pilot phase wraps up next quarter?</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>来四半期にパイロット期間が終わったら、条件を見直すことはできますか。</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R947" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>EX-0947</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>Let's meet in the middle on this.</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>ここは歩み寄りましょう。</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Let's meet in the middle on this — how about splitting the difference?</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>ここは歩み寄りましょう。差額を折半するのはどうですか。</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>Let's find a middle ground</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S948" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>EX-0948</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>反論・懸念,確認</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>That's contingent on a few factors we'd need to iron out first.</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>それはいくつかの条件を先に詰める必要があります。</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>That's contingent on a few factors we'd need to iron out first, such as volume discounts.</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>数量割引など、それはいくつかの条件を先に詰める必要があります。</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>EX-0949</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>I don't mean to rain on your parade, but have we considered the risks?</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>水を差すつもりはないのですが、リスクは検討済みでしょうか。</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>I don't mean to rain on your parade, but have we considered the risks of moving so quickly?</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>水を差すつもりはないのですが、そんなに急いで進めるリスクは検討済みでしょうか。</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>「rain on someone's parade」は「水を差す、興ざめさせる」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S950" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>EX-0950</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>反論・懸念,提案</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>Let's not put the cart before the horse on this one.</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>この件は順序を間違えないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Let's not put the cart before the horse — we should finalize the budget before hiring.</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>順序を間違えないようにしましょう。採用の前に予算を確定すべきです。</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>Let's not get ahead of ourselves</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>「put the cart before the horse」は「順序を逆にする」という意味の慣用句。</t>
+        </is>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S951"/>
+  <dimension ref="A1:S1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -72627,6 +72627,3941 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>EX-0951</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>Let's park that for now and come back to it later.</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>その件は一旦保留にして後で戻ってきましょう、という意味の表現。</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Let's park that for now and come back to it later once we have more data.</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>データが揃うまで、その件は一旦保留にして後で戻りましょう。</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>I think we should park the budget discussion until next week.</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>予算の議論は来週まで保留にすべきだと思います。</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>Let's table that for now,Let's put a pin in it</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>「park」は駐車のイメージで、議題を一時的に脇に置くニュアンス。</t>
+        </is>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S952" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>EX-0952</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>I'll circle back to you on that by end of day.</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>その件については本日中に改めて連絡する、という意味。</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>I'll circle back to you on that by end of day once I've checked with the team.</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>チームに確認した上で、本日中にその件について改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>I'll get back to you</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S953" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>EX-0953</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>I don't want to put too fine a point on it, but...</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>はっきり言いにくいことを前置きしつつ率直に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>I don't want to put too fine a point on it, but the current plan won't meet the deadline.</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>はっきり言いたくはないのですが、今の計画では締め切りに間に合いません。</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>To be blunt</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>やや遠回しに本音を切り出す前置き表現。</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S954" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>EX-0954</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>同意・肯定,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>I hear where you're coming from, but...</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>相手の立場を理解しつつ、異なる意見を述べる際の前置き。</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>I hear where you're coming from, but I think we need a more conservative estimate.</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>おっしゃることは分かりますが、もっと控えめな見積もりが必要だと思います。</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>I hear where you're coming from, but the client won't accept that timeline.</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>お気持ちは分かりますが、そのスケジュールではクライアントが納得しません。</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>I see your point, but</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R955" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S955" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>EX-0955</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>That's a bit outside my wheelhouse.</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>それは自分の専門分野ではない、という意味の表現。</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>That's a bit outside my wheelhouse—you should ask the legal team.</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>それは私の専門外なので、法務チームに聞いてください。</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>That's not really my area</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>カジュアルな場面で使われることが多い。</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R956" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S956" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>EX-0956</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>Could you walk me through the numbers?</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>数字について順を追って説明してほしい、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Could you walk me through the numbers before we finalize the report?</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>報告書を確定する前に、数字について説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Could you walk me through the numbers on slide 5 again?</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>スライド5の数字についてもう一度説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>Could you break it down for me</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S957" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>EX-0957</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>I want to make sure we're all on the same page before we move forward.</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>次に進む前に全員の認識を揃えたい、という表現。</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>I want to make sure we're all on the same page before we move forward with the launch.</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>ローンチを進める前に、全員の認識を揃えておきたいです。</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>Let's align on this first</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S958" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>EX-0958</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>Could we push the meeting back by half an hour?</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>会議の時間を30分後ろにずらしてほしい、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Could we push the meeting back by half an hour? Something urgent came up.</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>急用ができたので、会議を30分後ろにずらしていただけますか。</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>Could we move the meeting later</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S959" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>EX-0959</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>I'm going to have to push back on that.</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>その意見・提案に対して反対せざるを得ない、という表現。</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>I'm going to have to push back on that—the timeline just isn't realistic.</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>その点については反対せざるを得ません。スケジュールが現実的ではありません。</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>I'm going to have to push back on that proposal for budget reasons.</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>予算の都合上、その提案には反対せざるを得ません。</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>I have to disagree</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>EX-0960</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>Let's leave no stone unturned on this project.</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>このプロジェクトについてはあらゆる可能性を徹底的に検討しよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Given the stakes, let's leave no stone unturned on this project.</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>リスクの大きさを考えると、このプロジェクトはあらゆる可能性を徹底的に調べましょう。</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>Let's be thorough about this</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>やや大げさな決意表明のニュアンス。</t>
+        </is>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R961" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S961" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>EX-0961</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>I'll loop you in once I hear back from them.</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>先方から返事があり次第、共有・巻き込む、という表現。</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>I'll loop you in once I hear back from them on the contract terms.</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>契約条件について先方から返事があり次第、共有します。</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>I'll keep you posted</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S962" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>EX-0962</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>I'd like to table a motion to revisit the budget.</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>予算について再検討する議題を提出したい、という表現（フォーマルな議事進行）。</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>I'd like to table a motion to revisit the budget for Q3.</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>第3四半期の予算について再検討する議題を提出したいと思います。</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>米国では「table」は「棚上げする」、英国では「議題に上げる」の意味になるため文脈に注意。</t>
+        </is>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R963" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S963" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>EX-0963</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>That rings a bell, but I can't place it.</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>聞き覚えはあるが、はっきり思い出せない、という表現。</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>That rings a bell, but I can't place it—did we discuss this last quarter?</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>聞き覚えはあるのですが、思い出せません。前四半期に話しましたか。</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>That sounds familiar</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S964" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>EX-0964</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>確認,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>Correct me if I'm wrong, but didn't we agree on a different date?</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>間違っていたら訂正してほしいが、と前置きしつつ確認する表現。</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>Correct me if I'm wrong, but didn't we agree on a different date last time?</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>間違っていたらすみませんが、前回は別の日程で合意しませんでしたか。</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>If I'm not mistaken</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>EX-0965</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>Let's play devil's advocate for a second.</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>あえて反対の立場から意見を言ってみよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>Let's play devil's advocate for a second—what if the client says no?</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>あえて反対の立場で考えてみましょう。クライアントが断ったらどうしますか。</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>Let's consider the counterargument</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R966" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S966" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>EX-0966</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>依頼・断り,会議</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>I don't have the bandwidth to take that on right now.</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>今はその仕事を引き受ける余裕がない、という断りの表現。</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>I don't have the bandwidth to take that on right now, given the current workload.</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>今の業務量を考えると、その仕事を引き受ける余裕がありません。</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Sorry, I don't have the bandwidth this month—can we revisit in January?</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが今月は余裕がありません。1月に改めて検討できますか。</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>I'm at capacity right now</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R967" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S967" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>EX-0967</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>Let's put our heads together on this.</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>皆で知恵を出し合おう、という表現。</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Let's put our heads together on this and come up with a solution.</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>皆で知恵を出し合って、解決策を考えましょう。</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>Let's brainstorm together</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P968" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R968" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S968" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>EX-0968</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>I'm afraid that's a non-starter for us.</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>その条件は最初から検討にすら値しない、という強めの断り表現。</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>I'm afraid a price increase of that size is a non-starter for us.</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが、その規模の値上げは弊社としては受け入れられません。</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>That's not something we can consider</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>かなり強い拒否表現なので、関係性に注意して使う。</t>
+        </is>
+      </c>
+      <c r="P969" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R969" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S969" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>EX-0969</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>Just to play it safe, let's build in some buffer time.</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>念のため、余裕を持ったスケジュールにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>Just to play it safe, let's build in some buffer time before the launch.</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>念のため、ローンチ前に余裕を持たせたスケジュールにしましょう。</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>Let's leave some margin</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R970" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S970" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>EX-0970</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>交渉,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>断り・保留,確認</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>I'll need to run this by my manager first.</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>上司に確認してから返答する、という表現。</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>I'll need to run this by my manager first before I can confirm.</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>確定する前に、まず上司に確認する必要があります。</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>I need to check with my boss</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P971" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R971" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S971" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>EX-0971</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>Let's revisit this once the dust settles.</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>状況が落ち着いてから改めて検討しよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>Let's revisit this once the dust settles from the reorganization.</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>組織再編が落ち着いたら、改めてこの件を検討しましょう。</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>Let's wait until things calm down</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P972" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R972" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S972" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>EX-0972</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>Sorry to jump in, but could I add a quick point?</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>話に割り込んで一言付け加えたい時の丁寧な表現。</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>Sorry to jump in, but could I add a quick point about the budget?</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>割り込んですみませんが、予算について一言よろしいですか。</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>May I interject</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P973" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R973" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S973" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>EX-0973</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>I think we're splitting hairs at this point.</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>些細な違いにこだわりすぎている、という表現。</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>I think we're splitting hairs at this point—let's just pick one option.</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>もう些細な違いにこだわりすぎていると思います。どちらか選びましょう。</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>We're overanalyzing this</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P974" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R974" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S974" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>EX-0974</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>Let's get the ball rolling on this.</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>この件を始めよう、動き出そう、という表現。</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>Let's get the ball rolling on this so we don't fall behind schedule.</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>スケジュールに遅れないよう、この件を始めましょう。</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>Let's kick things off</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R975" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S975" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>EX-0975</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>I'm on the fence about this proposal.</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>賛成か反対か決めかねている、という表現。</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>I'm on the fence about this proposal—I need to see more data.</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>この提案については賛否を決めかねています。もっとデータが必要です。</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>I'm undecided</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P976" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R976" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S976" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>EX-0976</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>交渉,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>I'd like to sleep on it before giving you an answer.</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>即答せず一晩考えてから答えたい、という表現。</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>I'd like to sleep on it before giving you an answer on the contract.</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>契約についてお答えする前に、一晩考えさせてください。</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>Let me think it over</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P977" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R977" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S977" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>EX-0977</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>Let's iron out the details before we sign anything.</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>契約前に細かい点をきちんと詰めよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>Let's iron out the details before we sign anything with the vendor.</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>ベンダーと契約する前に、細かい点をきちんと詰めましょう。</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>Let's finalize the details</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P978" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R978" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S978" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>EX-0978</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>Let's agree to disagree on this one.</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>意見が合わないまま、その状態を受け入れて話を進めよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>Let's agree to disagree on this one and move on to the next agenda item.</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>この件は意見の相違を受け入れて、次の議題に進みましょう。</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P979" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R979" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S979" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>EX-0979</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>反論・懸念,確認</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>I want to flag a potential risk before we proceed.</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>先に進む前に懸念点を指摘したい、という表現。</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>I want to flag a potential risk before we proceed with the vendor contract.</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>ベンダー契約を進める前に、潜在的なリスクを指摘しておきたいです。</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>I want to flag a potential delay in the shipping schedule.</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>配送スケジュールの遅延の可能性について指摘しておきたいです。</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>I want to raise a concern</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P980" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R980" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S980" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>EX-0980</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>依頼,提案</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>Could we sync up sometime this week?</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>今週中に打ち合わせをしたい、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>Could we sync up sometime this week to align on next steps?</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>次のステップについて認識を合わせるため、今週中に打ち合わせできますか。</t>
+        </is>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>Could we have a quick call this week</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P981" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S981" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>EX-0981</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions just yet.</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>まだ結論を急がないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>Let's not jump to conclusions just yet—we haven't heard the client's side.</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>まだ結論を急がないでおきましょう。クライアントの言い分をまだ聞いていません。</t>
+        </is>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>Let's not be hasty</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P982" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R982" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S982" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>EX-0982</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>I'll keep this brief since I know everyone's busy.</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>皆忙しいと分かっているので簡潔に話す、というプレゼンの前置き。</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>I'll keep this brief since I know everyone's busy today.</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>皆さんお忙しいと存じますので、手短にお話しします。</t>
+        </is>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>I'll be quick</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P983" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R983" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S983" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>EX-0983</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>Let's wrap this up so we don't run over time.</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>時間超過しないように会議をまとめよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>Let's wrap this up so we don't run over time for the next meeting.</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>次の会議に遅れないよう、このあたりでまとめましょう。</t>
+        </is>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>Let's bring this to a close</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P984" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R984" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S984" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>EX-0984</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>I'd rather err on the side of caution here.</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>ここでは慎重な方を選びたい、という表現。</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>I'd rather err on the side of caution here and delay the launch by a week.</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>ここは慎重を期して、ローンチを1週間遅らせたいです。</t>
+        </is>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>Better safe than sorry</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P985" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R985" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S985" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>EX-0985</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>Let's not go down that rabbit hole right now.</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>今その話題を深掘りするのはやめておこう、という表現。</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Let's not go down that rabbit hole right now—we're short on time.</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>時間がないので、今それを深掘りするのはやめておきましょう。</t>
+        </is>
+      </c>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>Let's not get sidetracked</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P986" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R986" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S986" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>EX-0986</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>I appreciate you being upfront about the issue.</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>問題について率直に話してくれたことへの感謝表現。</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>I appreciate you being upfront about the issue instead of hiding it.</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>問題を隠さず率直に話してくれてありがとうございます。</t>
+        </is>
+      </c>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>Thanks for being honest about that</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P987" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R987" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S987" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>EX-0987</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>Let's take a step back and look at this from a different angle.</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>一旦立ち止まって別の視点から考えよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>Let's take a step back and look at this from a different angle before deciding.</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>決定する前に一旦立ち止まり、別の視点から見てみましょう。</t>
+        </is>
+      </c>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>Let's reconsider this</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P988" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R988" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S988" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>EX-0988</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>Let's see if we can meet in the middle on this.</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>お互い譲歩して折り合いをつけよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>Let's see if we can meet in the middle on this price point.</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>この価格については、お互い譲歩できないか考えましょう。</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Let's see if we can meet in the middle on the delivery date.</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>納期についてお互い折り合える点を探しましょう。</t>
+        </is>
+      </c>
+      <c r="M989" t="inlineStr">
+        <is>
+          <t>Let's find a compromise</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P989" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R989" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S989" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>EX-0989</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>依頼・断り,電話</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>I'm afraid my hands are tied on this matter.</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>自分の裁量ではどうにもできない、という強めの断り表現。</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>I'm afraid my hands are tied on this matter—it's company policy.</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>申し訳ありませんが、これは会社の方針のため私の裁量ではどうにもできません。</t>
+        </is>
+      </c>
+      <c r="M990" t="inlineStr">
+        <is>
+          <t>It's out of my control</t>
+        </is>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P990" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R990" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S990" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>EX-0990</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>メール,雑談</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>Thanks for looping me in on this.</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>共有・巻き込んでくれたことへの感謝表現。</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Thanks for looping me in on this—I'll take a look right away.</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>共有してくれてありがとうございます。すぐに確認します。</t>
+        </is>
+      </c>
+      <c r="M991" t="inlineStr">
+        <is>
+          <t>Thanks for including me</t>
+        </is>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P991" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R991" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S991" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>EX-0991</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>Let's zoom out and think about the long-term impact.</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>細部から離れて、長期的な影響を考えよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>Let's zoom out and think about the long-term impact of this decision.</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>この決定の長期的な影響について、視野を広げて考えましょう。</t>
+        </is>
+      </c>
+      <c r="M992" t="inlineStr">
+        <is>
+          <t>Let's think about the bigger picture</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P992" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S992" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>EX-0992</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>Let's not jump the gun on this decision.</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>早まった判断をしないようにしよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Let's not jump the gun on this decision until we've seen the full report.</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>完全な報告書を見るまでは、この決定について早まらないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="M993" t="inlineStr">
+        <is>
+          <t>Let's not be premature about this</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P993" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R993" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S993" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>EX-0993</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>提案,反論・懸念</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>We shouldn't bet everything on a single client.</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>一つの取引先だけに依存するのはリスクが高い、という表現。</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>We shouldn't bet everything on a single client—let's expand our portfolio.</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>一つの取引先だけに依存すべきではありません。取引先を広げましょう。</t>
+        </is>
+      </c>
+      <c r="M994" t="inlineStr">
+        <is>
+          <t>Let's diversify our client base</t>
+        </is>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P994" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R994" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S994" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>EX-0994</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>There's no need to start from square one.</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>一から始める必要はない、既存のものを活用しよう、という表現。</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>There's no need to start from square one—let's build on last year's plan.</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>一から始める必要はありません。昨年の計画を土台にしましょう。</t>
+        </is>
+      </c>
+      <c r="M995" t="inlineStr">
+        <is>
+          <t>No need to reinvent the wheel</t>
+        </is>
+      </c>
+      <c r="N995" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P995" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R995" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S995" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>EX-0995</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>反論・懸念,確認</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>Just to flag, this number doesn't quite add up.</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>念のため指摘しておくと、この数字は計算が合っていない、という表現。</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Just to flag, this number doesn't quite add up compared to the invoice.</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>念のため申し上げますが、この数字は請求書と合っていないようです。</t>
+        </is>
+      </c>
+      <c r="M996" t="inlineStr">
+        <is>
+          <t>Something looks off with this figure</t>
+        </is>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P996" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R996" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S996" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>EX-0996</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>反論・懸念,依頼</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>I hope you don't mind me weighing in, but I have a concern.</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>意見を挟むことをお許しいただきたいが、懸念がある、という前置き表現。</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>I hope you don't mind me weighing in, but I have a concern about the rollout date.</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>意見を挟むようで恐縮ですが、展開時期について懸念があります。</t>
+        </is>
+      </c>
+      <c r="M997" t="inlineStr">
+        <is>
+          <t>If I may add a concern</t>
+        </is>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P997" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R997" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S997" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>EX-0997</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>Let's get straight to the point.</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>遠回しにせず、単刀直入に話そう、という表現。</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Let's get straight to the point—what price are you offering?</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>単刀直入に聞きますが、どのような価格を提示していますか。</t>
+        </is>
+      </c>
+      <c r="M998" t="inlineStr">
+        <is>
+          <t>Let's not beat around the bush</t>
+        </is>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P998" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R998" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S998" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>EX-0998</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>Let's not waste any more time and get down to business.</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>無駄な時間を使わず、本題に取り掛かろう、という表現。</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Let's not waste any more time and get down to business on the contract terms.</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>これ以上時間を無駄にせず、契約条件について本題に入りましょう。</t>
+        </is>
+      </c>
+      <c r="M999" t="inlineStr">
+        <is>
+          <t>Let's get down to work</t>
+        </is>
+      </c>
+      <c r="N999" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P999" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S999" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>EX-0999</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>依頼,断り・保留</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>Would it be possible to discuss this separately after the meeting?</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>会議後に個別に話したい、と丁寧に切り出す表現。</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Would it be possible to discuss this separately after the meeting? It's a bit off-topic.</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>少し議題から逸れるので、会議後に個別にお話しできますか。</t>
+        </is>
+      </c>
+      <c r="M1000" t="inlineStr">
+        <is>
+          <t>Can we take this offline</t>
+        </is>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1000" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1000" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1000" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>EX-1000</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>I'll trust your judgment on the final call.</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>最終判断はあなたを信頼して任せる、という表現。</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>I'll trust your judgment on the final call for the vendor selection.</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>ベンダー選定の最終判断は、あなたを信頼してお任せします。</t>
+        </is>
+      </c>
+      <c r="M1001" t="inlineStr">
+        <is>
+          <t>I'll defer to you on this</t>
+        </is>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1001" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1001" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1001" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1001"/>
+  <dimension ref="A1:S1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -76562,6 +76562,881 @@
         </is>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>EX-1001</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>Let's park that for now and circle back later.</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>その話題を一旦保留にして、後で改めて話し合おうという提案。</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Let's park that for now and circle back later once we have more data.</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>その件は一旦保留にして、データが揃ってから改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>We're running out of time, so let's park this topic and circle back later in the week.</t>
+        </is>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>時間がないので、この話題は一旦保留にして今週後半に改めて取り上げましょう。</t>
+        </is>
+      </c>
+      <c r="M1002" t="inlineStr">
+        <is>
+          <t>Let's table this for now,Let's shelve this for the moment</t>
+        </is>
+      </c>
+      <c r="N1002" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1002" t="inlineStr">
+        <is>
+          <t>"park"は「一時的に置いておく」というカジュアルな比喩表現。フォーマルな会議でも使われる。</t>
+        </is>
+      </c>
+      <c r="P1002" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1002" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1002" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>EX-1002</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but...</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>相手の発言を勝手に解釈・代弁したくない、と前置きしながら自分の理解を確認する表現。</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but it sounds like you're leaning toward option B.</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>決めつけるつもりはないのですが、B案に傾いているように聞こえます。</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth, but are you suggesting we delay the launch?</t>
+        </is>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>勝手に解釈したくないのですが、発売延期を提案されているということでしょうか。</t>
+        </is>
+      </c>
+      <c r="M1003" t="inlineStr">
+        <is>
+          <t>Correct me if I'm wrong but,If I'm understanding you correctly</t>
+        </is>
+      </c>
+      <c r="N1003" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1003" t="inlineStr">
+        <is>
+          <t>相手の意図を確認しつつ、断定を避ける丁寧なクッション表現。</t>
+        </is>
+      </c>
+      <c r="P1003" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1003" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1003" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>EX-1003</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>Could you loop me in on the next steps?</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>今後の進め方について自分にも情報共有してほしいと依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Could you loop me in on the next steps once the client responds?</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>クライアントから返信があったら、今後の進め方について私にも共有していただけますか。</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Please loop me in on the next steps so I can plan accordingly.</t>
+        </is>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>こちらでも準備できるよう、今後の進め方を共有してください。</t>
+        </is>
+      </c>
+      <c r="M1004" t="inlineStr">
+        <is>
+          <t>Keep me posted,Keep me in the loop</t>
+        </is>
+      </c>
+      <c r="N1004" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1004" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1004" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1004" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>EX-1004</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>電話,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>I'll have to check my calendar and get back to you.</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>すぐに予定を確認できないため、後で返答すると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>I'll have to check my calendar and get back to you on the meeting time.</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>会議の時間については、予定を確認してから改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="M1005" t="inlineStr">
+        <is>
+          <t>Let me check my schedule and follow up</t>
+        </is>
+      </c>
+      <c r="N1005" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1005" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1005" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1005" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>EX-1005</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>Can we discuss this outside the meeting?</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>議題が長引きそうな場合、会議とは別の場で個別に話し合おうと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>This seems like a bigger topic — can we discuss this outside the meeting?</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>これは大きなテーマになりそうなので、会議とは別の場で話し合いませんか。</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>Let's not derail the agenda; can we discuss this outside the meeting instead?</t>
+        </is>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>議題から逸れてしまうので、この件は会議とは別に話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="M1006" t="inlineStr">
+        <is>
+          <t>Let's take this offline</t>
+        </is>
+      </c>
+      <c r="N1006" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1006" t="inlineStr">
+        <is>
+          <t>"take this offline"とほぼ同義で、会議の効率を保つための定番表現。</t>
+        </is>
+      </c>
+      <c r="P1006" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1006" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1006" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>EX-1006</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>That's a fair point, but let me push back a little.</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>相手の意見を認めつつ、自分の反対意見を丁寧に述べる表現。</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>That's a fair point, but let me push back a little on the timeline.</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>おっしゃることはもっともですが、スケジュールについては少し異論があります。</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>That's a fair point, but let me push back a little — I think the risk is higher than we think.</t>
+        </is>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>その点は理解できますが、少し反論させてください。リスクはもっと高いと思います。</t>
+        </is>
+      </c>
+      <c r="M1007" t="inlineStr">
+        <is>
+          <t>I see your point but I'd like to challenge that a bit</t>
+        </is>
+      </c>
+      <c r="N1007" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1007" t="inlineStr">
+        <is>
+          <t>相手を否定せず、対等な立場で反論するための緩衝表現。</t>
+        </is>
+      </c>
+      <c r="P1007" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1007" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1007" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>EX-1007</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>同意・肯定,確認</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>We're on the same page, then.</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>話し合いの結果、互いの理解や認識が一致していることを確認する表現。</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Great, we're on the same page, then. Let's move forward with the plan.</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>よかった、認識が一致していますね。それでは計画を進めましょう。</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>So we're on the same page — the deadline is next Friday, right?</t>
+        </is>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>つまり認識は一致していますね。締め切りは来週金曜日でよろしいですか。</t>
+        </is>
+      </c>
+      <c r="M1008" t="inlineStr">
+        <is>
+          <t>We're aligned,We see eye to eye on this</t>
+        </is>
+      </c>
+      <c r="N1008" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1008" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1008" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1008" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>EX-1008</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>I'll follow up with an email recap.</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>打ち合わせ内容を後でメールにまとめて送ると伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>I'll follow up with an email recap so everyone has the details in writing.</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>後ほどメールで要点をまとめて送りますので、皆さんも文書で確認できます。</t>
+        </is>
+      </c>
+      <c r="M1009" t="inlineStr">
+        <is>
+          <t>I'll send a summary email,I'll put this in writing</t>
+        </is>
+      </c>
+      <c r="N1009" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1009" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1009" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1009" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>EX-1009</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>提案,断り・保留</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>Can we table this discussion for our next meeting?</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>時間の都合などで、その議題を次回の会議に持ち越そうと提案する表現。</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>We're almost out of time — can we table this discussion for our next meeting?</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>時間がなくなってきたので、この議題は次回の会議に持ち越しませんか。</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Given the complexity, I'd suggest we table this discussion for our next meeting.</t>
+        </is>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>内容が複雑なので、この議論は次回の会議に持ち越すことを提案します。</t>
+        </is>
+      </c>
+      <c r="M1010" t="inlineStr">
+        <is>
+          <t>Let's revisit this next time</t>
+        </is>
+      </c>
+      <c r="N1010" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1010" t="inlineStr">
+        <is>
+          <t>米語では「先送りにする」意味だが、英式英語では逆に「即座に取り上げる」意味になることがあるため注意。</t>
+        </is>
+      </c>
+      <c r="P1010" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1010" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1010" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>EX-1010</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>会議,雑談</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>反論・懸念,提案</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>I think we might be overanalyzing this.</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>議論が細かくなりすぎている、考えすぎているのではないかと指摘する表現。</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>I think we might be overanalyzing this — let's just make a decision and move on.</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>少し考えすぎているかもしれません。決めて先に進みましょう。</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Honestly, I think we're overanalyzing this data point.</t>
+        </is>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>正直なところ、このデータポイントについては分析しすぎだと思います。</t>
+        </is>
+      </c>
+      <c r="M1011" t="inlineStr">
+        <is>
+          <t>We're overthinking this</t>
+        </is>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1011" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1011" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1011" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1011"/>
+  <dimension ref="A1:S1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -77437,6 +77437,841 @@
         </is>
       </c>
     </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>EX-1011</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Could we get this over the line by end of week?</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>今週末までにこれを完了・決着させられますか、という依頼表現。</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Could we get this over the line by end of week? The client is waiting on our confirmation.</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>今週末までにこれを片付けられますか。クライアントが確認を待っています。</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>If we can get this over the line today, we can start the next phase tomorrow.</t>
+        </is>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>今日中にこれを片付けられれば、明日から次のフェーズに入れます。</t>
+        </is>
+      </c>
+      <c r="M1012" t="inlineStr">
+        <is>
+          <t>wrap this up,cross the finish line</t>
+        </is>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1012" t="inlineStr">
+        <is>
+          <t>「over the line」はスポーツ由来で、物事を達成・完了させるというニュアンス。</t>
+        </is>
+      </c>
+      <c r="P1012" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1012" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1012" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>EX-1012</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>プレゼン,会議</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>Let's put our best foot forward on this proposal.</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>この提案では最善を尽くして、良い印象を与えましょうという表現。</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Let's put our best foot forward on this proposal since it's our first pitch to them.</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>この提案は先方への初めてのピッチなので、全力を尽くしましょう。</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>We need to put our best foot forward if we want to win this contract.</t>
+        </is>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>この契約を勝ち取りたいなら、最善を尽くす必要があります。</t>
+        </is>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1013" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1013" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1013" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>EX-1013</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>メール,会議</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>I'll flesh out the details and send them over tomorrow.</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>詳細を肉付けして（詰めて）、明日お送りしますという表現。</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>I'll flesh out the details and send them over tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>詳細を詰めて、明日の朝お送りします。</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Let me flesh out this outline before our next meeting.</t>
+        </is>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>次のミーティングまでにこの概要を詳しく詰めておきます。</t>
+        </is>
+      </c>
+      <c r="M1014" t="inlineStr">
+        <is>
+          <t>work out the details,iron out the specifics</t>
+        </is>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1014" t="inlineStr">
+        <is>
+          <t>「flesh out」は骨組みに肉付けするイメージで、大まかな案を具体化するときに使う。</t>
+        </is>
+      </c>
+      <c r="P1014" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1014" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1014" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>EX-1014</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>We're keeping an open mind about the possibilities.</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>様々な可能性に対して柔軟に、先入観なく考えているという表現。</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>We're keeping an open mind about the possibilities, so feel free to propose alternatives.</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>様々な可能性について柔軟に考えていますので、代替案があればお気軽にご提案ください。</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>At this stage, we're keeping an open mind about the possibilities before committing to a direction.</t>
+        </is>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>この段階では、方向性を決める前に色々な可能性に対して柔軟な姿勢でいます。</t>
+        </is>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1015" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1015" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>EX-1015</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Could you give me a ballpark figure for the total cost?</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>総費用のおおよその金額（概算）を教えてほしいという依頼表現。</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Could you give me a ballpark figure for the total cost before we finalize the scope?</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>スコープを確定する前に、総費用のおおよその金額を教えていただけますか。</t>
+        </is>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1016" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1016" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>EX-1016</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>断り・保留,確認</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>I'll have to get back to you once I've crunched the numbers.</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>数字を計算・分析した上で、改めて回答しますという保留の表現。</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>I'll have to get back to you once I've crunched the numbers on this budget.</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>この予算の数字を計算した上で、改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>Give me until tomorrow — I'll have to get back to you once I've crunched the numbers.</t>
+        </is>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>明日まで待ってください。数字を計算してから改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="N1017" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1017" t="inlineStr">
+        <is>
+          <t>「crunch the numbers」は数字を細かく計算・分析するという口語的表現。</t>
+        </is>
+      </c>
+      <c r="P1017" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1017" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1017" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>EX-1017</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Let's not put all our cards on the table just yet.</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>まだ手の内（情報や条件）を全て明かさないでおきましょう、という交渉時の表現。</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Let's not put all our cards on the table just yet — we can reveal our budget later in the negotiation.</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>まだ手の内を全て明かさないでおきましょう。予算については交渉の後半で伝えれば十分です。</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>I'd rather not put all our cards on the table before we understand their position.</t>
+        </is>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>先方の立場を理解する前に、こちらの手の内を全て明かしたくありません。</t>
+        </is>
+      </c>
+      <c r="M1018" t="inlineStr">
+        <is>
+          <t>keep something in reserve,play it close to the chest</t>
+        </is>
+      </c>
+      <c r="N1018" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1018" t="inlineStr">
+        <is>
+          <t>トランプ用語由来で、交渉における情報戦略を表す慣用句。</t>
+        </is>
+      </c>
+      <c r="P1018" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1018" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1018" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>EX-1018</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>I hope this finds you in good spirits.</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>お元気でお過ごしのことと思います、というメールの書き出しの挨拶表現。</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>I hope this finds you in good spirits as we head into the new quarter.</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>新しい四半期を迎えるにあたり、お元気でお過ごしのことと思います。</t>
+        </is>
+      </c>
+      <c r="M1019" t="inlineStr">
+        <is>
+          <t>I hope this email finds you well</t>
+        </is>
+      </c>
+      <c r="N1019" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1019" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1019" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1019" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>EX-1019</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>提案,依頼</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Could we reconvene once everyone's had a chance to review?</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>全員が確認する時間を取った後で、改めて集まりましょうか、という提案表現。</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Could we reconvene once everyone's had a chance to review the proposal in detail?</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>皆さんが提案書を詳しく確認する時間を取った後で、改めて集まりましょうか。</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Let's reconvene tomorrow afternoon once the team has reviewed the report.</t>
+        </is>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>チームが報告書を確認した後、明日の午後にまた集まりましょう。</t>
+        </is>
+      </c>
+      <c r="M1020" t="inlineStr">
+        <is>
+          <t>regroup later,meet again</t>
+        </is>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1020" t="inlineStr">
+        <is>
+          <t>「reconvene」はフォーマルな会議用語で、一度中断した会議を再度開くこと。</t>
+        </is>
+      </c>
+      <c r="P1020" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1020" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1020" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>EX-1020</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>I think we're on the right track with this approach.</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>このアプローチで正しい方向に進んでいると思います、という肯定的な意見表現。</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>I think we're on the right track with this approach, so let's keep going.</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>このアプローチで正しい方向に進んでいると思うので、このまま続けましょう。</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>After reviewing the results, I think we're on the right track with this approach.</t>
+        </is>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>結果を確認した上で、このアプローチは正しい方向だと思います。</t>
+        </is>
+      </c>
+      <c r="N1021" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1021" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1021" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1021" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1021"/>
+  <dimension ref="A1:S1031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -78272,6 +78272,851 @@
         </is>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>EX-1021</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>Let's unpack this a bit further.</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>このテーマについてもう少し詳しく掘り下げようという提案表現。</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Before we move on, let's unpack this a bit further.</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>次に進む前に、もう少しこの点を詳しく掘り下げましょう。</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>I think there's more to this issue — let's unpack it a bit further.</t>
+        </is>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>この問題にはもっと深い背景がありそうなので、もう少し掘り下げてみましょう。</t>
+        </is>
+      </c>
+      <c r="M1022" t="inlineStr">
+        <is>
+          <t>let's dig deeper into this,let's drill down into this</t>
+        </is>
+      </c>
+      <c r="N1022" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1022" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1022" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1022" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>EX-1022</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>It's great to reconnect after all this time!</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>久しぶりに再会・連絡が取れたことへの喜びを伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>It's great to reconnect after all this time! How have you been?</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>久しぶりに連絡が取れて嬉しいです！最近どうしてましたか？</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>It's great to reconnect after all this time — we should catch up properly soon.</t>
+        </is>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>久しぶりに繋がれて嬉しいです。近いうちにちゃんと話しましょう。</t>
+        </is>
+      </c>
+      <c r="M1023" t="inlineStr">
+        <is>
+          <t>it's been ages!,long time no see!</t>
+        </is>
+      </c>
+      <c r="N1023" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1023" t="inlineStr">
+        <is>
+          <t>カジュアルな再会だけでなく、ビジネスでの久々の連絡再開にも使える。</t>
+        </is>
+      </c>
+      <c r="P1023" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1023" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1023" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>EX-1023</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>How's everything shaping up these days?</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>相手の近況や物事の進み具合を気軽に尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>How's everything shaping up these days? Busy as usual?</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>最近どんな感じですか？相変わらず忙しいですか？</t>
+        </is>
+      </c>
+      <c r="M1024" t="inlineStr">
+        <is>
+          <t>how's it going?</t>
+        </is>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1024" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1024" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1024" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>EX-1024</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>Please see the attached spreadsheet for the breakdown.</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>詳細な内訳を添付のスプレッドシートで確認してほしいと伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Please see the attached spreadsheet for the breakdown of costs.</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>費用の内訳につきましては添付のスプレッドシートをご確認ください。</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>Please see the attached spreadsheet for the breakdown by department.</t>
+        </is>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>部門別の内訳は添付のスプレッドシートをご覧ください。</t>
+        </is>
+      </c>
+      <c r="M1025" t="inlineStr">
+        <is>
+          <t>please see the attached document for further details</t>
+        </is>
+      </c>
+      <c r="N1025" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1025" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1025" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1025" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>EX-1025</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>I wanted to give you a quick status update.</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>進捗状況を簡単に共有したいときに使う切り出し表現。</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>I wanted to give you a quick status update on the project before the weekend.</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>週末前にプロジェクトの進捗を簡単に共有したいと思います。</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>I wanted to give you a quick status update — we're on track to finish by Friday.</t>
+        </is>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>簡単に進捗をお伝えしますが、金曜日までに完了する見込みです。</t>
+        </is>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1026" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1026" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1026" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>EX-1026</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>You're cutting in and out — can you try reconnecting?</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>電話の音声が途切れているときに、接続し直すよう提案する表現。</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>You're cutting in and out — can you try reconnecting?</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>声が途切れ途切れです。一度繋ぎ直してもらえますか？</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Sorry, you're cutting in and out — let me call you back.</t>
+        </is>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>すみません、声が途切れているので、こちらからかけ直します。</t>
+        </is>
+      </c>
+      <c r="M1027" t="inlineStr">
+        <is>
+          <t>you're breaking up a little</t>
+        </is>
+      </c>
+      <c r="N1027" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1027" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1027" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1027" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>EX-1027</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>I'll transfer you over to our billing department.</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>別の部署に電話を取り次ぐときの表現。</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>I'll transfer you over to our billing department right away.</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>すぐに経理部へお繋ぎいたします。</t>
+        </is>
+      </c>
+      <c r="M1028" t="inlineStr">
+        <is>
+          <t>i'll transfer you to the right department</t>
+        </is>
+      </c>
+      <c r="N1028" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1028" t="inlineStr">
+        <is>
+          <t>「transfer A to B」の形で、電話対応の定型表現として頻出。</t>
+        </is>
+      </c>
+      <c r="P1028" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1028" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1028" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>EX-1028</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>Let me walk you through the roadmap for next quarter.</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>今後の計画・ロードマップを説明するときの導入表現。</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Let me walk you through the roadmap for next quarter.</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>来四半期のロードマップについてご説明します。</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Let me walk you through the roadmap before we open the floor to questions.</t>
+        </is>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>質疑応答に入る前に、ロードマップについてご説明します。</t>
+        </is>
+      </c>
+      <c r="M1029" t="inlineStr">
+        <is>
+          <t>let me walk you through the numbers</t>
+        </is>
+      </c>
+      <c r="N1029" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1029" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1029" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1029" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>EX-1029</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>I'm afraid this exceeds what we're authorized to approve.</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>権限の範囲を超えているため対応できないことを丁寧に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>I'm afraid this exceeds what we're authorized to approve at our level.</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>恐れ入りますが、これは私たちの権限で承認できる範囲を超えています。</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>I'm afraid this exceeds what we're authorized to approve without executive sign-off.</t>
+        </is>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>恐れ入りますが、これは役員の承認なしには対応できない範囲です。</t>
+        </is>
+      </c>
+      <c r="M1030" t="inlineStr">
+        <is>
+          <t>that's above my pay grade</t>
+        </is>
+      </c>
+      <c r="N1030" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1030" t="inlineStr">
+        <is>
+          <t>フォーマルな場面での丁寧な断り表現。カジュアルには「that's above my pay grade」に近い。</t>
+        </is>
+      </c>
+      <c r="P1030" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1030" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1030" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>EX-1030</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>提案,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>We could meet you halfway if you extend the timeline.</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>相手が条件を譲歩すればこちらも歩み寄る用意があると伝える交渉表現。</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>We could meet you halfway if you extend the timeline by a week.</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>納期を1週間延ばしていただければ、こちらも歩み寄ることができます。</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>We could meet you halfway if you're willing to adjust the volume.</t>
+        </is>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>数量を調整いただけるなら、こちらも歩み寄る用意があります。</t>
+        </is>
+      </c>
+      <c r="M1031" t="inlineStr">
+        <is>
+          <t>we can meet you halfway,let's find a middle ground</t>
+        </is>
+      </c>
+      <c r="N1031" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1031" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1031" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1031" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1031"/>
+  <dimension ref="A1:S1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -79117,6 +79117,846 @@
         </is>
       </c>
     </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>EX-1031</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>Let's park that for now and revisit it later.</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>その件は一旦保留にして、後で改めて話し合おうという提案。会議で議論が脱線しそうな時によく使う。</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>This is a great point, but let's park that for now and revisit it later in the meeting.</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>これは良い指摘ですが、一旦保留にして会議の後半で改めて話しましょう。</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>We don't have time to dig into pricing today, so let's park that for now.</t>
+        </is>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>今日は価格について深掘りする時間がないので、一旦保留にしましょう。</t>
+        </is>
+      </c>
+      <c r="M1032" t="inlineStr">
+        <is>
+          <t>Let's table that for now,Let's shelve that discussion</t>
+        </is>
+      </c>
+      <c r="N1032" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1032" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1032" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1032" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>EX-1032</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>I'll keep you posted as soon as I know more.</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>状況が分かり次第、相手に知らせるという意味。</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>I'll keep you posted as soon as I know more about the schedule change.</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>スケジュール変更について分かり次第、お知らせします。</t>
+        </is>
+      </c>
+      <c r="M1033" t="inlineStr">
+        <is>
+          <t>I'll update you as soon as I can,I'll let you know once I have more info</t>
+        </is>
+      </c>
+      <c r="N1033" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1033" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1033" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1033" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>EX-1033</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>Could you walk me through your reasoning on this?</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>相手がどのような考え方や根拠でその結論に至ったのかを、順を追って説明してほしいと頼む表現。</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Before we vote, could you walk me through your reasoning on this?</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>投票する前に、その結論に至った考え方を説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>I'd like you to walk me through your reasoning behind the new pricing model.</t>
+        </is>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>新しい価格モデルの背景にある考え方を説明してほしいです。</t>
+        </is>
+      </c>
+      <c r="M1034" t="inlineStr">
+        <is>
+          <t>Could you explain your thought process?,Walk me through how you got there</t>
+        </is>
+      </c>
+      <c r="N1034" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1034" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1034" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1034" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>EX-1034</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>I don't mean to put words in your mouth, but is that what you're suggesting?</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>相手の発言を勝手に解釈して決めつけたくはないが、確認のためにあえて聞き返す表現。反論や懸念を伝える前置きとしても使われる。</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>I don't mean to put words in your mouth, but is that what you're suggesting we do?</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>決めつけるつもりはありませんが、それが提案なのでしょうか。</t>
+        </is>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>I don't want to put words in your mouth — could you clarify what you meant?</t>
+        </is>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>勝手に解釈したくないので、意図を明確にしていただけますか。</t>
+        </is>
+      </c>
+      <c r="M1035" t="inlineStr">
+        <is>
+          <t>Correct me if I'm wrong but...,Just to clarify, are you saying...</t>
+        </is>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1035" t="inlineStr">
+        <is>
+          <t>相手の発言を誤解している可能性を示しつつ、丁寧に反論・確認したい場面で便利。</t>
+        </is>
+      </c>
+      <c r="P1035" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1035" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1035" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>EX-1035</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>Let's touch base once the figures come in.</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>数字（データ）が出揃ったタイミングで、改めて簡単に連絡・打ち合わせをしようという提案。</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>Let's touch base once the Q3 figures come in.</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>第3四半期の数字が出たら、改めて連絡しましょう。</t>
+        </is>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>I'll touch base with you once the survey figures come in next week.</t>
+        </is>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>来週アンケートの結果が出たら、あなたに連絡します。</t>
+        </is>
+      </c>
+      <c r="M1036" t="inlineStr">
+        <is>
+          <t>Let's check in once the numbers are ready,I'll follow up once we have the data</t>
+        </is>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1036" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1036" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1036" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>EX-1036</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Sorry to be a pain, but could you resend that file?</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>相手に手間をかけることを詫びながら、もう一度何かをお願いする際のカジュアルな前置き。</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Sorry to be a pain, but could you resend that file? I can't find it in my inbox.</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>お手数をおかけしますが、そのファイルを再送していただけますか。受信箱に見当たらなくて。</t>
+        </is>
+      </c>
+      <c r="M1037" t="inlineStr">
+        <is>
+          <t>Sorry to bother you again but...,I hate to ask again but...</t>
+        </is>
+      </c>
+      <c r="N1037" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1037" t="inlineStr">
+        <is>
+          <t>カジュアルな社内メールやチャットで使う表現。フォーマルな場では"I apologize for the inconvenience, but..."などに置き換える。</t>
+        </is>
+      </c>
+      <c r="P1037" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1037" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1037" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>EX-1037</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>雑談,会議</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>We're definitely on the same page there.</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>相手と自分の考え・理解が一致していることを強調して伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>We're definitely on the same page there — let's move forward with that plan.</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>その点については完全に同じ考えです。その計画で進めましょう。</t>
+        </is>
+      </c>
+      <c r="M1038" t="inlineStr">
+        <is>
+          <t>We see eye to eye on that,Agreed we're aligned</t>
+        </is>
+      </c>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1038" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1038" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1038" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>EX-1038</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Let me play devil's advocate for a moment.</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>あえて反対の立場や批判的な視点から意見を述べることを断る際の表現。議論を深めるために使われる。</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Let me play devil's advocate for a moment — what if the client says no?</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>あえて反論させてもらいますが、クライアントが断ったらどうしますか。</t>
+        </is>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>Just to play devil's advocate, have we considered the downside risks?</t>
+        </is>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>あえて反対意見を言わせてもらうと、下振れリスクは検討済みでしょうか。</t>
+        </is>
+      </c>
+      <c r="M1039" t="inlineStr">
+        <is>
+          <t>Just to challenge that idea...,Let me push back on that for a second</t>
+        </is>
+      </c>
+      <c r="N1039" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1039" t="inlineStr">
+        <is>
+          <t>相手の意見を否定するのではなく、議論を深める目的で使うことを明示するのがポイント。</t>
+        </is>
+      </c>
+      <c r="P1039" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1039" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1039" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>EX-1039</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>謝罪</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Thanks for bearing with me on such short notice.</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>急な依頼や変更に対応してくれたことへの感謝を伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Thanks for bearing with me on such short notice — I know this wasn't planned.</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>急なお願いにもかかわらず対応してくれてありがとうございます。予定外だったのは承知しています。</t>
+        </is>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>Thank you for bearing with me on such short notice; I'll make sure to give more lead time next time.</t>
+        </is>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>急な対応に感謝します。次回はもっと余裕を持ってお伝えします。</t>
+        </is>
+      </c>
+      <c r="M1040" t="inlineStr">
+        <is>
+          <t>Thanks for accommodating me on such short notice,I appreciate your flexibility</t>
+        </is>
+      </c>
+      <c r="N1040" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1040" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1040" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>EX-1040</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Let's not lose sight of the bigger picture here.</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>細部にとらわれすぎず、全体の目的や方向性を見失わないようにしようという呼びかけ。</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Let's not lose sight of the bigger picture here — our goal is long-term growth.</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>全体像を見失わないようにしましょう。私たちの目標は長期的な成長です。</t>
+        </is>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>It's easy to get caught up in details, but let's not lose sight of the bigger picture.</t>
+        </is>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>細部にこだわりがちですが、全体像を見失わないようにしましょう。</t>
+        </is>
+      </c>
+      <c r="M1041" t="inlineStr">
+        <is>
+          <t>Let's keep our eye on the ball,Don't lose the forest for the trees</t>
+        </is>
+      </c>
+      <c r="N1041" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1041" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1041" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1041" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1041"/>
+  <dimension ref="A1:S1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -79957,6 +79957,856 @@
         </is>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>EX-1041</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Let's circle back to this once we have more data.</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>「今は判断せず、材料が揃ってから改めて話し合おう」という意味。会議で結論を先送りにする際の定番表現。</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Let's circle back to this once we have more data from the pilot test.</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>パイロットテストのデータが揃ったら、この件は改めて話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>I think we should circle back to the budget question next week.</t>
+        </is>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>予算の件は来週改めて話し合った方がいいと思います。</t>
+        </is>
+      </c>
+      <c r="M1042" t="inlineStr">
+        <is>
+          <t>Let's revisit this later.,Let's table this for now.</t>
+        </is>
+      </c>
+      <c r="N1042" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1042" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1042" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1042" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>EX-1042</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>I don't want to put you on the spot, but could I get your take on this?</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>相手に意見を求める際、プレッシャーをかけたくない気持ちを添えて意見を尋ねる表現。「困らせるつもりはないけど」という前置き。</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>I don't want to put you on the spot, but could I get your take on this proposal?</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>困らせるつもりはないのですが、この提案についてのご意見を伺えますか。</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>I don't want to put you on the spot in front of everyone, but what's your honest opinion?</t>
+        </is>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>みんなの前で困らせたくはないのですが、率直な意見を聞かせてもらえますか。</t>
+        </is>
+      </c>
+      <c r="M1043" t="inlineStr">
+        <is>
+          <t>I'd value your honest opinion on this.</t>
+        </is>
+      </c>
+      <c r="N1043" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1043" t="inlineStr">
+        <is>
+          <t>"put someone on the spot" は「人に難しい状況で即答を迫る」という意味のイディオム。</t>
+        </is>
+      </c>
+      <c r="P1043" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1043" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1043" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>EX-1043</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>メール,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>I was wondering if we could extend the deadline by a couple of days.</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>締め切りの延長を丁寧に依頼する表現。"I was wondering if..."は柔らかい依頼の定番フレーズ。</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>I was wondering if we could extend the deadline by a couple of days due to some unexpected delays.</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>予期せぬ遅れがあったため、締め切りを数日延ばしていただけないかと思いまして。</t>
+        </is>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>Would it be possible to extend the deadline by a couple of days? We're still waiting on client feedback.</t>
+        </is>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>クライアントからのフィードバック待ちのため、締め切りを数日延ばすことは可能でしょうか。</t>
+        </is>
+      </c>
+      <c r="M1044" t="inlineStr">
+        <is>
+          <t>Would it be possible to push the deadline back?</t>
+        </is>
+      </c>
+      <c r="N1044" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1044" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1044" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1044" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>EX-1044</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>I'll cc you on this so you're in the loop.</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>メールでCC(写し)に入れて情報共有することを伝える表現。「常に情報を把握できるように」という意味。</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>I'll cc you on this so you're in the loop going forward.</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>今後も状況を把握できるよう、このメールにCCで入れておきますね。</t>
+        </is>
+      </c>
+      <c r="M1045" t="inlineStr">
+        <is>
+          <t>I'll keep you posted.,I'll copy you on this email.</t>
+        </is>
+      </c>
+      <c r="N1045" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1045" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1045" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1045" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>EX-1045</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>Sorry to interrupt, but could I jump in here?</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>会議中に発言を割り込んで発言したいときに使う丁寧な前置き表現。</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Sorry to interrupt, but could I jump in here for a second?</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>話の途中失礼します、少しだけ発言してもよろしいでしょうか。</t>
+        </is>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>Sorry to interrupt, but could I jump in with a quick question?</t>
+        </is>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>話の途中失礼します、少し質問してもいいですか。</t>
+        </is>
+      </c>
+      <c r="M1046" t="inlineStr">
+        <is>
+          <t>Can I add something here?,Mind if I jump in?</t>
+        </is>
+      </c>
+      <c r="N1046" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1046" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1046" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1046" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>EX-1046</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>Let's shelve that idea for the time being.</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>「そのアイデアは当面保留にしよう」という意味。"shelve"は「棚上げにする」という比喩表現。</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Let's shelve that idea for the time being and focus on the current project.</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>そのアイデアは当面棚上げにして、今のプロジェクトに集中しましょう。</t>
+        </is>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>Given the budget constraints, we decided to shelve the expansion plan.</t>
+        </is>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>予算の制約から、拡大計画は棚上げにすることにしました。</t>
+        </is>
+      </c>
+      <c r="M1047" t="inlineStr">
+        <is>
+          <t>Let's put that on hold.,Let's put that on the back burner.</t>
+        </is>
+      </c>
+      <c r="N1047" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1047" t="inlineStr">
+        <is>
+          <t>"shelve"は動詞で「(計画などを)一時中止する、棚上げする」という意味。</t>
+        </is>
+      </c>
+      <c r="P1047" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1047" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1047" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>EX-1047</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Just to make sure I'm on the same page, could you run that by me again?</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>話の内容を正しく理解できているか確認するために、もう一度説明してもらう表現。</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Just to make sure I'm on the same page, could you run that by me again?</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>認識が合っているか確認したいので、もう一度説明していただけますか。</t>
+        </is>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>Could you run the numbers by me again? I want to make sure I understood correctly.</t>
+        </is>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>もう一度数字を確認させてもらえますか。正しく理解できているか確認したいので。</t>
+        </is>
+      </c>
+      <c r="M1048" t="inlineStr">
+        <is>
+          <t>Could you walk me through that again?,Let me confirm I understood correctly.</t>
+        </is>
+      </c>
+      <c r="N1048" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1048" t="inlineStr">
+        <is>
+          <t>"be on the same page"は「認識が一致している」という意味の頻出イディオム。</t>
+        </is>
+      </c>
+      <c r="P1048" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1048" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1048" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>EX-1048</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>That works for me, no objections on my end.</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>提案や条件に対して「私の方は問題ありません、賛成です」と同意を示す表現。</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>That works for me, no objections on my end. Let's move forward with the plan.</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>私の方は問題ありません、このプランで進めましょう。</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>If Thursday works better for everyone, that works for me too, no objections on my end.</t>
+        </is>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>皆さんが木曜日の方が都合が良ければ、私も問題ありません。</t>
+        </is>
+      </c>
+      <c r="M1049" t="inlineStr">
+        <is>
+          <t>Sounds good to me.,I have no issue with that.</t>
+        </is>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1049" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1049" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1049" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>EX-1049</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>Anything new going on with you lately?</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>雑談の中で「最近何か変わったことあった?」と近況を尋ねるカジュアルな表現。</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Anything new going on with you lately? I feel like we haven't caught up in a while.</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>最近何か変わったことあった?しばらく話してなかった気がして。</t>
+        </is>
+      </c>
+      <c r="M1050" t="inlineStr">
+        <is>
+          <t>What's new with you?,How have things been?</t>
+        </is>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1050" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1050" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1050" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>EX-1050</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>Let me walk you through the key takeaways.</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>プレゼンや報告で「要点をご説明します」と伝える定番の導入表現。</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Let me walk you through the key takeaways from this quarter's results.</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>今四半期の結果について、要点をご説明させていただきます。</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>Before we wrap up, let me walk you through the key takeaways one more time.</t>
+        </is>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>締めくくる前に、もう一度要点をご説明させてください。</t>
+        </is>
+      </c>
+      <c r="M1051" t="inlineStr">
+        <is>
+          <t>Let me summarize the main points.,Let me highlight the key findings.</t>
+        </is>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1051" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1051" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1051" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1051"/>
+  <dimension ref="A1:S1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -80807,6 +80807,876 @@
         </is>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>EX-1051</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>Let's circle back to this later.</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>「この件は後でまた話し合いましょう」という意味で、会議中に議論を一旦保留する時に使う表現。</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Let's circle back to this later once we have more data.</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>データが揃ったら、この件は後でまた話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>We're running out of time, so let's circle back to this point tomorrow.</t>
+        </is>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>時間が足りないので、この点は明日また話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="M1052" t="inlineStr">
+        <is>
+          <t>Let's revisit this later,Let's come back to this</t>
+        </is>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1052" t="inlineStr">
+        <is>
+          <t>"table this"と似た意味だが、"circle back"の方がカジュアルで日常会議でよく使われる。</t>
+        </is>
+      </c>
+      <c r="P1052" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1052" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1052" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>EX-1052</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>I'll loop you in on the details.</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>「詳細については後で共有します」という意味で、情報を後で相手に伝えることを約束する表現。</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>I'll loop you in on the details once the contract is finalized.</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>契約が確定したら、詳細について共有します。</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>Could you loop me in on the meeting notes?</t>
+        </is>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>会議の議事録を共有していただけますか。</t>
+        </is>
+      </c>
+      <c r="M1053" t="inlineStr">
+        <is>
+          <t>keep you posted,fill you in</t>
+        </is>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1053" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1053" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1053" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>EX-1053</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>雑談,メール</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>Let's touch base sometime next week.</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>「来週あたりに近況を確認し合いましょう」という軽い提案の表現。</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Let's touch base sometime next week to see how the project is going.</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>プロジェクトの進捗確認のため、来週あたりに一度話しましょう。</t>
+        </is>
+      </c>
+      <c r="M1054" t="inlineStr">
+        <is>
+          <t>check in</t>
+        </is>
+      </c>
+      <c r="N1054" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1054" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1054" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1054" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>EX-1054</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>交渉,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not going to work for us.</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>相手の提案や条件を丁寧に断る際に使うフォーマルな表現。</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>I'm afraid that's not going to work for us given the current budget.</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>現在の予算を考えると、その条件はお受けできかねます。</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>I'm afraid that timeline isn't going to work for us.</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>そのスケジュールでは弊社では対応いたしかねます。</t>
+        </is>
+      </c>
+      <c r="M1055" t="inlineStr">
+        <is>
+          <t>That won't be possible on our end</t>
+        </is>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1055" t="inlineStr">
+        <is>
+          <t>"I'm afraid"を文頭に置くことで、断りの表現を柔らかくできる。</t>
+        </is>
+      </c>
+      <c r="P1055" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1055" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1055" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>EX-1055</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>Feel free to reach out if anything comes up.</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>「何かあればいつでも連絡してください」という、メールの結びによく使われる表現。</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Feel free to reach out if anything comes up before the deadline.</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>締め切り前に何かあれば、いつでもご連絡ください。</t>
+        </is>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Please feel free to reach out if you have any questions.</t>
+        </is>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>ご質問がございましたら、お気軽にご連絡ください。</t>
+        </is>
+      </c>
+      <c r="M1056" t="inlineStr">
+        <is>
+          <t>Don't hesitate to contact me</t>
+        </is>
+      </c>
+      <c r="N1056" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1056" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1056" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1056" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>EX-1056</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>会議,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>依頼,断り・保留</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>Can we push this to another time?</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>予定や議題を別の日時に変更したい時に使う表現。</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Can we push this to another time? I have a conflict this afternoon.</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>別の時間に変更できますか。午後は別の予定があります。</t>
+        </is>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>Would it be possible to push our call to another time this week?</t>
+        </is>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>今週の別の時間に通話を変更することは可能でしょうか。</t>
+        </is>
+      </c>
+      <c r="M1057" t="inlineStr">
+        <is>
+          <t>reschedule,move this to another slot</t>
+        </is>
+      </c>
+      <c r="N1057" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1057" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1057" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1057" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>EX-1057</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>Just wanted to follow up on my last email.</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>以前送ったメールへの返信がない時に、催促や確認の意味で送るフォローアップの表現。</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Just wanted to follow up on my last email regarding the invoice.</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>請求書の件でお送りした前回のメールについて、フォローアップさせていただきます。</t>
+        </is>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>Just wanted to follow up on my last email — did you get a chance to look at it?</t>
+        </is>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>前回のメールについてですが、ご確認いただけましたでしょうか。</t>
+        </is>
+      </c>
+      <c r="M1058" t="inlineStr">
+        <is>
+          <t>just checking in</t>
+        </is>
+      </c>
+      <c r="N1058" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1058" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1058" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1058" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>EX-1058</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>Let's park that idea for now.</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>「そのアイデアは今は一旦保留にしましょう」という意味で、議論を先送りする時の表現。</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Let's park that idea for now and focus on the main agenda.</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>そのアイデアは一旦保留にして、主要な議題に集中しましょう。</t>
+        </is>
+      </c>
+      <c r="M1059" t="inlineStr">
+        <is>
+          <t>put on hold,shelve the idea</t>
+        </is>
+      </c>
+      <c r="N1059" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1059" t="inlineStr">
+        <is>
+          <t>"park"を「保留する」という意味の動詞として使うカジュアルなビジネス表現。</t>
+        </is>
+      </c>
+      <c r="P1059" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1059" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1059" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>EX-1059</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>電話,メール</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>I'll get back to you on that by tomorrow.</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>「その件については明日までに回答します」という、即答を避けて後で返答することを約束する表現。</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>I'll get back to you on that by tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>その件については明日の朝までにご回答します。</t>
+        </is>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>Let me check with my team, and I'll get back to you on that by tomorrow.</t>
+        </is>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>チームに確認の上、明日までにご連絡します。</t>
+        </is>
+      </c>
+      <c r="M1060" t="inlineStr">
+        <is>
+          <t>I'll follow up with you</t>
+        </is>
+      </c>
+      <c r="N1060" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1060" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1060" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1060" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>EX-1060</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>反論・懸念,同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>That's a fair point, but here's another angle.</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>相手の意見を一定程度認めつつ、別の視点を提示する時に使う表現。</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>That's a fair point, but here's another angle we haven't considered.</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>それは一理ありますが、まだ検討していない別の視点があります。</t>
+        </is>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>That's a fair point, but here's another angle to think about.</t>
+        </is>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>それはもっともですが、考慮すべき別の視点があります。</t>
+        </is>
+      </c>
+      <c r="M1061" t="inlineStr">
+        <is>
+          <t>I see your point, however...</t>
+        </is>
+      </c>
+      <c r="N1061" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1061" t="inlineStr">
+        <is>
+          <t>反論する前に相手の意見を一度肯定することで、柔らかい印象を与えられる。</t>
+        </is>
+      </c>
+      <c r="P1061" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1061" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1061" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1061"/>
+  <dimension ref="A1:S1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -81677,6 +81677,891 @@
         </is>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>EX-1061</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>会議,メール</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>circle back</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>後で改めてその話題に戻る、後日相談する</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Let's circle back to this issue after lunch.</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>この件はランチの後にもう一度話し合いましょう。</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>I'll circle back with you once I have more data.</t>
+        </is>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>もっとデータが集まったら改めてご連絡します。</t>
+        </is>
+      </c>
+      <c r="M1062" t="inlineStr">
+        <is>
+          <t>revisit this later,come back to this</t>
+        </is>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1062" t="inlineStr">
+        <is>
+          <t>ビジネスシーンで頻出のカジュアルながらも丁寧な先送り表現。</t>
+        </is>
+      </c>
+      <c r="P1062" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1062" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1062" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>EX-1062</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>雑談,メール,電話</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>確認,相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>touch base</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>近況を確認する、軽く連絡を取り合う</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Let's touch base next week to see how the project is going.</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>来週、プロジェクトの進捗確認のために連絡を取り合いましょう。</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>I just wanted to touch base before the meeting.</t>
+        </is>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>会議の前に軽くご連絡したかっただけです。</t>
+        </is>
+      </c>
+      <c r="M1063" t="inlineStr">
+        <is>
+          <t>check in,catch up</t>
+        </is>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1063" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1063" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1063" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>EX-1063</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>会議,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>確認,依頼</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>run it by someone</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>何かを誰かに確認してもらう、意見を聞く</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Can I run this idea by you before I present it?</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>発表する前にこのアイデアについてご意見をいただけますか。</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>Let me run it by my manager first.</t>
+        </is>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>まず上司に確認させてください。</t>
+        </is>
+      </c>
+      <c r="M1064" t="inlineStr">
+        <is>
+          <t>bounce it off someone,get someone's take on it</t>
+        </is>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1064" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1064" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1064" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>EX-1064</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>table this discussion</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>この議論を一旦保留にする、先送りにする</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Given the time, let's table this discussion until next week.</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>時間の都合上、この議論は来週まで保留にしましょう。</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>The committee decided to table the proposal for further review.</t>
+        </is>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>委員会はさらなる検討のためその提案を保留することにした。</t>
+        </is>
+      </c>
+      <c r="M1065" t="inlineStr">
+        <is>
+          <t>put this on hold,shelve this topic</t>
+        </is>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1065" t="inlineStr">
+        <is>
+          <t>米では「保留」の意味だが、英では逆に「今すぐ議論する」という意味になることがあるため注意。</t>
+        </is>
+      </c>
+      <c r="P1065" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1065" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1065" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>EX-1065</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>put someone on the spot</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>誰かを不意に困らせるような質問・状況に置く</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>I didn't mean to put you on the spot with that question.</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>あの質問であなたを困らせるつもりはありませんでした。</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>She was put on the spot during the Q&amp;A session.</t>
+        </is>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>彼女は質疑応答の時間に不意に答えを求められた。</t>
+        </is>
+      </c>
+      <c r="M1066" t="inlineStr">
+        <is>
+          <t>catch someone off guard</t>
+        </is>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1066" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1066" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1066" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>EX-1066</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>交渉,会議</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>確認,提案</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>iron out the details</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>細かい点を詰める、調整して解決する</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>We still need to iron out a few details before signing the contract.</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>契約書に署名する前にまだいくつかの細部を詰める必要があります。</t>
+        </is>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>Let's schedule a call to iron out the remaining issues.</t>
+        </is>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>残った問題を解決するために電話会議を設定しましょう。</t>
+        </is>
+      </c>
+      <c r="M1067" t="inlineStr">
+        <is>
+          <t>work out the kinks,hammer out the details</t>
+        </is>
+      </c>
+      <c r="N1067" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1067" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1067" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1067" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>EX-1067</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>get the ball rolling</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>物事を始動させる、着手する</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Let's get the ball rolling on the new marketing campaign.</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>新しいマーケティングキャンペーンに着手しましょう。</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>I'll get the ball rolling by sending out the first draft.</t>
+        </is>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>まず最初の草案を送ることから始めます。</t>
+        </is>
+      </c>
+      <c r="M1068" t="inlineStr">
+        <is>
+          <t>kick things off,get things started</t>
+        </is>
+      </c>
+      <c r="N1068" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1068" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1068" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1068" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>EX-1068</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>メール,会議,電話</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>確認,相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>keep someone in the loop</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>誰かに情報を共有し続ける、最新情報を伝える</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Please keep me in the loop on any updates regarding the client.</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>クライアントに関する最新情報があれば、随時共有してください。</t>
+        </is>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>I'll keep the whole team in the loop about the schedule changes.</t>
+        </is>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>スケジュール変更についてはチーム全体に共有します。</t>
+        </is>
+      </c>
+      <c r="M1069" t="inlineStr">
+        <is>
+          <t>keep someone posted,keep someone updated</t>
+        </is>
+      </c>
+      <c r="N1069" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1069" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1069" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1069" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>EX-1069</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>会議,交渉</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>反論・懸念</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>push back on something</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>何かに対して異議を唱える、反対する</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>The finance team pushed back on the proposed budget increase.</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>経理チームは提案された予算増額に異議を唱えた。</t>
+        </is>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>I want to push back on the idea of delaying the launch.</t>
+        </is>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>発売延期という案には反対したいと思います。</t>
+        </is>
+      </c>
+      <c r="M1070" t="inlineStr">
+        <is>
+          <t>object to,raise concerns about</t>
+        </is>
+      </c>
+      <c r="N1070" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1070" t="inlineStr">
+        <is>
+          <t>直接的な反論よりやや柔らかい印象を与える表現。</t>
+        </is>
+      </c>
+      <c r="P1070" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1070" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1070" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>EX-1070</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>sweeten the deal</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>取引条件をより魅力的にする、好条件を付け加える</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>To close the deal, they offered to sweeten it with a discount.</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>契約をまとめるため、彼らは割引を付けて条件を良くすることを申し出た。</t>
+        </is>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>Can we sweeten the deal by including free shipping?</t>
+        </is>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>送料無料を含めることで取引条件を良くできますか。</t>
+        </is>
+      </c>
+      <c r="M1071" t="inlineStr">
+        <is>
+          <t>add an incentive,make it more attractive</t>
+        </is>
+      </c>
+      <c r="N1071" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1071" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1071" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1071" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1071"/>
+  <dimension ref="A1:S1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -82562,6 +82562,855 @@
         </is>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>EX-1091</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr"/>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>Let's stick to the agenda and address that separately.</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>話が脱線しそうなときに、議題に沿って進めようと穏やかに提案する表現。</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Let's stick to the agenda and address that separately.</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>その件は議題に沿って、別途対応しましょう。</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>I appreciate the input, but let's stick to the agenda for now.</t>
+        </is>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>ご意見はありがたいのですが、いったん議題に沿って進めましょう。</t>
+        </is>
+      </c>
+      <c r="M1072" t="inlineStr">
+        <is>
+          <t>Let's stay on topic,Let's keep this on track</t>
+        </is>
+      </c>
+      <c r="N1072" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1072" t="inlineStr">
+        <is>
+          <t>会議の脱線を穏やかに軌道修正する際によく使われる。</t>
+        </is>
+      </c>
+      <c r="P1072" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1072" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1072" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>EX-1092</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>It's a pleasure to finally meet you in person.</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>これまでメールやオンラインでやり取りしていた相手と、実際に対面できた際の挨拶表現。</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>It's a pleasure to finally meet you in person.</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>ようやく直接お会いできて光栄です。</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>It's a pleasure to finally meet you in person after all our email exchanges.</t>
+        </is>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>メールでのやり取りを重ねてきましたが、ようやく直接お会いできて嬉しいです。</t>
+        </is>
+      </c>
+      <c r="M1073" t="inlineStr">
+        <is>
+          <t>Great to finally put a face to the name</t>
+        </is>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1073" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1073" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1073" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>EX-1093</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>依頼,確認</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>フォーマル</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>I'm reaching out to request a status update on the invoice.</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>請求書などの進捗状況を確認したい旨をメールで丁寧に伝える表現。</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>I'm reaching out to request a status update on the invoice we sent last week.</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>先週お送りした請求書について、進捗状況を確認させてください。</t>
+        </is>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>I'm reaching out to request a status update on the shipment.</t>
+        </is>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>出荷状況について確認のためご連絡差し上げております。</t>
+        </is>
+      </c>
+      <c r="M1074" t="inlineStr">
+        <is>
+          <t>I'm writing to check on the status of...</t>
+        </is>
+      </c>
+      <c r="N1074" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1074" t="inlineStr">
+        <is>
+          <t>「reaching out」はビジネスメールでカジュアルすぎず柔らかい印象を与える言い回し。</t>
+        </is>
+      </c>
+      <c r="P1074" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1074" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1074" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>EX-1094</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr"/>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>Let me pass you along to someone who can help.</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>電話対応で、担当者に取り次ぐ際に使う表現。</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Let me pass you along to someone who can help with that.</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>その件について対応できる者にお繋ぎします。</t>
+        </is>
+      </c>
+      <c r="M1075" t="inlineStr">
+        <is>
+          <t>Let me transfer you,Let me put you through</t>
+        </is>
+      </c>
+      <c r="N1075" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1075" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1075" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1075" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>EX-1095</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>依頼・断り,電話</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>I'll have to check my calendar before I can commit to that.</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>即答を避け、予定を確認してから返事をしたいときに使う表現。</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>I'll have to check my calendar before I can commit to that.</t>
+        </is>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>それについては予定を確認してからでないとお約束できません。</t>
+        </is>
+      </c>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>I'll have to check my calendar before I can commit to another trip this month.</t>
+        </is>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>今月もう一度出張できるかは、予定を確認してからでないとお約束できません。</t>
+        </is>
+      </c>
+      <c r="M1076" t="inlineStr">
+        <is>
+          <t>Let me get back to you on that</t>
+        </is>
+      </c>
+      <c r="N1076" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1076" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1076" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1076" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>EX-1096</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>We're prepared to offer a discount if you sign a longer-term contract.</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>長期契約を条件に値引きを提示する際の交渉表現。</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>We're prepared to offer a discount if you sign a longer-term contract.</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>長期契約にご同意いただければ、割引をご提供する用意がございます。</t>
+        </is>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>We're prepared to offer a discount if you commit to a minimum order quantity.</t>
+        </is>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>最低発注数量をお約束いただければ、割引をご提供する用意がございます。</t>
+        </is>
+      </c>
+      <c r="M1077" t="inlineStr">
+        <is>
+          <t>We can offer better terms for a longer commitment</t>
+        </is>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1077" t="inlineStr">
+        <is>
+          <t>交渉で譲歩を切り出す際の定番表現。条件を明示することで説得力が増す。</t>
+        </is>
+      </c>
+      <c r="P1077" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1077" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1077" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>EX-1097</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>会議,プレゼン</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>Would you mind sharing your screen so we can all follow along?</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>オンライン会議で、画面共有を丁寧に依頼する表現。</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Would you mind sharing your screen so we can all follow along?</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>皆で確認できるよう、画面を共有していただけますか。</t>
+        </is>
+      </c>
+      <c r="M1078" t="inlineStr">
+        <is>
+          <t>Could you share your screen?,Can you pull that up on screen?</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1078" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1078" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1078" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>EX-1098</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>メール,電話</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>Just to confirm, are we still on for tomorrow at 10?</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>予定が変わっていないかを軽く確認する表現。</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Just to confirm, are we still on for tomorrow at 10?</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>念のための確認ですが、明日10時の予定に変更はありませんか。</t>
+        </is>
+      </c>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Just to confirm, are we still on for the call this afternoon?</t>
+        </is>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>念のための確認ですが、今日の午後の電話会議の予定に変更はありませんか。</t>
+        </is>
+      </c>
+      <c r="M1079" t="inlineStr">
+        <is>
+          <t>Just checking, is our meeting still on?</t>
+        </is>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1079" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1079" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1079" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>EX-1099</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>That sounds like quite an adventure!</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>相手の話（旅行や出来事など）に興味や驚きを示す相槌表現。</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>That sounds like quite an adventure! How did you even find that place?</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>それはすごい冒険だったね！どうやってその場所を見つけたの？</t>
+        </is>
+      </c>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>That sounds like quite an adventure — I'm a little jealous.</t>
+        </is>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>すごい体験だったんだね、ちょっと羨ましいよ。</t>
+        </is>
+      </c>
+      <c r="M1080" t="inlineStr">
+        <is>
+          <t>Wow, that's wild!</t>
+        </is>
+      </c>
+      <c r="N1080" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1080" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1080" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1080" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>EX-1100</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr"/>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>Let's dive into the numbers behind this recommendation.</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>プレゼンで、提案の根拠となる数値の説明に入る際の導入表現。</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Let's dive into the numbers behind this recommendation.</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>それでは、この提案の根拠となる数値を見ていきましょう。</t>
+        </is>
+      </c>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>Let's dive into the numbers behind this recommendation before we discuss next steps.</t>
+        </is>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>次のステップについて話す前に、この提案を裏付ける数値を確認しましょう。</t>
+        </is>
+      </c>
+      <c r="M1081" t="inlineStr">
+        <is>
+          <t>Let's take a closer look at the data</t>
+        </is>
+      </c>
+      <c r="N1081" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1081" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1081" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1081" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expressions_list.xlsx
+++ b/expressions_list.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1081"/>
+  <dimension ref="A1:S1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -82578,7 +82578,6 @@
           <t>会議</t>
         </is>
       </c>
-      <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr">
         <is>
           <t>ミドル</t>
@@ -82666,7 +82665,6 @@
           <t>雑談</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr">
         <is>
           <t>ミドル,フォーマル</t>
@@ -82841,7 +82839,6 @@
           <t>電話</t>
         </is>
       </c>
-      <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr">
         <is>
           <t>ミドル</t>
@@ -83344,7 +83341,6 @@
           <t>プレゼン</t>
         </is>
       </c>
-      <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr">
         <is>
           <t>ミドル,フォーマル</t>
@@ -83408,6 +83404,8671 @@
       <c r="S1081" t="inlineStr">
         <is>
           <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>EX-1101</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>Do you have this in a different color?</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>これの違う色はありますか、という色違いを尋ねる買い物の定番表現。</t>
+        </is>
+      </c>
+      <c r="P1082" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1082" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1082" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>EX-1102</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>Can I get a receipt, please?</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>レシートをもらえますか、という会計時にレシートを求める表現。</t>
+        </is>
+      </c>
+      <c r="P1083" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1083" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1083" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>EX-1103</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>Do you accept credit cards?</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>クレジットカードは使えますか、という支払い方法を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1084" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1084" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1084" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>EX-1104</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>Is this item on sale?</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>これはセール品ですか、という値引きの有無を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1085" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1085" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1085" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>EX-1105</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>Where can I find the fitting room?</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>試着室はどこですか、という店内で場所を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1086" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1086" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1086" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>EX-1106</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>I'll take this one.</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>これをください、という購入を決めた時の表現。</t>
+        </is>
+      </c>
+      <c r="P1087" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1087" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1087" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>EX-1107</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>Can I return this if it doesn't fit?</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>サイズが合わなかったら返品できますか、という返品可否を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1088" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1088" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1088" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>EX-1108</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>Do you have this in stock?</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>これの在庫はありますか、という在庫確認の表現。</t>
+        </is>
+      </c>
+      <c r="P1089" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1089" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1089" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>EX-1109</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>Could you gift-wrap this, please?</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>これをギフト包装してもらえますか、という贈り物の包装を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1090" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1090" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1090" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>EX-1110</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>I'm looking for a birthday present.</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>誕生日プレゼントを探しています、という買い物の目的を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1091" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1091" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1091" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>EX-1111</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>Can you give me a discount?</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>値引きしてもらえますか、という値引き交渉の表現。</t>
+        </is>
+      </c>
+      <c r="P1092" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1092" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1092" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>EX-1112</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>Where is the nearest cash register?</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>一番近いレジはどこですか、というレジの場所を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1093" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1093" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1093" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>EX-1113</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>Do you have a smaller size?</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>もっと小さいサイズはありますか、というサイズ違いを求める表現。</t>
+        </is>
+      </c>
+      <c r="P1094" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1094" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1094" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>EX-1114</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>Can I pay by installments?</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>分割払いはできますか、という支払い方法を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1095" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1095" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1095" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>EX-1115</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>I'd like to exchange this.</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>これを交換したいです、という交換を申し出る表現。</t>
+        </is>
+      </c>
+      <c r="P1096" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1096" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1096" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>EX-1116</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>Table for two, please.</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>2名でお願いします、という入店時に人数を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1097" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1097" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1097" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>EX-1117</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>Can I see the menu, please?</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>メニューを見せてもらえますか、という着席後にメニューを求める表現。</t>
+        </is>
+      </c>
+      <c r="P1098" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1098" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1098" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>EX-1118</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>What's today's special?</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>今日のおすすめは何ですか、という日替わりメニューを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1099" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1099" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1099" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>EX-1119</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>Could I get some water, please?</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>お水をいただけますか、という水を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1100" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1100" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1100" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>EX-1120</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>Is this dish spicy?</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>この料理は辛いですか、という辛さを確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1101" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1101" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1101" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>EX-1121</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>Can we split the bill?</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>会計は割り勘にできますか、という支払いを分けたい時の表現。</t>
+        </is>
+      </c>
+      <c r="P1102" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1102" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1102" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>EX-1122</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>Do you have any vegetarian options?</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>ベジタリアン向けのメニューはありますか、という食事制限を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1103" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1103" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1103" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>EX-1123</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>Could I get a to-go box?</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>持ち帰り用の容器をもらえますか、という食べ残しの持ち帰りを頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1104" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1104" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>EX-1124</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>Excuse me, could we order now?</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>すみません、注文してもいいですか、という店員を呼ぶ表現。</t>
+        </is>
+      </c>
+      <c r="P1105" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1105" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1105" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>EX-1125</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>This was delicious.</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>とても美味しかったです、という食事の感想を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1106" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1106" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1106" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>EX-1126</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>Could we sit by the window?</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>窓際の席にしてもらえますか、という席の希望を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1107" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1107" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1107" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>EX-1127</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>How long is the wait?</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>どのくらい待ちますか、という順番待ちの時間を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1108" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1108" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1108" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>EX-1128</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>Do you have a reservation under Tanaka?</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>タナカの名前で予約していますが、という予約を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1109" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1109" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1109" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>EX-1129</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>Could you recommend a wine that goes with this?</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>これに合うワインを教えてもらえますか、という料理に合う飲み物を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1110" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1110" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1110" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>EX-1130</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>Is service charge included?</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>サービス料は含まれていますか、という会計内容を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1111" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1111" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1111" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>EX-1131</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>Which platform does this train leave from?</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>この電車は何番線から出ますか、という電車のホームを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1112" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1112" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1112" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>EX-1132</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>How do I get to the airport from here?</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>ここから空港までどう行けばいいですか、という行き方を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1113" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1113" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1113" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>EX-1133</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>Is there an ATM nearby?</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>近くにATMはありますか、という両替・引き出し場所を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1114" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1114" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1114" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>EX-1134</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>Do you have a map of the area?</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>この辺りの地図はありますか、という観光案内所などでの表現。</t>
+        </is>
+      </c>
+      <c r="P1115" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1115" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1115" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>EX-1135</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>What time does the last train leave?</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>最終電車は何時ですか、という終電時刻を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1116" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1116" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1116" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>EX-1136</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Can I store my luggage here?</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>ここに荷物を預けられますか、という荷物預かりを頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1117" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1117" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1117" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>EX-1137</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>Is breakfast included in the room rate?</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>朝食は宿泊料金に含まれていますか、というホテルでの確認表現。</t>
+        </is>
+      </c>
+      <c r="P1118" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1118" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1118" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>EX-1138</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>Could I have a wake-up call at 7?</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>7時にモーニングコールをお願いできますか、というホテルでの依頼表現。</t>
+        </is>
+      </c>
+      <c r="P1119" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1119" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1119" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>EX-1139</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>What's the WiFi password?</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>WiFiのパスワードは何ですか、という宿泊先や店での定番表現。</t>
+        </is>
+      </c>
+      <c r="P1120" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1120" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1120" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>EX-1140</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>How much is a ticket to the museum?</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>美術館のチケットはいくらですか、という入場料を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1121" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1121" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1121" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>EX-1141</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>Is there a discount for students?</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>学生割引はありますか、という割引の有無を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1122" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1122" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1122" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>EX-1142</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>I think I left my bag on the train.</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>電車にバッグを忘れたと思います、という忘れ物を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1123" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1123" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1123" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>EX-1143</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>Could you recommend a good local restaurant?</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>地元のおすすめのレストランを教えてもらえますか、という現地のお店を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1124" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1124" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1124" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>EX-1144</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>What currency do you accept here?</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>ここではどの通貨が使えますか、という通貨を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1125" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1125" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1125" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>EX-1145</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>Is this the right bus to the city center?</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>これは中心部行きのバスで合っていますか、というバスの行き先を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1126" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1126" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1126" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>EX-1146</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>Want to grab a coffee sometime?</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>今度コーヒーでもどう、という軽く誘う表現。</t>
+        </is>
+      </c>
+      <c r="P1127" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1127" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1127" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>EX-1147</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>Long time no see!</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>久しぶり！という久々に会った時の定番表現。</t>
+        </is>
+      </c>
+      <c r="P1128" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1128" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1128" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>EX-1148</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>What have you been up to lately?</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>最近どうしてた、という近況を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1129" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1129" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1129" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>EX-1149</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>I had a really great time today.</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>今日は本当に楽しかった、という別れ際の感想表現。</t>
+        </is>
+      </c>
+      <c r="P1130" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1130" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1130" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>EX-1150</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>Congratulations!</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>おめでとう！というお祝いを伝える定番表現。</t>
+        </is>
+      </c>
+      <c r="P1131" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1131" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>EX-1151</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>Let's do this again sometime.</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>また今度やろうね、という次の機会を約束する表現。</t>
+        </is>
+      </c>
+      <c r="P1132" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1132" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1132" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>EX-1152</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>I'm so glad we met.</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>会えて本当によかった、という気持ちを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1133" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1133" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1133" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>EX-1153</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>Do you want to come to my place this weekend?</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>今週末、うちに来ない、という自宅に招く表現。</t>
+        </is>
+      </c>
+      <c r="P1134" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1134" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1134" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>EX-1154</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>I'll text you the details later.</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>詳細は後でメッセージするね、という連絡を約束する表現。</t>
+        </is>
+      </c>
+      <c r="P1135" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1135" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1135" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>EX-1155</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>That's so kind of you.</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>それは優しいね、という相手の気遣いへの感謝表現。</t>
+        </is>
+      </c>
+      <c r="P1136" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1136" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1136" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>EX-1156</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>Sorry I'm running a bit late.</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>ちょっと遅れそう、ごめん、という遅刻を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1137" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1137" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1137" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>EX-1157</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>I really needed to hear that, thanks.</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>それを聞けてよかった、ありがとう、という励まされた時の表現。</t>
+        </is>
+      </c>
+      <c r="P1138" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1138" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1138" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>EX-1158</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>What do you do for fun?</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>趣味は何、という相手の趣味を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1139" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1139" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1139" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>EX-1159</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>Let me know if you're ever free.</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>暇な時があれば教えて、という予定を合わせたい時の表現。</t>
+        </is>
+      </c>
+      <c r="P1140" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1140" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1140" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>EX-1160</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>It was nice catching up with you.</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>近況を話せてよかった、という久々の再会の別れ際の表現。</t>
+        </is>
+      </c>
+      <c r="P1141" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1141" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1141" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>EX-1161</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>I have a fever.</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>熱があります、という発熱を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1142" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1142" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1142" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>EX-1162</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>My stomach hurts.</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>お腹が痛いです、という腹痛を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1143" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1143" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1143" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>EX-1163</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>I have a sore throat.</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>喉が痛いです、という喉の不調を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1144" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1144" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1144" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>EX-1164</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>I twisted my ankle.</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>足首をひねりました、というけがを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1145" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1145" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1145" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>EX-1165</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>Could I get some medicine for a cold?</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>風邪薬をもらえますか、という薬局での定番表現。</t>
+        </is>
+      </c>
+      <c r="P1146" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1146" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1146" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>EX-1166</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>Where's the nearest pharmacy?</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>一番近い薬局はどこですか、という薬局の場所を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1147" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1147" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1147" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>EX-1167</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>I need to see a doctor.</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>医者に診てもらう必要があります、という受診の必要性を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1148" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1148" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1148" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>EX-1168</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>I'm feeling much better now.</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>だいぶよくなりました、という回復を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1149" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1149" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1149" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>EX-1169</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>Can I take the day off?</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>今日は休んでもいいですか、という体調不良での休みを願い出る表現。</t>
+        </is>
+      </c>
+      <c r="P1150" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1150" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1150" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>EX-1170</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Do you have anything for a headache?</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>頭痛に効くものはありますか、という薬局での症状相談表現。</t>
+        </is>
+      </c>
+      <c r="P1151" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1151" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1151" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>EX-1171</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>I feel a bit dizzy.</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>少しめまいがします、というめまいを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1152" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1152" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1152" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>EX-1172</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>I've had this cough for a few days.</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>数日前からこの咳が続いています、という症状の経過を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1153" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1153" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1153" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>EX-1173</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>Should I go to the hospital?</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>病院に行った方がいいですか、という受診の必要性を相談する表現。</t>
+        </is>
+      </c>
+      <c r="P1154" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1154" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1154" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>EX-1174</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>I'm allergic to this medicine.</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>この薬にはアレルギーがあります、という薬のアレルギーを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1155" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1155" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1155" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>EX-1175</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>Get well soon.</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>早く良くなってね、という体調不良の相手を気遣う表現。</t>
+        </is>
+      </c>
+      <c r="P1156" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1156" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1156" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>EX-1176</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>Could you show me a few more options in this style?</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>このスタイルの他の選択肢も見せてもらえますか、という追加の提案を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1157" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1157" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1157" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>EX-1177</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>I'm trying to find something similar to this, but a bit cheaper.</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>これに似ていて、もう少し安いものを探しています、という予算を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1158" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1158" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1158" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>EX-1178</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>Would it be possible to hold this for me until tomorrow?</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>これを明日まで取り置きしてもらえますか、という取り置きを依頼する表現。</t>
+        </is>
+      </c>
+      <c r="P1159" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1159" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1159" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>EX-1179</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>I bought this last week, but it turned out to be defective.</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>先週これを買ったのですが、不良品でした、という不具合を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1160" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1160" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1160" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>EX-1180</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>What's the difference between these two models?</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>この2つのモデルの違いは何ですか、という商品比較を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1161" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1161" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1161" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>EX-1181</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>I'd like to check the return policy before I decide.</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>決める前に返品規定を確認したいです、という購入前の確認表現。</t>
+        </is>
+      </c>
+      <c r="P1162" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1162" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1162" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>EX-1182</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>Is there a warranty on electronics like this?</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>こういった電化製品には保証がありますか、という保証の有無を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1163" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1163" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1163" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>EX-1183</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>I'm not quite sure which one would suit me better.</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>どちらが自分に合うか、まだよくわかりません、と迷いを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1164" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1164" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1164" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>EX-1184</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Could you help me find something within this budget?</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>この予算内で何か探すのを手伝ってもらえますか、という予算内での提案を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1165" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1165" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1165" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>EX-1185</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>I'll need to think about it a bit more before deciding.</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>決める前にもう少し考えたいです、という即決を避ける表現。</t>
+        </is>
+      </c>
+      <c r="P1166" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1166" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1166" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>EX-1186</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>Do you offer free shipping if I order online instead?</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>オンライン注文なら送料無料になりますか、というオンライン購入の条件を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1167" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1167" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1167" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>EX-1187</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>This isn't quite what I had in mind, actually.</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>実はイメージしていたものとは少し違います、という遠回しな不満表現。</t>
+        </is>
+      </c>
+      <c r="P1168" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1168" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1168" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>EX-1188</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>Could you set this aside while I look around a bit more?</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>もう少し見て回る間、これを取っておいてもらえますか、という一時保留を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1169" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1169" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1169" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>EX-1189</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>I'd like to speak with a manager about this issue.</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>この件について責任者と話したいです、という上位者対応を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1170" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1170" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1170" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>EX-1190</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>Is there a loyalty program I could sign up for?</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>登録できる会員特典プログラムはありますか、というポイント制度を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1171" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1171" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1171" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>EX-1191</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>Could you tell me which dishes are the most popular here?</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>ここで一番人気の料理を教えてもらえますか、という人気メニューを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1172" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1172" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1172" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>EX-1192</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>We're celebrating a birthday tonight, is there anything special you could do?</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>今夜は誕生日のお祝いなのですが、何か特別なことをしてもらえますか、という特別対応を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1173" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1173" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1173" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>EX-1193</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>Would it be possible to modify this dish slightly?</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>この料理を少しアレンジしてもらうことは可能ですか、というカスタマイズを頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1174" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1174" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1174" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>EX-1194</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>I'd like to make a reservation for six people this Friday.</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>今週金曜日に6名で予約を取りたいです、という予約表現。</t>
+        </is>
+      </c>
+      <c r="P1175" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1175" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1175" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>EX-1195</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>Could we get a bit more time before ordering?</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>注文の前にもう少し時間をもらえますか、という注文を先延ばしする表現。</t>
+        </is>
+      </c>
+      <c r="P1176" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1176" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1176" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>EX-1196</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>This isn't quite what I ordered, I think there's been a mix-up.</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>これは注文したものと違うようです、という注文ミスを伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1177" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1177" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>EX-1197</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>Is it possible to combine these two set meals?</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>この2つのセットを組み合わせることはできますか、というメニューの組み合わせを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1178" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1178" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1178" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>EX-1198</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>Could you bring the check whenever you get a chance?</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>手が空いたときにお会計をお願いできますか、という急かさずに会計を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1179" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1179" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1179" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>EX-1199</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>We're in a bit of a hurry, could we order quickly?</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>少し急いでいるので、すぐ注文してもいいですか、という時間の制約を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1180" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1180" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>EX-1200</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>I'd love to try something you'd personally recommend.</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>あなたが個人的におすすめするものを試してみたいです、という店員個人のおすすめを求める表現。</t>
+        </is>
+      </c>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1181" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1181" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>EX-1201</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>Could I get this without onions, if that's possible?</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>できれば玉ねぎ抜きでお願いできますか、という食材を抜く依頼表現。</t>
+        </is>
+      </c>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1182" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1182" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>EX-1202</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>The food was amazing, please pass that along to the chef.</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>料理が素晴らしかったので、シェフにお伝えください、という感謝を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1183" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1183" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>EX-1203</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>Would it be okay if we stayed a little longer?</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>もう少し長くいても大丈夫ですか、という滞在延長を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1184" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1184" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>EX-1204</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>Is there a corkage fee if we bring our own wine?</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>持ち込みのワインにはコルク料金がかかりますか、という持ち込み料を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1185" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1185" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1185" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>EX-1205</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>外食</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>Could you box up the rest for us to take home?</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>残りを持ち帰り用に詰めてもらえますか、という持ち帰りを頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1186" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1186" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1186" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>EX-1206</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>Could you recommend a route that avoids the crowds?</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>混雑を避けられるルートを教えてもらえますか、という混雑回避のルートを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1187" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1187" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>EX-1207</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>I'd like to change my reservation to an earlier flight if possible.</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>できれば予約をもっと早い便に変更したいです、というフライト変更を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1188" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1188" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1188" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>EX-1208</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>Is it worth booking tickets in advance, or can we just walk in?</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>事前予約する価値はありますか、それとも当日でも大丈夫ですか、という予約の要否を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1189" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1189" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>EX-1209</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>We're trying to decide between these two areas to stay in.</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>宿泊するエリアをこの2つで迷っています、と相談を持ちかける表現。</t>
+        </is>
+      </c>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1190" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1190" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>EX-1210</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>Could you point us toward somewhere less touristy?</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>あまり観光地化されていない場所を教えてもらえますか、という穴場を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1191" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1191" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1191" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>EX-1211</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>I think I might have taken the wrong exit at the station.</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>駅で違う出口を出てしまったかもしれません、という道に迷った状況を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1192" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1192" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1192" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>EX-1212</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>Is there a way to get a refund if the tour gets cancelled?</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>ツアーが中止になった場合、返金してもらえますか、というキャンセル時の対応を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1193" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1193" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1193" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>EX-1213</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>We'd like to extend our stay by one more night, if there's availability.</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>空きがあればもう1泊延長したいです、という宿泊延長を頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1194" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1194" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>EX-1214</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>Could you help us figure out the best way to get around the city?</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>街を移動する一番良い方法を教えてもらえますか、という移動手段の相談表現。</t>
+        </is>
+      </c>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1195" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1195" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>EX-1215</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>I'm a bit worried we won't make our connecting flight.</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>乗り継ぎ便に間に合わないのではと少し心配です、という乗り継ぎの不安を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1196" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1196" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>EX-1216</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>Is travel insurance something you'd recommend for this trip?</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>この旅行には旅行保険をおすすめしますか、という保険加入の相談表現。</t>
+        </is>
+      </c>
+      <c r="P1197" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1197" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1197" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>EX-1217</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>We'd like to arrange an early check-out tomorrow.</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>明日は早めのチェックアウトを手配したいです、という早期チェックアウトを頼む表現。</t>
+        </is>
+      </c>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1198" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1198" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>EX-1218</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>Could you suggest something off the beaten path?</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>定番ではない場所を提案してもらえますか、という穴場スポットを尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1199" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1199" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>EX-1219</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>I left my passport at the hotel, is there anything I can do?</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>パスポートをホテルに置き忘れてしまいました、何かできることはありますか、という忘れ物の相談表現。</t>
+        </is>
+      </c>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1200" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1200" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>EX-1220</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>Would it be possible to store our luggage after check-out?</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>チェックアウト後に荷物を預けることはできますか、という荷物預かりの依頼表現。</t>
+        </is>
+      </c>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1201" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1201" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>EX-1221</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>I've been meaning to reach out, sorry it's been so long.</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>連絡しようと思っていました、ご無沙汰してすみません、という久々の連絡を詫びる表現。</t>
+        </is>
+      </c>
+      <c r="P1202" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1202" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1202" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>EX-1222</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>Would you be up for trying that new place downtown sometime?</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>今度街の新しいお店に行ってみない、という誘いの表現。</t>
+        </is>
+      </c>
+      <c r="P1203" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1203" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1203" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>EX-1223</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>I really appreciate you being there for me lately.</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>最近そばにいてくれて本当に感謝しています、という感謝を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1204" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1204" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>EX-1224</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>Honestly, I could use some advice if you have a minute.</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>正直、時間があればアドバイスが欲しいです、と率直に相談を持ちかける表現。</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1205" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1205" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>EX-1225</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>I heard you've been going through a rough patch, how are you holding up?</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>大変な時期だと聞いたけど、大丈夫、という相手を気遣う表現。</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1206" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1206" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>EX-1226</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>Let's not let so much time pass before we hang out again.</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>次に会うまであまり間を空けないようにしよう、という次回の約束を促す表現。</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1207" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1207" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>EX-1227</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>I hope it's not too forward, but could I ask you something personal?</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>出過ぎたことでなければいいけど、個人的なことを聞いてもいい、という踏み込んだ質問の前置き表現。</t>
+        </is>
+      </c>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1208" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1208" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>EX-1228</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>It means a lot that you remembered.</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>覚えていてくれて本当に嬉しい、という感謝を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1209" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1209" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>EX-1229</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>I feel like we haven't had a real conversation in ages.</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>しばらくちゃんと話せていない気がする、という会話不足を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1210" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1210" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>EX-1230</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>Would you mind if I brought a plus-one to the party?</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>パーティーに一人連れて行ってもいい、という同伴者の許可を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1211" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1211" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>EX-1231</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>I owe you one for helping me out the other day.</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>この前助けてくれた借りがあるね、という感謝と恩義を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1212" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1212" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1212" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>EX-1232</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>Let's plan something for once, instead of just talking about it.</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>話すだけじゃなくて、たまには実際に予定を立てよう、という行動を促す表現。</t>
+        </is>
+      </c>
+      <c r="P1213" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1213" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1213" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>EX-1233</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>I've been meaning to introduce you to a friend of mine.</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>前から友達を紹介したいと思っていた、という紹介を申し出る表現。</t>
+        </is>
+      </c>
+      <c r="P1214" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1214" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1214" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>EX-1234</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>Sorry for venting, I just needed to get that off my chest.</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>愚痴っちゃってごめん、ただ吐き出したかっただけ、という愚痴を詫びる表現。</t>
+        </is>
+      </c>
+      <c r="P1215" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1215" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1215" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>EX-1235</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>友人</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>Let's make sure we actually follow through this time.</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>今度こそちゃんと実行しよう、という有言実行を促す表現。</t>
+        </is>
+      </c>
+      <c r="P1216" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1216" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1216" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>EX-1236</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>I've been feeling a bit off for the past couple of days.</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>ここ数日、少し体調がすぐれません、という不調の継続を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1217" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1217" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1217" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>EX-1237</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>The medicine doesn't seem to be working as well as before.</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>薬が以前ほど効いていないようです、という薬の効き目の変化を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1218" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1218" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1218" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>EX-1238</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>Is there anything I should avoid eating while taking this?</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>この薬を飲んでいる間、避けるべき食べ物はありますか、という食事制限を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1219" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1219" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1219" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>EX-1239</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>I'm worried this might be more than just a cold.</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>これはただの風邪以上のものかもしれないと心配しています、という不安を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1220" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1220" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1220" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>EX-1240</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>Could you recommend a specialist for this kind of issue?</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>こういった症状に詳しい専門医を紹介してもらえますか、という専門医の紹介を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1221" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1221" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1221" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>EX-1241</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>I've been having trouble sleeping because of the pain.</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>痛みのせいで眠れずにいます、という不眠の原因を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1222" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1222" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1222" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>EX-1242</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>Is it normal to feel this tired after the treatment?</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>治療後にこんなに疲れを感じるのは普通ですか、という治療後の症状を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1223" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1223" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1223" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>EX-1243</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>I'd like to get a second opinion, if that's okay.</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>できればセカンドオピニオンをもらいたいです、という他の医師の意見を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1224" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1224" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1224" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>EX-1244</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>The symptoms seem to come and go throughout the day.</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>症状は一日を通して出たり消えたりするようです、という症状の変動を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1225" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1225" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1225" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>EX-1245</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>Could you explain what these test results actually mean?</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>この検査結果が実際どういう意味か説明してもらえますか、という検査結果の説明を求める表現。</t>
+        </is>
+      </c>
+      <c r="P1226" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1226" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1226" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>EX-1246</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>I think I might need to take a few days off to recover.</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>回復のために数日休む必要があるかもしれません、という休養の必要性を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1227" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1227" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1227" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>EX-1247</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>Is this condition something that runs in families?</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>この症状は遺伝的なものですか、という家族性の有無を尋ねる表現。</t>
+        </is>
+      </c>
+      <c r="P1228" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1228" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1228" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>EX-1248</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>I've cut back on caffeine, but I'm still not sleeping well.</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>カフェインを控えたのに、まだよく眠れません、という改善しない状況を伝える表現。</t>
+        </is>
+      </c>
+      <c r="P1229" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1229" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1229" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>EX-1249</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>Would physical therapy help with this kind of injury?</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>このようなけがには理学療法が効果的ですか、という治療法の相談表現。</t>
+        </is>
+      </c>
+      <c r="P1230" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1230" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1230" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>EX-1250</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>体調</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>カジュアル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>I just want to make sure I'm not overreacting about this.</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>大げさに考えすぎていないか確認したいだけです、という心配の妥当性を確認する表現。</t>
+        </is>
+      </c>
+      <c r="P1231" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1231" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1231" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>EX-1251</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>Let's park that for now</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>その話題は一旦保留にして、後で扱おうという表現</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>Let's park that for now and come back to it after lunch.</t>
+        </is>
+      </c>
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>その件は一旦保留にして、昼食後にまた話しましょう。</t>
+        </is>
+      </c>
+      <c r="K1232" t="inlineStr">
+        <is>
+          <t>I think we should park this issue until we have more data.</t>
+        </is>
+      </c>
+      <c r="L1232" t="inlineStr">
+        <is>
+          <t>もっとデータが揃うまで、この問題は保留にすべきだと思います。</t>
+        </is>
+      </c>
+      <c r="M1232" t="inlineStr">
+        <is>
+          <t>put this on hold,table this for later</t>
+        </is>
+      </c>
+      <c r="N1232" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1232" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1232" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1232" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>EX-1252</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>ミドル,カジュアル</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>I'll loop you in on this</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>情報を共有してもらうために、相手をやり取りに加える・巻き込むという意味</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>I'll loop you in on this so you're up to speed.</t>
+        </is>
+      </c>
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>状況を把握できるよう、あなたもやり取りに加えますね。</t>
+        </is>
+      </c>
+      <c r="M1233" t="inlineStr">
+        <is>
+          <t>keep someone in the loop,cc someone on this</t>
+        </is>
+      </c>
+      <c r="N1233" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1233" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1233" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1233" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>EX-1253</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>会議,依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>Can we push this to next week?</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>予定や締め切りを来週に延期できないか尋ねる表現</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>Can we push this to next week? I need more time to prepare.</t>
+        </is>
+      </c>
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>これを来週に延期できますか？準備にもう少し時間が必要です。</t>
+        </is>
+      </c>
+      <c r="K1234" t="inlineStr">
+        <is>
+          <t>Would it be possible to push the deadline to next week?</t>
+        </is>
+      </c>
+      <c r="L1234" t="inlineStr">
+        <is>
+          <t>締め切りを来週に延ばすことは可能でしょうか？</t>
+        </is>
+      </c>
+      <c r="M1234" t="inlineStr">
+        <is>
+          <t>postpone this to next week,move this back a week</t>
+        </is>
+      </c>
+      <c r="N1234" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1234" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1234" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1234" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>EX-1254</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>雑談</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>相槌・共感</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>カジュアル</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>That's music to my ears</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>嬉しい知らせを聞いて「それは嬉しい話だ」と喜びを表す表現</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>You got the budget approved? That's music to my ears!</t>
+        </is>
+      </c>
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>予算が承認されたの？それは嬉しい知らせだね！</t>
+        </is>
+      </c>
+      <c r="K1235" t="inlineStr">
+        <is>
+          <t>Sales are up 20%? That's music to my ears.</t>
+        </is>
+      </c>
+      <c r="L1235" t="inlineStr">
+        <is>
+          <t>売上が20%増えた？それは嬉しいニュースだ。</t>
+        </is>
+      </c>
+      <c r="M1235" t="inlineStr">
+        <is>
+          <t>that's great news,I'm glad to hear that</t>
+        </is>
+      </c>
+      <c r="N1235" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1235" t="inlineStr">
+        <is>
+          <t>カジュアルな場面向け。フォーマルな場では"That's excellent news"などが無難。</t>
+        </is>
+      </c>
+      <c r="P1235" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1235" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1235" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>EX-1255</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>電話,会議</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>ミドル,フォーマル</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>Let me get back to you on that</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>その場では即答せず、後で回答すると伝える表現</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>I'm not sure about the numbers. Let me get back to you on that.</t>
+        </is>
+      </c>
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>数字については確信が持てないので、後ほど回答します。</t>
+        </is>
+      </c>
+      <c r="M1236" t="inlineStr">
+        <is>
+          <t>I'll follow up with you,let me check and get back to you</t>
+        </is>
+      </c>
+      <c r="N1236" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1236" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1236" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1236" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>EX-1256</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>同意・肯定</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>ミドル</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>We're on the same page</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>お互いの認識や理解が一致していることを確認する表現</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>Before we move on, let's make sure we're on the same page.</t>
+        </is>
+      </c>
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>先に進む前に、認識が一致しているか確認しましょう。</t>
+        </is>
+      </c>
+      <c r="K1237" t="inlineStr">
+        <is>
+          <t>Good, sounds like we're on the same page about the timeline.</t>
+        </is>
+      </c>
+      <c r="L1237" t="inlineStr">
+        <is>
+          <t>良かったです、スケジュールについては認識が一致しているようですね。</t>
+        </is>
+      </c>
+      <c r="M1237" t="inlineStr">
+        <is>
+          <t>we're in agreement,we see eye to eye</t>
+        </is>
+      </c>
+      <c r="N1237" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1237" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1237" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1237" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>EX-1257</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>依頼・断り</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>断り・保留</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>ミドル,カジュアル</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>I don't have the bandwidth right now</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>時間的・人的な余裕がなく、新しい仕事を引き受けられないことを伝える表現</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>I'd love to help, but I don't have the bandwidth right now.</t>
+        </is>
+      </c>
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>手伝いたいのはやまやまですが、今は余裕がありません。</t>
+        </is>
+      </c>
+      <c r="K1238" t="inlineStr">
+        <is>
+          <t>The team doesn't have the bandwidth to take on another project this quarter.</t>
+        </is>
+      </c>
+      <c r="L1238" t="inlineStr">
+        <is>
+          <t>今四半期、チームには新たなプロジェクトを引き受ける余裕がありません。</t>
+        </is>
+      </c>
+      <c r="M1238" t="inlineStr">
+        <is>
+          <t>I'm stretched too thin,my plate is full</t>
+        </is>
+      </c>
+      <c r="N1238" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1238" t="inlineStr">
+        <is>
+          <t>"bandwidth"はIT業界由来のビジネス俗語で、時間や処理能力の余裕を指す。</t>
+        </is>
+      </c>
+      <c r="P1238" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1238" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1238" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>EX-1258</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>会議</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>Let's table this discussion</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>この議論を今は取り扱わず、後回しにしようという提案</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>We're running out of time, so let's table this discussion for now.</t>
+        </is>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>時間がなくなってきたので、この議論は一旦保留にしましょう。</t>
+        </is>
+      </c>
+      <c r="K1239" t="inlineStr">
+        <is>
+          <t>I suggest we table this item and revisit it next meeting.</t>
+        </is>
+      </c>
+      <c r="L1239" t="inlineStr">
+        <is>
+          <t>この議題は保留にして、次回の会議で再度扱うことを提案します。</t>
+        </is>
+      </c>
+      <c r="M1239" t="inlineStr">
+        <is>
+          <t>let's shelve this for now,let's set this aside</t>
+        </is>
+      </c>
+      <c r="N1239" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="O1239" t="inlineStr">
+        <is>
+          <t>"table"は米では「保留にする」、英では逆に「今すぐ議題に上げる」という意味になるため、相手が米式か英式か注意。</t>
+        </is>
+      </c>
+      <c r="P1239" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1239" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>EX-1259</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>プレゼン</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>Let me walk you through the numbers</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>数字やデータを一つずつ順を追って説明するという表現</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>Let me walk you through the numbers before we discuss next steps.</t>
+        </is>
+      </c>
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>次のステップを話し合う前に、数字を順を追ってご説明します。</t>
+        </is>
+      </c>
+      <c r="K1240" t="inlineStr">
+        <is>
+          <t>I'll walk you through the quarterly results slide by slide.</t>
+        </is>
+      </c>
+      <c r="L1240" t="inlineStr">
+        <is>
+          <t>四半期の業績についてスライドごとに順を追ってご説明します。</t>
+        </is>
+      </c>
+      <c r="M1240" t="inlineStr">
+        <is>
+          <t>let me take you through the data,let me break down the figures</t>
+        </is>
+      </c>
+      <c r="N1240" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1240" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1240" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1240" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>EX-1260</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>交渉</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>フォーマル,ミドル</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>Let's find a middle ground</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>双方が納得できる妥協点を探そうという表現</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>Neither side is happy, so let's find a middle ground.</t>
+        </is>
+      </c>
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>どちらも満足していないので、妥協点を見つけましょう。</t>
+        </is>
+      </c>
+      <c r="K1241" t="inlineStr">
+        <is>
+          <t>I'm confident we can find a middle ground that works for both parties.</t>
+        </is>
+      </c>
+      <c r="L1241" t="inlineStr">
+        <is>
+          <t>双方にとって納得できる妥協点を見つけられると確信しています。</t>
+        </is>
+      </c>
+      <c r="M1241" t="inlineStr">
+        <is>
+          <t>meet in the middle,reach a compromise</t>
+        </is>
+      </c>
+      <c r="N1241" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
+      <c r="P1241" t="inlineStr">
+        <is>
+          <t>AI生成のみ</t>
+        </is>
+      </c>
+      <c r="R1241" t="inlineStr">
+        <is>
+          <t>公開</t>
+        </is>
+      </c>
+      <c r="S1241" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
